--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\test\network_proj_dns_updated\NO_MPLS_SAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\test\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9EB89D-D4C8-4E49-AEC6-B889D00C2612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7271D11B-77E3-4B85-80BD-ECEFFD078E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="65">
   <si>
     <t>site</t>
   </si>
@@ -86,6 +86,9 @@
     <t>DHCP</t>
   </si>
   <si>
+    <t>dns_servers</t>
+  </si>
+  <si>
     <t>g0/</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
     <t>TACACS-KEY</t>
   </si>
   <si>
+    <t>192.168.255.1</t>
+  </si>
+  <si>
     <t>vrf</t>
   </si>
   <si>
@@ -197,6 +203,15 @@
     <t>tunnel 40</t>
   </si>
   <si>
+    <t>etherchan_num</t>
+  </si>
+  <si>
+    <t>span_mode</t>
+  </si>
+  <si>
+    <t>ERSPAN</t>
+  </si>
+  <si>
     <t>SW</t>
   </si>
   <si>
@@ -224,23 +239,26 @@
     <t>10.1-200.1-20.5-30.5-40.2</t>
   </si>
   <si>
-    <t>dns_servers</t>
-  </si>
-  <si>
-    <t>192.168.255.1</t>
-  </si>
-  <si>
-    <t>etherchan_num</t>
-  </si>
-  <si>
-    <t>span_port</t>
+    <t>erspan_destination</t>
+  </si>
+  <si>
+    <t>MONITORING ip</t>
+  </si>
+  <si>
+    <t>tunnel 50</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>10.51.0.10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -293,25 +311,25 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -339,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -386,108 +404,847 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="162">
+  <dxfs count="111">
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color auto="1"/>
+        <family val="2"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
         <sz val="11"/>
         <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
         <sz val="11"/>
         <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
         <sz val="11"/>
         <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
         <sz val="11"/>
         <color auto="1"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
         <color theme="1"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
         <color theme="1"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
         <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -537,1960 +1294,6 @@
     <dxf>
       <font>
         <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
@@ -2542,9 +1345,7 @@
       </font>
     </dxf>
   </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{3896F4F4-B33D-4D2A-9235-AB6CC9464053}"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2565,74 +1366,79 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="161"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="160"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="159"/>
-    <tableColumn id="10" xr3:uid="{B5E168AC-AF43-4637-AE64-122A38B00215}" name="dns_servers" dataDxfId="158"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="110"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="109"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="108"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A22:G23" headerRowDxfId="106" dataDxfId="105" totalsRowDxfId="104">
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="site" dataDxfId="103">
-      <calculatedColumnFormula>A2</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A28:L29" totalsRowShown="0">
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="SW" dataDxfId="75">
+      <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="brukernavn" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="passord" dataDxfId="101"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="vty_lines" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="secret" dataDxfId="99"/>
-    <tableColumn id="6" xr3:uid="{6E1C64EA-E908-43A5-A19B-99C374EB85DA}" name="etherchan_num" dataDxfId="98"/>
-    <tableColumn id="7" xr3:uid="{F98D4D3D-F93C-49B0-A82E-E7735EE28F3A}" name="span_port" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="MGMT Vlan" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="MGMT ip" dataDxfId="73">
+      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="gateway" dataDxfId="72">
+      <calculatedColumnFormula>$E$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="mask" dataDxfId="71">
+      <calculatedColumnFormula>$F$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="num_ports_tot" dataDxfId="70"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0B00-00000B000000}" name="skiped_ports" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="num_downlink" dataDxfId="68"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="vlan-antall" dataDxfId="67"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="intf_prefix" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="num_port_ledig" dataDxfId="65">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR($G$26="ERSPAN",$G$26="SPAN",$G$26="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{5BF5BD4F-225D-489A-8CDF-AAA6E48E5D60}" name="MONITORING ip">
+      <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell2" displayName="Tabell2" ref="A4:K8" headerRowDxfId="97" dataDxfId="96" totalsRowDxfId="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{634A8FD4-8571-4BCC-85D4-2B5A07AC1330}" name="Tabell62" displayName="Tabell62" ref="A4:K9">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="vrf" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="vlan" dataDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="interface" dataDxfId="92"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="nett id" dataDxfId="91"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="gateway" dataDxfId="90"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="mask" dataDxfId="89"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="address min" dataDxfId="88"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="address max" dataDxfId="87"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="antall-res" dataDxfId="86"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="pri-afxx" dataDxfId="85"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0B00-00000B000000}" name="pri-1-10" dataDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{51A00784-472E-49CF-AB4A-279D1E5F7B9C}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{0AC213EB-F23B-417D-9F08-693C5016AF16}" name="vlan"/>
+    <tableColumn id="3" xr3:uid="{30AB63AA-0A28-4CCA-9ED5-30D361B8C76A}" name="interface"/>
+    <tableColumn id="4" xr3:uid="{A0462661-F868-403F-A123-45EAFE448835}" name="nett id">
+      <calculatedColumnFormula>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{53173473-4848-4094-B887-60D154C9D1A3}" name="gateway">
+      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{0EF4F429-8CF5-4E5D-BAB2-A0706E9A911A}" name="mask"/>
+    <tableColumn id="7" xr3:uid="{C14D05D9-1F50-4794-BF3B-FAC75A4167EA}" name="address min">
+      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{3FDE25A7-0BCB-41BA-9E6B-B97A44D97EF9}" name="address max"/>
+    <tableColumn id="9" xr3:uid="{4F21A854-19B3-4F08-8736-4A49F53BB969}" name="antall-res" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{EB637840-6D35-4793-BE43-FF44BBC60DCE}" name="pri-afxx"/>
+    <tableColumn id="11" xr3:uid="{99B9B3BB-6A06-4A9B-B262-495BFC762025}" name="pri-1-10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{F6D2D0B3-AC19-4330-8EA4-141F9D281721}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A25:K26" totalsRowShown="0" headerRowDxfId="83">
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{560831C8-B596-49F3-902F-46F69E211EA1}" name="SW" dataDxfId="82">
-      <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{E82596D6-B991-40CC-95CB-F21DAE7174AF}" name="MGMT Vlan" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{5DE7EB2B-4947-4A2E-96FE-713844832608}" name="MGMT ip" dataDxfId="80">
-      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{96CD71AE-EBD8-4706-A140-6AC053EB9D28}" name="gateway" dataDxfId="79">
-      <calculatedColumnFormula>$E$5</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{EB395938-8C00-462D-9B40-47A26EDC7494}" name="mask" dataDxfId="78">
-      <calculatedColumnFormula>$F$5</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{BEB39869-24FF-4EAE-8FE0-8926AB748E68}" name="num_ports_tot" dataDxfId="77"/>
-    <tableColumn id="11" xr3:uid="{7B550E67-B906-4FBE-A432-CB0264AAA31E}" name="skiped_ports" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{09844D28-5E38-4CAF-946D-C86202E9AB1E}" name="num_downlink" dataDxfId="75"/>
-    <tableColumn id="7" xr3:uid="{DE656B07-9307-42AC-BAE7-A54033CC0179}" name="vlan-antall" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{C038B262-B22A-4F60-9F95-C1B59C71979D}" name="intf_prefix" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{50AA9385-3687-4437-9979-70EDBEC87403}" name="num_port_ledig" dataDxfId="72">
-      <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2 - IF($G$23,1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DEAB4086-8D7B-4A54-842E-F5FF605F74B3}" name="Tabell77" displayName="Tabell77" ref="A11:C16">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{2DDE23F5-B55E-41DC-9821-E156BB4192AB}" name="vrf"/>
+    <tableColumn id="3" xr3:uid="{4B983E8F-FEC0-4EB3-9057-196596922493}" name="loopback"/>
+    <tableColumn id="4" xr3:uid="{0BF06AAB-2838-4BC9-B570-20B71610B1A2}" name="laddr">
+      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2640,124 +1446,130 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{E77F9053-1CAC-4536-82D9-E6B1B13AB72B}" name="Tabell125" displayName="Tabell125" ref="A1:I2" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{29423377-EE71-45EC-AE04-512C3676B300}" name="Tabell18" displayName="Tabell18" ref="A1:I2" dataDxfId="51">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E6E46586-344C-4403-BB01-8EDB21806028}" name="site" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{FCB86D2F-39D7-4C90-9092-FDE5589AE525}" name="intf_prefix" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{4C85F93E-6153-4941-AADD-4019A25224B0}" name="router-id" dataDxfId="66">
+    <tableColumn id="1" xr3:uid="{C426CE2C-D824-495E-9943-0D5ED22178FC}" name="site" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{BD14A14C-CA02-4292-9A53-DBBFAEFFB41E}" name="intf_prefix" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{1E884DEF-6FA0-43D2-90D1-A472ED2D772F}" name="router-id" dataDxfId="48">
       <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5628DB3F-6470-4F58-9719-CDC226F91032}" name="brukernavn" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{994E14D8-8E32-40DE-BC25-819473006B20}" name="passord" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{2510C162-2769-467E-B239-B42884D23CB5}" name="vty_lines" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{088B1191-63A9-47D4-9FD9-A962552749AB}" name="secret" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{6F304FFA-3989-4D92-B562-E9570C9F3576}" name="tacacs_key" dataDxfId="61">
+    <tableColumn id="4" xr3:uid="{5C62684E-F01D-41F8-91C7-33CAC2305C15}" name="brukernavn" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{270B3B2A-8408-4EDF-B211-8DE1F1AB0681}" name="passord" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{9804D10C-4308-4EBD-A637-0ED093054024}" name="vty_lines" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{B0910EE6-E1E3-4DBC-9F9C-47058BA9B153}" name="secret" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{D19E2A7E-21D0-4E2A-88C9-9F37D9A65437}" name="tacacs_key" dataDxfId="43">
       <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3C3A8CE7-2167-44CF-8A83-CBF8A3913DF1}" name="dns_servers" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{068D3A60-B781-41C3-BF0A-B042AD809343}" name="dns_servers" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{E5A2C5BB-52BB-4C1C-9F21-28A1781370B3}" name="Tabell326" displayName="Tabell326" ref="A10:C14" headerRowDxfId="59" dataDxfId="58" totalsRowDxfId="57">
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{CF7349DE-C31B-4FC6-83C6-8B6628474834}" name="vrf" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{53625FDA-B6AB-45DC-B3A1-11B9F3FB71ED}" name="loopback" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{E89555BA-5F3F-4C0B-9EB1-2E878627A098}" name="laddr" dataDxfId="54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E6493EE3-7235-424D-A185-8FB87B73E9D5}" name="Tabell49" displayName="Tabell49" ref="A18:J23" dataDxfId="41">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{14E90C76-B5F6-4A0B-A8EA-BBD1846F7ADE}" name="tunnel id" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{1DD92107-ED9E-41DA-9538-710D3656664D}" name="vrf" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{9CD976E2-E62F-4E14-BA9A-80672F5BC615}" name="ip address" dataDxfId="38">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{D92BBF85-664B-4383-9EDD-4C7538D00C07}" name="mask" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{41200B4B-99C3-46CD-8919-D19A650DFC09}" name="source" dataDxfId="36">
+      <calculatedColumnFormula>$C$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{181D5214-8751-4D00-98A5-040FCE4E5826}" name="destination" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{595FE496-14D9-4619-8CC2-BDE4B0AE5AE1}" name="gre mode" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{C91D47FC-885E-4808-80A0-244D7156BD13}" name="network-id" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{D7BBBCE6-3579-420D-920C-EF19B478A7C2}" name="ipsec" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{E379820A-7358-40BE-83E4-07100824C704}" name="ipsec key" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{65A662B1-EB00-41C5-9AA3-10F1A1AB2E06}" name="Tabell427" displayName="Tabell427" ref="A16:J20" headerRowDxfId="53" dataDxfId="52" totalsRowDxfId="51">
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{2ECB4295-60F9-49EA-9455-A3D81A24F7A0}" name="tunnel id" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{13A72EC2-1D8A-4222-BD41-BE2592A960A7}" name="vrf" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{223D8914-883F-4017-82DA-E5AB71951DF9}" name="ip address" dataDxfId="48">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7318DFAD-8A4D-4CFA-8FA6-6B5A78470C24}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="30">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{F6D980DA-8008-4018-B306-D36AE654DA5F}" name="site" dataDxfId="29">
+      <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{24341D21-5A53-49ED-81C2-4F808B523A33}" name="mask" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{B6651250-1C15-4916-9DD5-0DECA970E8E7}" name="source" dataDxfId="46">
-      <calculatedColumnFormula>$C$2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{8B863BC6-A759-4605-BC9F-50C3CABE8006}" name="destination" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{BF23358A-67B7-45E8-AFF4-D27FC9289BE3}" name="gre mode" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{C26012CA-6896-40EB-BAB9-E2B7AC017DAF}" name="network-id" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{D286B9CB-857F-4868-8DE1-FD5BECC2B334}" name="ipsec" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{293E9FC5-D0E5-407D-A659-65944E4EA279}" name="ipsec key" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{0D82B2DE-B4FA-4290-8C52-0CD4C0EAA67D}" name="brukernavn" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{27B9EF4E-512F-4DAC-8CB6-D2912CB2CDDA}" name="passord" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{6414CFB9-90E9-4655-838B-2676C80D7C06}" name="vty_lines" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{D51FD26F-2705-47EA-AED0-D3C21699B51F}" name="secret" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{ABC2D354-96CD-4993-8E5C-3CCEFAEF4846}" name="etherchan_num" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{3F9B25BE-C31E-4660-A97F-1B6AF14759A6}" name="span_mode" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{CA2E1FD4-EBFB-4BF5-8DD2-EE090C2F889B}" name="erspan_destination" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1E2C2B46-26EF-4E8A-BF33-BE80A9579C3A}" name="Tabell1319253028" displayName="Tabell1319253028" ref="A22:G23" headerRowDxfId="40" dataDxfId="39" totalsRowDxfId="38">
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{DA701FF9-2640-4ED3-9CA5-2E83863ECACD}" name="site" dataDxfId="37">
-      <calculatedColumnFormula>A2</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8BA68FF7-7C6C-4673-9B18-11015BB5ECE9}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A28:L29" totalsRowShown="0">
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{8ADEAF6D-0562-4F81-93E4-69481AB6E718}" name="SW" dataDxfId="21">
+      <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A0A92227-4ED4-45A6-AF74-08CAD53943A6}" name="brukernavn" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{760D6751-0B3C-4CD1-BBA0-61B78451CA09}" name="passord" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{EFF5613C-F01D-4E28-95CD-C69E310DD62B}" name="vty_lines" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{2102378C-EB85-46A2-AACC-F9D8E8BE9DD6}" name="secret" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{B5B5EDC5-D203-4FAB-BF0C-B091D363D2A5}" name="etherchan_num" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{EEE8114C-5818-4125-AFC9-23640FDD8FDB}" name="span_port" dataDxfId="2" totalsRowDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{795F6504-A97F-4DFB-87AB-D0C3A93E475F}" name="MGMT Vlan" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{074C8822-FEF3-4C00-8C20-E4AAA6F87C8F}" name="MGMT ip" dataDxfId="19">
+      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{9E7BBCA3-A734-4692-A8F8-31365B75A063}" name="gateway" dataDxfId="18">
+      <calculatedColumnFormula>$E$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{B9D0B580-B85A-45C6-8EE9-922E6A0BDCD5}" name="mask" dataDxfId="17">
+      <calculatedColumnFormula>$F$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{136103A4-087C-4FA7-8332-FE71D232375E}" name="num_ports_tot" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{A0C44AB8-80BB-4052-A5FD-EE8530AB6772}" name="skiped_ports" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{52404E39-8CD5-4B37-A91F-C35409540738}" name="num_downlink" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{5B37CE82-3036-45D8-A546-50FF289EDBAD}" name="vlan-antall" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{79F10BE9-3D80-4FF6-A4B6-9184B24A72B4}" name="intf_prefix" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{5CB772C2-CF05-454F-BBBD-8EDEC112C696}" name="num_port_ledig" dataDxfId="11">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{065F9F0A-8DB1-44A2-B7B3-97742E5CD0E1}" name="MONITORING ip">
+      <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{769C0F37-0A83-420D-A8E1-9EE1313312AC}" name="Tabell231" displayName="Tabell231" ref="A4:K8" headerRowDxfId="31" dataDxfId="30" totalsRowDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{95B0B071-F602-4A16-BA0D-4B172283BAE9}" name="Tabell6214" displayName="Tabell6214" ref="A4:K9">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{B8E867F1-3F4C-41D0-86F6-FE265CF06F61}" name="vrf" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{D18AC450-DB0E-4854-A38A-3EB64C6DD4EB}" name="vlan" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{95B88648-5211-4200-988D-51B7D899A2BF}" name="interface" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{341E7F84-C497-477E-9951-D8B1F0235F22}" name="nett id" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{21C6E08A-5925-4A18-B96B-DC4B4117EAD0}" name="gateway" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{94861C51-5403-456D-87AF-7FC76DBA28A5}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{50243E8E-018E-40C1-A37D-ED67F4B092B0}" name="vlan"/>
+    <tableColumn id="3" xr3:uid="{A63B107D-5FA2-40D8-A99A-E280CFCC8C79}" name="interface"/>
+    <tableColumn id="4" xr3:uid="{A4267435-D295-44C3-B51E-0D1F4DD5C78B}" name="nett id">
+      <calculatedColumnFormula>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{DC7B96FF-EAB7-4E6B-8DE8-85902CDECD19}" name="gateway">
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{16980205-5AE1-4CAF-9B95-493327E6B6C3}" name="mask" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{4660DC90-F49A-4202-BD4B-71BC6584979A}" name="address min" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{1D8E9334-405A-4906-8238-47E036EC7609}" name="mask"/>
+    <tableColumn id="7" xr3:uid="{B5F525F7-1C0B-4D5D-BD37-F7614B933163}" name="address min">
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{ADA93C1E-2F32-478C-AA86-4FC2ED08742C}" name="address max" dataDxfId="21">
-      <calculatedColumnFormula>LEFT(D5,FIND(".",D5,FIND(".",D5)+1)-1)&amp;".255.254"</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{CA8441FD-37D1-4117-91A7-FA904F322160}" name="antall-res" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{1F6500D8-8B23-4118-A326-933F33A88F27}" name="pri-afxx" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{AC9A4C9B-1C06-4728-8D9C-E07A015E6BCA}" name="pri-1-10" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{BB245EF9-E497-4445-9E11-811371F6669C}" name="address max"/>
+    <tableColumn id="9" xr3:uid="{8BE1DAE2-2DC3-4655-8CD3-ACB1B1D4A0F3}" name="antall-res" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{7934A4A2-4EDA-4DF0-9DAF-BA3DD0375EC2}" name="pri-afxx"/>
+    <tableColumn id="11" xr3:uid="{D8ADAB0C-E2D6-490F-A501-86D8C692367E}" name="pri-1-10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{CEC4A60A-F98B-45B0-B6EF-F3AF53EA1619}" name="Tabell16182428253233" displayName="Tabell16182428253233" ref="A25:K26" totalsRowShown="0" headerRowDxfId="17">
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4102DBA8-76EC-46C2-97AC-C45CCA6C3959}" name="SW" dataDxfId="16">
-      <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{88524807-430F-4F05-A66A-A026753796D8}" name="MGMT Vlan" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{AC8B28E6-E5DC-45AE-BE1C-4C52D8077002}" name="MGMT ip" dataDxfId="14">
-      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{07AB9192-8CD5-4149-8F18-77D5ACBE4F9E}" name="gateway" dataDxfId="13">
-      <calculatedColumnFormula>$E$5</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{D5DA3E60-36DA-4C88-88FF-10FDD9C14A18}" name="mask" dataDxfId="12">
-      <calculatedColumnFormula>$F$5</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{4E3337F9-025D-4DA0-982C-3E70497F895A}" name="num_ports_tot" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{647707FF-22D1-4F6D-A670-EDBB67D47D4B}" name="skiped_ports" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{BE2F1799-FA72-40F2-9D10-AF25AC3BCF6E}" name="num_downlink" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{E6B5A026-07C4-4081-84E5-F4A83023F33C}" name="vlan-antall" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{88056F0E-CDA4-4FC7-B241-EE7FA7CD666F}" name="intf_prefix" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{016D87AC-4D94-4EDA-B2B6-4B3887442A16}" name="num_port_ledig" dataDxfId="6">
-      <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2 - IF($G$23,1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3B6A134F-5EA0-448A-B9C1-D15432398AB5}" name="Tabell7715" displayName="Tabell7715" ref="A11:C16">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{FA02FDEA-9585-4542-97E7-C1202764FFEC}" name="vrf"/>
+    <tableColumn id="3" xr3:uid="{840408ED-7E47-4F28-B0EB-9EDF05B3AEB2}" name="loopback"/>
+    <tableColumn id="4" xr3:uid="{FCE403FB-283B-4BF0-B99C-780D900D988D}" name="laddr">
+      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2765,17 +1577,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabell6" displayName="Tabell6" ref="A4:K8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabell6" displayName="Tabell6" ref="A4:K9">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="interface"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id">
+      <calculatedColumnFormula>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="gateway"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="157"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="106"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -2784,12 +1598,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabell7" displayName="Tabell7" ref="A10:C14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabell7" displayName="Tabell7" ref="A11:C16">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="vrf"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="loopback"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="laddr">
-      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B11)</calculatedColumnFormula>
+      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2797,15 +1611,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabell8" displayName="Tabell8" ref="A16:J20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabell8" displayName="Tabell8" ref="A18:J23">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="tunnel id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="vrf"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</calculatedColumnFormula>
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="156">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="105">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -2819,45 +1633,49 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A22:G23" dataDxfId="155">
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="154">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="8">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="7">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="153"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="152"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="151"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="150"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="149"/>
-    <tableColumn id="7" xr3:uid="{2F89DC28-B462-4A4B-9338-E6327171D3B6}" name="span_port" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{A8B916C7-04E3-4A58-909F-34F3F1BEB3E4}" name="erspan_destination" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A25:K27" totalsRowShown="0" headerRowDxfId="148">
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="147">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:L30" totalsRowShown="0">
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="104">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="146"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="145">
-      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="103"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="102">
+      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="144">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="101">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="143">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="100">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="142"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="140"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="139"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="138"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="0">
-      <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2 - IF($G$23,1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="99"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="98"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="97"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="96"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="95"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="94">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR($G$26="ERSPAN",$G$26="SPAN",$G$26="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{F45C6C35-68DB-43FE-9CBF-B6A2844A42CD}" name="MONITORING ip" dataDxfId="9">
+      <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2865,52 +1683,59 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:I2" headerRowDxfId="137" dataDxfId="136" totalsRowDxfId="135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:I2" dataDxfId="93">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="134"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="133"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="132"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="131"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="130"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="129"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="128"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="127">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="85">
       <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A5DE2194-7404-46E4-B6C2-ABF2C830FF23}" name="dns_servers" dataDxfId="126"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell3" displayName="Tabell3" ref="A10:C14" headerRowDxfId="125" dataDxfId="124" totalsRowDxfId="123">
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="vrf" dataDxfId="122"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="loopback" dataDxfId="121"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="laddr" dataDxfId="120"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="64">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="tunnel id" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="vrf" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="ip address" dataDxfId="61">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="mask" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="source" dataDxfId="59">
+      <calculatedColumnFormula>$C$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="destination" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="gre mode" dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="network-id" dataDxfId="56"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="ipsec" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="ipsec key" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell4" displayName="Tabell4" ref="A16:J20" headerRowDxfId="119" dataDxfId="118" totalsRowDxfId="117">
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="tunnel id" dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="vrf" dataDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="ip address" dataDxfId="114">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:H26" dataDxfId="83">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="site" dataDxfId="82">
+      <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="mask" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="source" dataDxfId="112">
-      <calculatedColumnFormula>$C$2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="destination" dataDxfId="111"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="gre mode" dataDxfId="110"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="network-id" dataDxfId="109"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="ipsec" dataDxfId="108"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="ipsec key" dataDxfId="107"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="brukernavn" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="passord" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="vty_lines" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="secret" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="etherchan_num" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="span_mode" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{BFD011F6-587B-466E-BAE0-BEEA0A83891E}" name="erspan_destination" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3111,20 +1936,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1002"/>
+  <dimension ref="A1:L1005"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="66" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="66" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="66" customWidth="1"/>
     <col min="6" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="66" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="39.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3156,7 +1982,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3164,32 +1990,32 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>1.1.1.0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3204,42 +2030,42 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="9">
         <v>10</v>
@@ -3248,18 +2074,18 @@
         <v>0</v>
       </c>
       <c r="D5" s="8" t="str">
-        <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <f>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.11.0.0</v>
       </c>
       <c r="E5" s="8" t="str">
-        <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <f>LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.11.0.1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="8" t="str">
-        <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <f t="shared" ref="G5:G7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.11.0.1</v>
       </c>
       <c r="H5" s="8" t="str">
@@ -3278,7 +2104,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="9">
         <v>20</v>
@@ -3287,18 +2113,18 @@
         <v>0</v>
       </c>
       <c r="D6" s="8" t="str">
-        <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;(B6+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.21.0.0</v>
       </c>
       <c r="E6" s="8" t="str">
+        <f t="shared" ref="E6:E7" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
+        <v>10.21.0.1</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>10.21.0.1</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="8" t="str">
-        <f t="shared" si="1"/>
         <v>10.21.0.1</v>
       </c>
       <c r="H6" s="8" t="str">
@@ -3317,7 +2143,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" s="9">
         <v>30</v>
@@ -3326,18 +2152,18 @@
         <v>0</v>
       </c>
       <c r="D7" s="8" t="str">
-        <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <f t="shared" si="1"/>
         <v>10.31.0.0</v>
       </c>
       <c r="E7" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>10.31.0.1</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>10.31.0.1</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <f t="shared" si="1"/>
         <v>10.31.0.1</v>
       </c>
       <c r="H7" s="8" t="str">
@@ -3356,7 +2182,7 @@
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="9">
         <v>40</v>
@@ -3365,18 +2191,18 @@
         <v>0</v>
       </c>
       <c r="D8" s="8" t="str">
-        <f>10&amp;"."&amp;(B8+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <f t="shared" si="1"/>
         <v>10.41.0.0</v>
       </c>
       <c r="E8" s="8" t="str">
-        <f t="shared" ref="E8" si="2">LEFT(D8,LEN(D8)-1)&amp;"1"</f>
+        <f t="shared" ref="E8" si="3">LEFT(D8,LEN(D8)-1)&amp;"1"</f>
         <v>10.41.0.1</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G8" s="8" t="str">
-        <f t="shared" ref="G8" si="3">LEFT(D8,LEN(D8)-1)&amp;"1"</f>
+        <f t="shared" ref="G8" si="4">LEFT(D8,LEN(D8)-1)&amp;"1"</f>
         <v>10.41.0.1</v>
       </c>
       <c r="H8" s="8" t="str">
@@ -3394,30 +2220,57 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="9">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>10.51.0.0</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <f t="shared" ref="E9" si="5">LEFT(D9,LEN(D9)-1)&amp;"1"</f>
+        <v>10.51.0.1</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="8" t="str">
+        <f t="shared" ref="G9" si="6">LEFT(D9,LEN(D9)-1)&amp;"1"</f>
+        <v>10.51.0.1</v>
+      </c>
+      <c r="H9" s="8" t="str">
+        <f>LEFT(D9,FIND(".",D9,FIND(".",D9)+1)-1)&amp;".0.254"</f>
+        <v>10.51.0.254</v>
+      </c>
+      <c r="I9" s="8">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>43</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>31</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="8">
-        <v>10</v>
-      </c>
-      <c r="C11" s="8" t="str">
-        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B11)</f>
-        <v>1.1.1.10</v>
+      <c r="A11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3425,157 +2278,123 @@
         <v>27</v>
       </c>
       <c r="B12" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="8" t="str">
-        <f t="shared" ref="C12:C14" si="4">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
-        <v>1.1.1.20</v>
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
+        <v>1.1.1.10</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1.30</v>
+        <f t="shared" ref="C13:C15" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B13)</f>
+        <v>1.1.1.20</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="8">
+        <v>30</v>
+      </c>
+      <c r="C14" s="8" t="str">
+        <f t="shared" si="7"/>
+        <v>1.1.1.30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="8">
         <v>40</v>
       </c>
-      <c r="C14" s="8" t="str">
-        <f t="shared" si="4"/>
+      <c r="C15" s="8" t="str">
+        <f t="shared" si="7"/>
         <v>1.1.1.40</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="A16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="8">
+        <v>50</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f t="shared" ref="C16" si="8">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B16)</f>
+        <v>1.1.1.50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="B18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="D18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="F18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="G18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
+      <c r="I18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="8" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</f>
+      <c r="J18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="8" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</f>
         <v>172.16.0.11</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="8" t="str">
-        <f t="shared" ref="E17:E20" si="5">$C$2</f>
-        <v>1.1.1.0</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="2">
-        <v>10</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="8" t="str">
-        <f t="shared" ref="C18:C19" si="6">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H18+$A$2)</f>
-        <v>172.16.0.21</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="8" t="str">
-        <f t="shared" si="5"/>
-        <v>1.1.1.0</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="2">
-        <v>20</v>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="8" t="str">
-        <f t="shared" si="6"/>
-        <v>172.16.0.31</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="E19" s="8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E19:E23" si="9">$C$2</f>
         <v>1.1.1.0</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="b">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>45</v>
       </c>
@@ -3583,204 +2402,306 @@
         <v>29</v>
       </c>
       <c r="C20" s="8" t="str">
-        <f t="shared" ref="C20" si="7">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
-        <v>172.16.0.41</v>
+        <f t="shared" ref="C20:C21" si="10">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
+        <v>172.16.0.21</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E20" s="8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.1.1.0</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2">
+        <v>20</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="8" t="str">
+        <f t="shared" si="10"/>
+        <v>172.16.0.31</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="8" t="str">
+        <f t="shared" si="9"/>
+        <v>1.1.1.0</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="2">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="8" t="str">
+        <f t="shared" ref="C22" si="11">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H22+$A$2)</f>
+        <v>172.16.0.41</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="8" t="str">
+        <f t="shared" si="9"/>
+        <v>1.1.1.0</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="2">
         <v>40</v>
       </c>
-      <c r="I20" s="2" t="b">
+      <c r="I22" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="8" t="str">
+        <f t="shared" ref="C23" si="12">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H23+$A$2)</f>
+        <v>172.16.0.51</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v>1.1.1.0</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="2">
+        <v>50</v>
+      </c>
+      <c r="I23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
+      <c r="F25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
         <f>A2</f>
         <v>1</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2">
+      <c r="D26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2">
         <v>2</v>
       </c>
-      <c r="G23" s="2" t="b">
+      <c r="G26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="15" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
+      <c r="K28" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
         <f>(ROW())-(ROW()-1)</f>
         <v>1</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B29" s="8">
         <v>10</v>
       </c>
-      <c r="C26" s="8" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</f>
+      <c r="C29" s="8" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</f>
         <v>10.11.0.2</v>
       </c>
-      <c r="D26" s="8" t="str">
+      <c r="D29" s="8" t="str">
         <f>$E$5</f>
         <v>10.11.0.1</v>
       </c>
-      <c r="E26" s="8" t="str">
+      <c r="E29" s="8" t="str">
         <f>$F$5</f>
         <v>255.255.0.0</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F29" s="8">
         <v>24</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G29" s="8">
         <v>1</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H29" s="11">
         <v>3</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="2">
-        <f t="shared" ref="K26:K27" si="8">IF($A26=1,F26-G26-H26*$F$23-2 - IF($G$23,1,0),F26-G26-(1+H26)*$F$23-1)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="17">
+      <c r="I29" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K29" s="2">
+        <f t="shared" ref="K29:K30" si="13">IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <v>15</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" ref="L29:L30" si="14">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
+        <v>10.51.0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="17">
         <v>2</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B30" s="17">
         <v>10</v>
       </c>
-      <c r="C27" s="17" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A27)</f>
+      <c r="C30" s="17" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A30)</f>
         <v>10.11.0.3</v>
       </c>
-      <c r="D27" s="17" t="str">
+      <c r="D30" s="17" t="str">
         <f>$E$5</f>
         <v>10.11.0.1</v>
       </c>
-      <c r="E27" s="17" t="str">
+      <c r="E30" s="17" t="str">
         <f>$F$5</f>
         <v>255.255.0.0</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F30" s="17">
         <v>24</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G30" s="17">
         <v>1</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H30" s="17">
         <v>0</v>
       </c>
-      <c r="I27" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="2">
-        <f t="shared" si="8"/>
+      <c r="I30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="K30" s="2">
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="L30" t="str">
+        <f t="shared" si="14"/>
+        <v>10.51.0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4751,10 +3672,16 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26:I27" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29:I30" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="G26" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4771,21 +3698,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K995"/>
+  <dimension ref="A1:L998"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="14" customWidth="1"/>
     <col min="2" max="2" width="13" style="14" customWidth="1"/>
-    <col min="3" max="3" width="75.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="75.85546875" style="14" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="75.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="75.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="12.5703125" style="14"/>
+    <col min="5" max="5" width="75.85546875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="75.85546875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="22" style="14" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="14" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="14" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="16384" width="12.5703125" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4814,7 +3742,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4822,405 +3750,458 @@
         <v>2</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="14" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>2.2.2.0</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>11</v>
       </c>
       <c r="H2" s="14" t="str">
         <f>'Site 1 (HUB)'!H2</f>
         <v>TACACS-KEY</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="E4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="F4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="G4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="H4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="I4" s="6" t="s">
         <v>24</v>
       </c>
+      <c r="J4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="9">
         <v>10</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="8">
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="str">
-        <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+      <c r="D5" s="8" t="str">
+        <f>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.12.0.0</v>
       </c>
-      <c r="E5" s="14" t="str">
-        <f t="shared" ref="E5:E8" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="E5" s="8" t="str">
+        <f>LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="14" t="str">
-        <f t="shared" ref="G5:G8" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="F5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="8" t="str">
+        <f t="shared" ref="G5:G9" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="H5" s="14" t="str">
+      <c r="H5" s="8" t="str">
         <f>LEFT(D5,FIND(".",D5,FIND(".",D5)+1)-1)&amp;".255.254"</f>
         <v>10.12.255.254</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="8">
         <v>10</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <v>21</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="14">
+      <c r="A6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9">
         <v>20</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="8">
         <v>0</v>
       </c>
-      <c r="D6" s="14" t="str">
-        <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+      <c r="D6" s="8" t="str">
+        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;(B6+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.22.0.0</v>
       </c>
-      <c r="E6" s="14" t="str">
+      <c r="E6" s="8" t="str">
+        <f t="shared" ref="E6:E9" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
+        <v>10.22.0.1</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>10.22.0.1</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>10.22.0.1</v>
-      </c>
-      <c r="H6" s="14" t="str">
+      <c r="H6" s="8" t="str">
         <f>LEFT(D6,FIND(".",D6,FIND(".",D6)+1)-1)&amp;".255.254"</f>
         <v>10.22.255.254</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="8">
         <v>10</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <v>11</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="9">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>10.32.0.0</v>
+      </c>
+      <c r="E7" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>10.32.0.1</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="14">
-        <v>30</v>
-      </c>
-      <c r="C7" s="14">
-        <v>0</v>
-      </c>
-      <c r="D7" s="14" t="str">
-        <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
-        <v>10.32.0.0</v>
-      </c>
-      <c r="E7" s="14" t="str">
+      <c r="G7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>10.32.0.1</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>10.32.0.1</v>
-      </c>
-      <c r="H7" s="14" t="str">
+      <c r="H7" s="8" t="str">
         <f>LEFT(D7,FIND(".",D7,FIND(".",D7)+1)-1)&amp;".255.254"</f>
         <v>10.32.255.254</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="8">
         <v>10</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7">
         <v>42</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="14">
+    <row r="8" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="9">
         <v>40</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="8">
         <v>0</v>
       </c>
-      <c r="D8" s="14" t="str">
-        <f>10&amp;"."&amp;(B8+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+      <c r="D8" s="8" t="str">
+        <f t="shared" si="1"/>
         <v>10.42.0.0</v>
       </c>
-      <c r="E8" s="14" t="str">
+      <c r="E8" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>10.42.0.1</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>10.42.0.1</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>10.42.0.1</v>
-      </c>
-      <c r="H8" s="14" t="str">
+      <c r="H8" s="8" t="str">
         <f>LEFT(D8,FIND(".",D8,FIND(".",D8)+1)-1)&amp;".255.254"</f>
         <v>10.42.255.254</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="8">
         <v>10</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8">
         <v>41</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="14" t="s">
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="9">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>10.52.0.0</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>10.52.0.1</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>10.52.0.1</v>
+      </c>
+      <c r="H9" s="8" t="str">
+        <f>LEFT(D9,FIND(".",D9,FIND(".",D9)+1)-1)&amp;".0.254"</f>
+        <v>10.52.0.254</v>
+      </c>
+      <c r="I9" s="8">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>43</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+    </row>
+    <row r="11" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+    </row>
+    <row r="12" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="8">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
+        <v>2.2.2.10</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+    </row>
+    <row r="13" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="8">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B13)</f>
+        <v>2.2.2.20</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+    </row>
+    <row r="14" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="B14" s="8">
+        <v>30</v>
+      </c>
+      <c r="C14" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>2.2.2.30</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+    </row>
+    <row r="15" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="14">
-        <v>10</v>
-      </c>
-      <c r="C11" s="14" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(B11)</f>
-        <v>2.2.2.10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
+      <c r="B15" s="8">
+        <v>40</v>
+      </c>
+      <c r="C15" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>2.2.2.40</v>
+      </c>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+    </row>
+    <row r="16" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="8">
+        <v>50</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>2.2.2.50</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="14">
-        <v>20</v>
-      </c>
-      <c r="C12" s="14" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(B12)</f>
-        <v>2.2.2.20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="14">
-        <v>30</v>
-      </c>
-      <c r="C13" s="14" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(B13)</f>
-        <v>2.2.2.30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="14">
-        <v>40</v>
-      </c>
-      <c r="C14" s="14" t="str">
-        <f t="shared" ref="C14" si="2">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B14)</f>
-        <v>2.2.2.40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="14" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</f>
-        <v>172.16.0.12</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="14" t="str">
-        <f t="shared" ref="E17:E20" si="3">$C$2</f>
-        <v>2.2.2.0</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="14">
-        <v>10</v>
-      </c>
-      <c r="I17" s="14">
-        <f t="array" ref="I17">'Site 1 (HUB)'!I17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="14" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H18+$A$2)</f>
-        <v>172.16.0.22</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>2.2.2.0</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="14">
-        <v>20</v>
-      </c>
-      <c r="I18" s="14" cm="1">
-        <f t="array" ref="I18">'Site 1 (HUB)'!I18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>28</v>
       </c>
       <c r="C19" s="14" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</f>
-        <v>172.16.0.32</v>
+        <v>172.16.0.12</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E19:E23" si="4">$C$2</f>
         <v>2.2.2.0</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="14">
-        <v>30</v>
-      </c>
-      <c r="I19" s="14" t="b">
+        <v>44</v>
+      </c>
+      <c r="H19" s="22">
+        <v>10</v>
+      </c>
+      <c r="I19" s="14">
         <f t="array" ref="I19">'Site 1 (HUB)'!I19</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>45</v>
       </c>
@@ -5228,157 +4209,256 @@
         <v>29</v>
       </c>
       <c r="C20" s="14" t="str">
-        <f t="shared" ref="C20" si="4">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
+        <v>172.16.0.22</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="22">
+        <v>20</v>
+      </c>
+      <c r="I20" s="14" cm="1">
+        <f t="array" ref="I20">'Site 1 (HUB)'!I20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="14" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H21+$A$2)</f>
+        <v>172.16.0.32</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="22">
+        <v>30</v>
+      </c>
+      <c r="I21" s="14" t="b">
+        <f>'Site 1 (HUB)'!I21</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="14" t="str">
+        <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H22+$A$2)</f>
         <v>172.16.0.42</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="14" t="str">
-        <f t="shared" si="3"/>
+      <c r="D22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="14" t="str">
+        <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
-      <c r="G20" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="14">
+      <c r="G22" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="22">
         <v>40</v>
       </c>
-      <c r="I20" s="14" t="b">
-        <f>'Site 1 (HUB)'!I20</f>
+      <c r="I22" s="14" t="b">
+        <f>'Site 1 (HUB)'!I22</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>172.16.0.52</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="19">
+        <v>50</v>
+      </c>
+      <c r="I23" s="14" t="b">
+        <f>'Site 1 (HUB)'!I23</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B25" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C25" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D25" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E25" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14">
+      <c r="F25" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="14">
         <f>A2</f>
         <v>2</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="B26" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="C26" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="14">
+      <c r="D26" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="14">
         <v>2</v>
       </c>
-      <c r="G23" s="14" t="b">
+      <c r="G26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="15" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
+      <c r="K28" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
         <f>(ROW())-(ROW()-1)</f>
         <v>1</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B29" s="8">
         <v>10</v>
       </c>
-      <c r="C26" s="8" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</f>
+      <c r="C29" s="8" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</f>
         <v>10.12.0.2</v>
       </c>
-      <c r="D26" s="8" t="str">
+      <c r="D29" s="8" t="str">
         <f>$E$5</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="E26" s="8" t="str">
+      <c r="E29" s="8" t="str">
         <f>$F$5</f>
         <v>255.255.0.0</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F29" s="8">
         <v>24</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G29" s="8">
         <v>1</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H29" s="11">
         <v>0</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="2">
-        <f>IF($A26=1,F26-G26-H26*$F$23-2 - IF($G$23,1,0),F26-G26-(1+H26)*$F$23-1)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="I29" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K29" s="2">
+        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <v>21</v>
+      </c>
+      <c r="L29" t="str">
+        <f>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
+        <v>10.52.0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6342,10 +5422,16 @@
     <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26" xr:uid="{D1026AEF-88A1-41AD-A0F5-089AD26E947E}">
-      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="G26" xr:uid="{00000000-0002-0000-0100-000001000000}">
+      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6362,20 +5448,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="75.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="75.85546875" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="75.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="75.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="58.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
@@ -6404,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
@@ -6414,30 +5501,30 @@
         <v>3</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="14" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>3.3.3.0</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>11</v>
       </c>
       <c r="H2" s="14" t="str">
         <f>'Site 1 (HUB)'!H2</f>
         <v>TACACS-KEY</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
@@ -6455,452 +5542,390 @@
       <c r="J3" s="14"/>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="14" t="s">
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="E4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="F4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="G4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="H4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="I4" s="6" t="s">
         <v>24</v>
       </c>
+      <c r="J4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="9">
         <v>10</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="8">
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="str">
-        <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+      <c r="D5" s="8" t="str">
+        <f>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.13.0.0</v>
       </c>
-      <c r="E5" s="14" t="str">
-        <f t="shared" ref="E5:E8" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="E5" s="8" t="str">
+        <f>LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.13.0.1</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="14" t="str">
-        <f t="shared" ref="G5:G8" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+      <c r="F5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="8" t="str">
+        <f t="shared" ref="G5:G9" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.13.0.1</v>
       </c>
-      <c r="H5" s="14" t="str">
+      <c r="H5" s="8" t="str">
         <f>LEFT(D5,FIND(".",D5,FIND(".",D5)+1)-1)&amp;".255.254"</f>
         <v>10.13.255.254</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="8">
         <v>10</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <v>21</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="14">
+      <c r="A6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9">
         <v>20</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="8">
         <v>0</v>
       </c>
-      <c r="D6" s="14" t="str">
-        <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+      <c r="D6" s="8" t="str">
+        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;(B6+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.23.0.0</v>
       </c>
-      <c r="E6" s="14" t="str">
+      <c r="E6" s="8" t="str">
+        <f t="shared" ref="E6:E9" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
+        <v>10.23.0.1</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>10.23.0.1</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>10.23.0.1</v>
-      </c>
-      <c r="H6" s="14" t="str">
+      <c r="H6" s="8" t="str">
         <f>LEFT(D6,FIND(".",D6,FIND(".",D6)+1)-1)&amp;".255.254"</f>
         <v>10.23.255.254</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="8">
         <v>10</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <v>11</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="9">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>10.33.0.0</v>
+      </c>
+      <c r="E7" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>10.33.0.1</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="14">
-        <v>30</v>
-      </c>
-      <c r="C7" s="14">
-        <v>0</v>
-      </c>
-      <c r="D7" s="14" t="str">
-        <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
-        <v>10.33.0.0</v>
-      </c>
-      <c r="E7" s="14" t="str">
+      <c r="G7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>10.33.0.1</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>10.33.0.1</v>
-      </c>
-      <c r="H7" s="14" t="str">
+      <c r="H7" s="8" t="str">
         <f>LEFT(D7,FIND(".",D7,FIND(".",D7)+1)-1)&amp;".255.254"</f>
         <v>10.33.255.254</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="8">
         <v>10</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7">
         <v>42</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="14">
+      <c r="A8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="9">
         <v>40</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="8">
         <v>0</v>
       </c>
-      <c r="D8" s="14" t="str">
-        <f>10&amp;"."&amp;(B8+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+      <c r="D8" s="8" t="str">
+        <f t="shared" si="1"/>
         <v>10.43.0.0</v>
       </c>
-      <c r="E8" s="14" t="str">
+      <c r="E8" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>10.43.0.1</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>10.43.0.1</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>10.43.0.1</v>
-      </c>
-      <c r="H8" s="14" t="str">
+      <c r="H8" s="8" t="str">
         <f>LEFT(D8,FIND(".",D8,FIND(".",D8)+1)-1)&amp;".255.254"</f>
         <v>10.43.255.254</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="8">
         <v>10</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8">
         <v>41</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-    </row>
-    <row r="10" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="14" t="s">
+      <c r="A9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="9">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>10.53.0.0</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>10.53.0.1</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>10.53.0.1</v>
+      </c>
+      <c r="H9" s="8" t="str">
+        <f>LEFT(D9,FIND(".",D9,FIND(".",D9)+1)-1)&amp;".0.254"</f>
+        <v>10.53.0.254</v>
+      </c>
+      <c r="I9" s="8">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>43</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="8">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
+        <v>3.3.3.10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="8">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B13)</f>
+        <v>3.3.3.20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="B14" s="8">
+        <v>30</v>
+      </c>
+      <c r="C14" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>3.3.3.30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-    </row>
-    <row r="11" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="14">
-        <v>10</v>
-      </c>
-      <c r="C11" s="14" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(B11)</f>
-        <v>3.3.3.10</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-    </row>
-    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="14">
-        <v>20</v>
-      </c>
-      <c r="C12" s="14" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(B12)</f>
-        <v>3.3.3.20</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-    </row>
-    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="14">
-        <v>30</v>
-      </c>
-      <c r="C13" s="14" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(B13)</f>
-        <v>3.3.3.30</v>
-      </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-    </row>
-    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="14">
+      <c r="B15" s="8">
         <v>40</v>
       </c>
-      <c r="C14" s="14" t="str">
-        <f t="shared" ref="C14" si="2">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B14)</f>
+      <c r="C15" s="8" t="str">
+        <f t="shared" si="3"/>
         <v>3.3.3.40</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-    </row>
-    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
     </row>
     <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" s="14"/>
-    </row>
-    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="14" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</f>
-        <v>172.16.0.13</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="14" t="str">
-        <f t="shared" ref="E17:E20" si="3">$C$2</f>
-        <v>3.3.3.0</v>
-      </c>
+      <c r="A16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="8">
+        <v>50</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>3.3.3.50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
       <c r="F17" s="14"/>
-      <c r="G17" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="14">
-        <v>10</v>
-      </c>
-      <c r="I17" s="14">
-        <f t="array" ref="I17">'Site 1 (HUB)'!I17</f>
-        <v>0</v>
-      </c>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="14"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B18" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="C18" s="14" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H18+$A$2)</f>
-        <v>172.16.0.23</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="14">
-        <v>20</v>
-      </c>
-      <c r="I18" s="14" cm="1">
-        <f t="array" ref="I18">'Site 1 (HUB)'!I18</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-    </row>
-    <row r="19" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>28</v>
       </c>
       <c r="C19" s="14" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</f>
-        <v>172.16.0.33</v>
+        <v>172.16.0.13</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E19:E23" si="4">$C$2</f>
         <v>3.3.3.0</v>
       </c>
       <c r="F19" s="14"/>
       <c r="G19" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="14">
-        <v>30</v>
-      </c>
-      <c r="I19" s="14" t="b">
+        <v>44</v>
+      </c>
+      <c r="H19" s="22">
+        <v>10</v>
+      </c>
+      <c r="I19" s="14">
         <f t="array" ref="I19">'Site 1 (HUB)'!I19</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="14"/>
     </row>
-    <row r="20" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>45</v>
       </c>
@@ -6908,99 +5933,127 @@
         <v>29</v>
       </c>
       <c r="C20" s="14" t="str">
-        <f t="shared" ref="C20" si="4">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
-        <v>172.16.0.43</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
+        <v>172.16.0.23</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E20" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.3.3.0</v>
       </c>
       <c r="F20" s="14"/>
       <c r="G20" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="14">
-        <v>40</v>
-      </c>
-      <c r="I20" s="14" t="b">
-        <f>'Site 1 (HUB)'!I20</f>
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="H20" s="22">
+        <v>20</v>
+      </c>
+      <c r="I20" s="14" cm="1">
+        <f t="array" ref="I20">'Site 1 (HUB)'!I20</f>
+        <v>0</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+    <row r="21" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="14" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H21+$A$2)</f>
+        <v>172.16.0.33</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
       <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
+      <c r="G21" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="22">
+        <v>30</v>
+      </c>
+      <c r="I21" s="14" t="b">
+        <f>'Site 1 (HUB)'!I21</f>
+        <v>1</v>
+      </c>
       <c r="J21" s="14"/>
       <c r="K21" s="14"/>
     </row>
-    <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C22" s="14" t="str">
+        <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H22+$A$2)</f>
+        <v>172.16.0.43</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>57</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="E22" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F22" s="14"/>
       <c r="G22" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
+        <v>44</v>
+      </c>
+      <c r="H22" s="22">
+        <v>40</v>
+      </c>
+      <c r="I22" s="14" t="b">
+        <f>'Site 1 (HUB)'!I22</f>
+        <v>1</v>
+      </c>
       <c r="J22" s="14"/>
       <c r="K22" s="14"/>
     </row>
-    <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A23" s="14">
-        <f>A2</f>
-        <v>3</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="14">
-        <v>2</v>
-      </c>
-      <c r="G23" s="14" t="b">
+    <row r="23" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>172.16.0.53</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="19">
+        <v>50</v>
+      </c>
+      <c r="I23" s="14" t="b">
+        <f>'Site 1 (HUB)'!I23</f>
         <v>1</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+      <c r="J23" s="21"/>
       <c r="K23" s="14"/>
     </row>
-    <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="14"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -7013,82 +6066,66 @@
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="25" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="15" t="s">
+    <row r="25" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="15" t="s">
+      <c r="G25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="H25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+    </row>
+    <row r="26" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="14">
+        <f>A2</f>
+        <v>3</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="14">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H25" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <f>(ROW())-(ROW()-1)</f>
-        <v>1</v>
-      </c>
-      <c r="B26" s="8">
-        <v>10</v>
-      </c>
-      <c r="C26" s="8" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</f>
-        <v>10.13.0.2</v>
-      </c>
-      <c r="D26" s="8" t="str">
-        <f>$E$5</f>
-        <v>10.13.0.1</v>
-      </c>
-      <c r="E26" s="8" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F26" s="8">
-        <v>24</v>
-      </c>
-      <c r="G26" s="8">
-        <v>1</v>
-      </c>
-      <c r="H26" s="11">
-        <v>0</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="2">
-        <f>IF($A26=1,F26-G26-H26*$F$23-2 - IF($G$23,1,0),F26-G26-(1+H26)*$F$23-1)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="H26" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+    </row>
+    <row r="27" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -7101,10 +6138,95 @@
       <c r="J27" s="14"/>
       <c r="K27" s="14"/>
     </row>
+    <row r="28" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <f>(ROW())-(ROW()-1)</f>
+        <v>1</v>
+      </c>
+      <c r="B29" s="8">
+        <v>10</v>
+      </c>
+      <c r="C29" s="8" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</f>
+        <v>10.13.0.2</v>
+      </c>
+      <c r="D29" s="8" t="str">
+        <f>$E$5</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="E29" s="8" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F29" s="8">
+        <v>24</v>
+      </c>
+      <c r="G29" s="8">
+        <v>1</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K29" s="2">
+        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <v>21</v>
+      </c>
+      <c r="L29" t="str">
+        <f>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
+        <v>10.53.0.2</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26" xr:uid="{44077420-E806-44F5-BB6E-60A45CE71946}">
-      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{7287270F-FA36-42B0-936E-CB6AE119A013}">
+      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="G26" xr:uid="{96B8245A-DA04-4B17-A070-977D41BECEDD}">
+      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\test\NO_MPLS_SAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7271D11B-77E3-4B85-80BD-ECEFFD078E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D57BF4F-8D10-450D-B670-CDBF6187C342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -357,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -404,20 +404,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -427,6 +418,454 @@
   <dxfs count="111">
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <sz val="11"/>
         <color auto="1"/>
         <family val="2"/>
@@ -486,830 +925,6 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <u val="none"/>
         <sz val="10"/>
         <color theme="1"/>
@@ -1341,6 +956,383 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
     </dxf>
@@ -1366,10 +1358,10 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="110"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="109"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="108"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="107"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="66"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1378,26 +1370,26 @@
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A28:L29" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="SW" dataDxfId="75">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="SW" dataDxfId="80">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="MGMT Vlan" dataDxfId="74"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="MGMT ip" dataDxfId="73">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="MGMT Vlan" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="MGMT ip" dataDxfId="78">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="gateway" dataDxfId="72">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="gateway" dataDxfId="77">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="mask" dataDxfId="71">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="mask" dataDxfId="76">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="num_ports_tot" dataDxfId="70"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0B00-00000B000000}" name="skiped_ports" dataDxfId="69"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="num_downlink" dataDxfId="68"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="vlan-antall" dataDxfId="67"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="intf_prefix" dataDxfId="66"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="num_port_ledig" dataDxfId="65">
-      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR($G$26="ERSPAN",$G$26="SPAN",$G$26="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="num_ports_tot" dataDxfId="75"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0B00-00000B000000}" name="skiped_ports" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="num_downlink" dataDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="vlan-antall" dataDxfId="72"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="intf_prefix" dataDxfId="71"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="num_port_ledig" dataDxfId="70">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2,F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{5BF5BD4F-225D-489A-8CDF-AAA6E48E5D60}" name="MONITORING ip">
       <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
@@ -1424,7 +1416,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{3FDE25A7-0BCB-41BA-9E6B-B97A44D97EF9}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{4F21A854-19B3-4F08-8736-4A49F53BB969}" name="antall-res" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{4F21A854-19B3-4F08-8736-4A49F53BB969}" name="antall-res" dataDxfId="69"/>
     <tableColumn id="10" xr3:uid="{EB637840-6D35-4793-BE43-FF44BBC60DCE}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{99B9B3BB-6A06-4A9B-B262-495BFC762025}" name="pri-1-10"/>
   </tableColumns>
@@ -1446,61 +1438,61 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{29423377-EE71-45EC-AE04-512C3676B300}" name="Tabell18" displayName="Tabell18" ref="A1:I2" dataDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{29423377-EE71-45EC-AE04-512C3676B300}" name="Tabell18" displayName="Tabell18" ref="A1:I2" dataDxfId="41">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C426CE2C-D824-495E-9943-0D5ED22178FC}" name="site" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{BD14A14C-CA02-4292-9A53-DBBFAEFFB41E}" name="intf_prefix" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{1E884DEF-6FA0-43D2-90D1-A472ED2D772F}" name="router-id" dataDxfId="48">
+    <tableColumn id="1" xr3:uid="{C426CE2C-D824-495E-9943-0D5ED22178FC}" name="site" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{BD14A14C-CA02-4292-9A53-DBBFAEFFB41E}" name="intf_prefix" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{1E884DEF-6FA0-43D2-90D1-A472ED2D772F}" name="router-id" dataDxfId="38">
       <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5C62684E-F01D-41F8-91C7-33CAC2305C15}" name="brukernavn" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{270B3B2A-8408-4EDF-B211-8DE1F1AB0681}" name="passord" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{9804D10C-4308-4EBD-A637-0ED093054024}" name="vty_lines" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{B0910EE6-E1E3-4DBC-9F9C-47058BA9B153}" name="secret" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{D19E2A7E-21D0-4E2A-88C9-9F37D9A65437}" name="tacacs_key" dataDxfId="43">
+    <tableColumn id="4" xr3:uid="{5C62684E-F01D-41F8-91C7-33CAC2305C15}" name="brukernavn" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{270B3B2A-8408-4EDF-B211-8DE1F1AB0681}" name="passord" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{9804D10C-4308-4EBD-A637-0ED093054024}" name="vty_lines" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{B0910EE6-E1E3-4DBC-9F9C-47058BA9B153}" name="secret" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{D19E2A7E-21D0-4E2A-88C9-9F37D9A65437}" name="tacacs_key" dataDxfId="33">
       <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{068D3A60-B781-41C3-BF0A-B042AD809343}" name="dns_servers" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{068D3A60-B781-41C3-BF0A-B042AD809343}" name="dns_servers" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E6493EE3-7235-424D-A185-8FB87B73E9D5}" name="Tabell49" displayName="Tabell49" ref="A18:J23" dataDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E6493EE3-7235-424D-A185-8FB87B73E9D5}" name="Tabell49" displayName="Tabell49" ref="A18:J23" dataDxfId="31">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{14E90C76-B5F6-4A0B-A8EA-BBD1846F7ADE}" name="tunnel id" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{1DD92107-ED9E-41DA-9538-710D3656664D}" name="vrf" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{9CD976E2-E62F-4E14-BA9A-80672F5BC615}" name="ip address" dataDxfId="38">
+    <tableColumn id="1" xr3:uid="{14E90C76-B5F6-4A0B-A8EA-BBD1846F7ADE}" name="tunnel id" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{1DD92107-ED9E-41DA-9538-710D3656664D}" name="vrf" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{9CD976E2-E62F-4E14-BA9A-80672F5BC615}" name="ip address" dataDxfId="28">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D92BBF85-664B-4383-9EDD-4C7538D00C07}" name="mask" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{41200B4B-99C3-46CD-8919-D19A650DFC09}" name="source" dataDxfId="36">
+    <tableColumn id="4" xr3:uid="{D92BBF85-664B-4383-9EDD-4C7538D00C07}" name="mask" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{41200B4B-99C3-46CD-8919-D19A650DFC09}" name="source" dataDxfId="26">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{181D5214-8751-4D00-98A5-040FCE4E5826}" name="destination" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{595FE496-14D9-4619-8CC2-BDE4B0AE5AE1}" name="gre mode" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{C91D47FC-885E-4808-80A0-244D7156BD13}" name="network-id" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{D7BBBCE6-3579-420D-920C-EF19B478A7C2}" name="ipsec" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{E379820A-7358-40BE-83E4-07100824C704}" name="ipsec key" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{181D5214-8751-4D00-98A5-040FCE4E5826}" name="destination" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{595FE496-14D9-4619-8CC2-BDE4B0AE5AE1}" name="gre mode" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{C91D47FC-885E-4808-80A0-244D7156BD13}" name="network-id" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{D7BBBCE6-3579-420D-920C-EF19B478A7C2}" name="ipsec" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{E379820A-7358-40BE-83E4-07100824C704}" name="ipsec key" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7318DFAD-8A4D-4CFA-8FA6-6B5A78470C24}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7318DFAD-8A4D-4CFA-8FA6-6B5A78470C24}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="20">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F6D980DA-8008-4018-B306-D36AE654DA5F}" name="site" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{F6D980DA-8008-4018-B306-D36AE654DA5F}" name="site" dataDxfId="19">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0D82B2DE-B4FA-4290-8C52-0CD4C0EAA67D}" name="brukernavn" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{27B9EF4E-512F-4DAC-8CB6-D2912CB2CDDA}" name="passord" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{6414CFB9-90E9-4655-838B-2676C80D7C06}" name="vty_lines" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{D51FD26F-2705-47EA-AED0-D3C21699B51F}" name="secret" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{ABC2D354-96CD-4993-8E5C-3CCEFAEF4846}" name="etherchan_num" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{3F9B25BE-C31E-4660-A97F-1B6AF14759A6}" name="span_mode" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{CA2E1FD4-EBFB-4BF5-8DD2-EE090C2F889B}" name="erspan_destination" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{0D82B2DE-B4FA-4290-8C52-0CD4C0EAA67D}" name="brukernavn" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{27B9EF4E-512F-4DAC-8CB6-D2912CB2CDDA}" name="passord" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{6414CFB9-90E9-4655-838B-2676C80D7C06}" name="vty_lines" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{D51FD26F-2705-47EA-AED0-D3C21699B51F}" name="secret" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{ABC2D354-96CD-4993-8E5C-3CCEFAEF4846}" name="etherchan_num" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{3F9B25BE-C31E-4660-A97F-1B6AF14759A6}" name="span_mode" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{CA2E1FD4-EBFB-4BF5-8DD2-EE090C2F889B}" name="erspan_destination" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1509,26 +1501,26 @@
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8BA68FF7-7C6C-4673-9B18-11015BB5ECE9}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A28:L29" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{8ADEAF6D-0562-4F81-93E4-69481AB6E718}" name="SW" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{8ADEAF6D-0562-4F81-93E4-69481AB6E718}" name="SW" dataDxfId="11">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{795F6504-A97F-4DFB-87AB-D0C3A93E475F}" name="MGMT Vlan" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{074C8822-FEF3-4C00-8C20-E4AAA6F87C8F}" name="MGMT ip" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{795F6504-A97F-4DFB-87AB-D0C3A93E475F}" name="MGMT Vlan" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{074C8822-FEF3-4C00-8C20-E4AAA6F87C8F}" name="MGMT ip" dataDxfId="9">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9E7BBCA3-A734-4692-A8F8-31365B75A063}" name="gateway" dataDxfId="18">
+    <tableColumn id="4" xr3:uid="{9E7BBCA3-A734-4692-A8F8-31365B75A063}" name="gateway" dataDxfId="8">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B9D0B580-B85A-45C6-8EE9-922E6A0BDCD5}" name="mask" dataDxfId="17">
+    <tableColumn id="5" xr3:uid="{B9D0B580-B85A-45C6-8EE9-922E6A0BDCD5}" name="mask" dataDxfId="7">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{136103A4-087C-4FA7-8332-FE71D232375E}" name="num_ports_tot" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{A0C44AB8-80BB-4052-A5FD-EE8530AB6772}" name="skiped_ports" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{52404E39-8CD5-4B37-A91F-C35409540738}" name="num_downlink" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{5B37CE82-3036-45D8-A546-50FF289EDBAD}" name="vlan-antall" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{79F10BE9-3D80-4FF6-A4B6-9184B24A72B4}" name="intf_prefix" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{5CB772C2-CF05-454F-BBBD-8EDEC112C696}" name="num_port_ledig" dataDxfId="11">
-      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{136103A4-087C-4FA7-8332-FE71D232375E}" name="num_ports_tot" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{A0C44AB8-80BB-4052-A5FD-EE8530AB6772}" name="skiped_ports" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{52404E39-8CD5-4B37-A91F-C35409540738}" name="num_downlink" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5B37CE82-3036-45D8-A546-50FF289EDBAD}" name="vlan-antall" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{79F10BE9-3D80-4FF6-A4B6-9184B24A72B4}" name="intf_prefix" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{5CB772C2-CF05-454F-BBBD-8EDEC112C696}" name="num_port_ledig" dataDxfId="0">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2,F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{065F9F0A-8DB1-44A2-B7B3-97742E5CD0E1}" name="MONITORING ip">
       <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
@@ -1555,7 +1547,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{BB245EF9-E497-4445-9E11-811371F6669C}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{8BE1DAE2-2DC3-4655-8CD3-ACB1B1D4A0F3}" name="antall-res" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{8BE1DAE2-2DC3-4655-8CD3-ACB1B1D4A0F3}" name="antall-res" dataDxfId="1"/>
     <tableColumn id="10" xr3:uid="{7934A4A2-4EDA-4DF0-9DAF-BA3DD0375EC2}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{D8ADAB0C-E2D6-490F-A501-86D8C692367E}" name="pri-1-10"/>
   </tableColumns>
@@ -1589,7 +1581,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="106"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="64"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1619,7 +1611,7 @@
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="105">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="63">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -1633,18 +1625,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="62">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="61">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{A8B916C7-04E3-4A58-909F-34F3F1BEB3E4}" name="erspan_destination" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{A8B916C7-04E3-4A58-909F-34F3F1BEB3E4}" name="erspan_destination" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1653,28 +1645,28 @@
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:L30" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="104">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="53">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="103"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="102">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="51">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="101">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="50">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="100">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="49">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="99"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="98"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="97"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="96"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="95"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="94">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="43">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR($G$26="ERSPAN",$G$26="SPAN",$G$26="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F45C6C35-68DB-43FE-9CBF-B6A2844A42CD}" name="MONITORING ip" dataDxfId="9">
+    <tableColumn id="12" xr3:uid="{F45C6C35-68DB-43FE-9CBF-B6A2844A42CD}" name="MONITORING ip" dataDxfId="42">
       <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1683,59 +1675,59 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:I2" dataDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:I2" dataDxfId="110">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="88"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="86"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="85">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="108"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="107"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="106"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="105"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="104"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="103"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="102">
       <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="101"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="100">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="tunnel id" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="vrf" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="ip address" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="tunnel id" dataDxfId="99"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="vrf" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="ip address" dataDxfId="97">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="mask" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="source" dataDxfId="59">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="mask" dataDxfId="96"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="source" dataDxfId="95">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="destination" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="gre mode" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="network-id" dataDxfId="56"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="ipsec" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="ipsec key" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="destination" dataDxfId="94"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="gre mode" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="network-id" dataDxfId="92"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="ipsec" dataDxfId="91"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="ipsec key" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:H26" dataDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:H26" dataDxfId="89">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="site" dataDxfId="82">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="site" dataDxfId="88">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="brukernavn" dataDxfId="81"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="passord" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="vty_lines" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="secret" dataDxfId="78"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="etherchan_num" dataDxfId="77"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="span_mode" dataDxfId="76"/>
-    <tableColumn id="8" xr3:uid="{BFD011F6-587B-466E-BAE0-BEEA0A83891E}" name="erspan_destination" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="brukernavn" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="passord" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="vty_lines" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="secret" dataDxfId="84"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="etherchan_num" dataDxfId="83"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="span_mode" dataDxfId="82"/>
+    <tableColumn id="8" xr3:uid="{BFD011F6-587B-466E-BAE0-BEEA0A83891E}" name="erspan_destination" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2496,7 +2488,7 @@
       <c r="D23" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="18" t="str">
+      <c r="E23" s="8" t="str">
         <f t="shared" si="9"/>
         <v>1.1.1.0</v>
       </c>
@@ -2570,7 +2562,7 @@
       <c r="G26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="20" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2649,11 +2641,11 @@
         <v>10</v>
       </c>
       <c r="K29" s="2">
-        <f t="shared" ref="K29:K30" si="13">IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
-        <v>15</v>
+        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN", UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <v>14</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" ref="L29:L30" si="14">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
+        <f t="shared" ref="L29:L30" si="13">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
         <v>10.51.0.2</v>
       </c>
     </row>
@@ -2692,11 +2684,11 @@
         <v>10</v>
       </c>
       <c r="K30" s="2">
+        <f>IF($A30=1,F30-G30-H30*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F30-G30-(1+H30)*$F$26-1)</f>
+        <v>20</v>
+      </c>
+      <c r="L30" t="str">
         <f t="shared" si="13"/>
-        <v>20</v>
-      </c>
-      <c r="L30" t="str">
-        <f t="shared" si="14"/>
         <v>10.51.0.3</v>
       </c>
     </row>
@@ -4193,7 +4185,7 @@
       <c r="G19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="14">
         <v>10</v>
       </c>
       <c r="I19" s="14">
@@ -4222,7 +4214,7 @@
       <c r="G20" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="14">
         <v>20</v>
       </c>
       <c r="I20" s="14" cm="1">
@@ -4251,7 +4243,7 @@
       <c r="G21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="14">
         <v>30</v>
       </c>
       <c r="I21" s="14" t="b">
@@ -4280,7 +4272,7 @@
       <c r="G22" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="14">
         <v>40</v>
       </c>
       <c r="I22" s="14" t="b">
@@ -4289,35 +4281,35 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="19" t="str">
+      <c r="C23" s="18" t="str">
         <f t="shared" si="5"/>
         <v>172.16.0.52</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="20" t="str">
+      <c r="E23" s="18" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19" t="s">
+      <c r="F23" s="18"/>
+      <c r="G23" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="18">
         <v>50</v>
       </c>
       <c r="I23" s="14" t="b">
         <f>'Site 1 (HUB)'!I23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="19"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4369,7 +4361,7 @@
       <c r="G26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="20" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4448,7 +4440,7 @@
         <v>10</v>
       </c>
       <c r="K29" s="2">
-        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <f>IF($A29=1,F29-G29-H29*$F$26-2,F29-G29-(1+H29)*$F$26-1)</f>
         <v>21</v>
       </c>
       <c r="L29" t="str">
@@ -5915,7 +5907,7 @@
       <c r="G19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="14">
         <v>10</v>
       </c>
       <c r="I19" s="14">
@@ -5947,7 +5939,7 @@
       <c r="G20" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="14">
         <v>20</v>
       </c>
       <c r="I20" s="14" cm="1">
@@ -5979,7 +5971,7 @@
       <c r="G21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="14">
         <v>30</v>
       </c>
       <c r="I21" s="14" t="b">
@@ -6011,7 +6003,7 @@
       <c r="G22" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="14">
         <v>40</v>
       </c>
       <c r="I22" s="14" t="b">
@@ -6022,35 +6014,35 @@
       <c r="K22" s="14"/>
     </row>
     <row r="23" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="19" t="str">
+      <c r="C23" s="18" t="str">
         <f t="shared" si="5"/>
         <v>172.16.0.53</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="20" t="str">
+      <c r="E23" s="18" t="str">
         <f t="shared" si="4"/>
         <v>3.3.3.0</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19" t="s">
+      <c r="F23" s="18"/>
+      <c r="G23" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="18">
         <v>50</v>
       </c>
       <c r="I23" s="14" t="b">
         <f>'Site 1 (HUB)'!I23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="19"/>
       <c r="K23" s="14"/>
     </row>
     <row r="24" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
@@ -6118,7 +6110,7 @@
       <c r="G26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="20" t="s">
         <v>64</v>
       </c>
       <c r="I26" s="14"/>
@@ -6212,7 +6204,7 @@
         <v>10</v>
       </c>
       <c r="K29" s="2">
-        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <f>IF($A29=1,F29-G29-H29*$F$26-2,F29-G29-(1+H29)*$F$26-1)</f>
         <v>21</v>
       </c>
       <c r="L29" t="str">

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D57BF4F-8D10-450D-B670-CDBF6187C342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64F6F03-3C24-48D5-AAD3-1CE8B27A124A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28440" yWindow="0" windowWidth="23265" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
     <sheet name="Site 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Site 3" sheetId="4" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -57,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="64">
   <si>
     <t>site</t>
   </si>
@@ -209,9 +211,6 @@
     <t>span_mode</t>
   </si>
   <si>
-    <t>ERSPAN</t>
-  </si>
-  <si>
     <t>SW</t>
   </si>
   <si>
@@ -236,9 +235,6 @@
     <t>num_port_ledig</t>
   </si>
   <si>
-    <t>10.1-200.1-20.5-30.5-40.2</t>
-  </si>
-  <si>
     <t>erspan_destination</t>
   </si>
   <si>
@@ -252,13 +248,16 @@
   </si>
   <si>
     <t>10.51.0.10</t>
+  </si>
+  <si>
+    <t>SPAN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -313,16 +312,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -357,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -392,36 +381,49 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="111">
+  <dxfs count="69">
     <dxf>
       <font>
         <color theme="1"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -431,22 +433,7 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -456,343 +443,39 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="11"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="11"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -966,73 +649,6 @@
         <color rgb="FF000000"/>
         <name val="Arial"/>
         <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
       </font>
     </dxf>
     <dxf>
@@ -1349,6 +965,27 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Site 1 (HUB)"/>
+      <sheetName val="Site 2"/>
+      <sheetName val="Site 3"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:J2">
   <tableColumns count="10">
@@ -1358,10 +995,10 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="66"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1370,26 +1007,26 @@
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A28:L29" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="SW" dataDxfId="80">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="SW" dataDxfId="10">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="MGMT Vlan" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="MGMT ip" dataDxfId="78">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="MGMT Vlan" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="MGMT ip" dataDxfId="8">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="gateway" dataDxfId="77">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="gateway" dataDxfId="7">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="mask" dataDxfId="76">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="mask" dataDxfId="6">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="num_ports_tot" dataDxfId="75"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0B00-00000B000000}" name="skiped_ports" dataDxfId="74"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="num_downlink" dataDxfId="73"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="vlan-antall" dataDxfId="72"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="intf_prefix" dataDxfId="71"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="num_port_ledig" dataDxfId="70">
-      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2,F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0B00-00000A000000}" name="num_ports_tot" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0B00-00000B000000}" name="skiped_ports" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="num_downlink" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="vlan-antall" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0B00-000008000000}" name="intf_prefix" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0B00-000009000000}" name="num_port_ledig" dataDxfId="0">
+      <calculatedColumnFormula array="1">[1]!Tabell161824282532[num_port_ledig]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{5BF5BD4F-225D-489A-8CDF-AAA6E48E5D60}" name="MONITORING ip">
       <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
@@ -1416,7 +1053,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{3FDE25A7-0BCB-41BA-9E6B-B97A44D97EF9}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{4F21A854-19B3-4F08-8736-4A49F53BB969}" name="antall-res" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{4F21A854-19B3-4F08-8736-4A49F53BB969}" name="antall-res" dataDxfId="38"/>
     <tableColumn id="10" xr3:uid="{EB637840-6D35-4793-BE43-FF44BBC60DCE}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{99B9B3BB-6A06-4A9B-B262-495BFC762025}" name="pri-1-10"/>
   </tableColumns>
@@ -1437,137 +1074,6 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{29423377-EE71-45EC-AE04-512C3676B300}" name="Tabell18" displayName="Tabell18" ref="A1:I2" dataDxfId="41">
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C426CE2C-D824-495E-9943-0D5ED22178FC}" name="site" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{BD14A14C-CA02-4292-9A53-DBBFAEFFB41E}" name="intf_prefix" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{1E884DEF-6FA0-43D2-90D1-A472ED2D772F}" name="router-id" dataDxfId="38">
-      <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{5C62684E-F01D-41F8-91C7-33CAC2305C15}" name="brukernavn" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{270B3B2A-8408-4EDF-B211-8DE1F1AB0681}" name="passord" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{9804D10C-4308-4EBD-A637-0ED093054024}" name="vty_lines" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{B0910EE6-E1E3-4DBC-9F9C-47058BA9B153}" name="secret" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{D19E2A7E-21D0-4E2A-88C9-9F37D9A65437}" name="tacacs_key" dataDxfId="33">
-      <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{068D3A60-B781-41C3-BF0A-B042AD809343}" name="dns_servers" dataDxfId="32"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E6493EE3-7235-424D-A185-8FB87B73E9D5}" name="Tabell49" displayName="Tabell49" ref="A18:J23" dataDxfId="31">
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{14E90C76-B5F6-4A0B-A8EA-BBD1846F7ADE}" name="tunnel id" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{1DD92107-ED9E-41DA-9538-710D3656664D}" name="vrf" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{9CD976E2-E62F-4E14-BA9A-80672F5BC615}" name="ip address" dataDxfId="28">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{D92BBF85-664B-4383-9EDD-4C7538D00C07}" name="mask" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{41200B4B-99C3-46CD-8919-D19A650DFC09}" name="source" dataDxfId="26">
-      <calculatedColumnFormula>$C$2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{181D5214-8751-4D00-98A5-040FCE4E5826}" name="destination" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{595FE496-14D9-4619-8CC2-BDE4B0AE5AE1}" name="gre mode" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{C91D47FC-885E-4808-80A0-244D7156BD13}" name="network-id" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{D7BBBCE6-3579-420D-920C-EF19B478A7C2}" name="ipsec" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{E379820A-7358-40BE-83E4-07100824C704}" name="ipsec key" dataDxfId="21"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7318DFAD-8A4D-4CFA-8FA6-6B5A78470C24}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="20">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F6D980DA-8008-4018-B306-D36AE654DA5F}" name="site" dataDxfId="19">
-      <calculatedColumnFormula>A2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{0D82B2DE-B4FA-4290-8C52-0CD4C0EAA67D}" name="brukernavn" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{27B9EF4E-512F-4DAC-8CB6-D2912CB2CDDA}" name="passord" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{6414CFB9-90E9-4655-838B-2676C80D7C06}" name="vty_lines" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{D51FD26F-2705-47EA-AED0-D3C21699B51F}" name="secret" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{ABC2D354-96CD-4993-8E5C-3CCEFAEF4846}" name="etherchan_num" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{3F9B25BE-C31E-4660-A97F-1B6AF14759A6}" name="span_mode" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{CA2E1FD4-EBFB-4BF5-8DD2-EE090C2F889B}" name="erspan_destination" dataDxfId="12"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8BA68FF7-7C6C-4673-9B18-11015BB5ECE9}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A28:L29" totalsRowShown="0">
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{8ADEAF6D-0562-4F81-93E4-69481AB6E718}" name="SW" dataDxfId="11">
-      <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{795F6504-A97F-4DFB-87AB-D0C3A93E475F}" name="MGMT Vlan" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{074C8822-FEF3-4C00-8C20-E4AAA6F87C8F}" name="MGMT ip" dataDxfId="9">
-      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{9E7BBCA3-A734-4692-A8F8-31365B75A063}" name="gateway" dataDxfId="8">
-      <calculatedColumnFormula>$E$5</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{B9D0B580-B85A-45C6-8EE9-922E6A0BDCD5}" name="mask" dataDxfId="7">
-      <calculatedColumnFormula>$F$5</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{136103A4-087C-4FA7-8332-FE71D232375E}" name="num_ports_tot" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{A0C44AB8-80BB-4052-A5FD-EE8530AB6772}" name="skiped_ports" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{52404E39-8CD5-4B37-A91F-C35409540738}" name="num_downlink" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{5B37CE82-3036-45D8-A546-50FF289EDBAD}" name="vlan-antall" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{79F10BE9-3D80-4FF6-A4B6-9184B24A72B4}" name="intf_prefix" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{5CB772C2-CF05-454F-BBBD-8EDEC112C696}" name="num_port_ledig" dataDxfId="0">
-      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2,F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="12" xr3:uid="{065F9F0A-8DB1-44A2-B7B3-97742E5CD0E1}" name="MONITORING ip">
-      <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{95B0B071-F602-4A16-BA0D-4B172283BAE9}" name="Tabell6214" displayName="Tabell6214" ref="A4:K9">
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{94861C51-5403-456D-87AF-7FC76DBA28A5}" name="vrf"/>
-    <tableColumn id="2" xr3:uid="{50243E8E-018E-40C1-A37D-ED67F4B092B0}" name="vlan"/>
-    <tableColumn id="3" xr3:uid="{A63B107D-5FA2-40D8-A99A-E280CFCC8C79}" name="interface"/>
-    <tableColumn id="4" xr3:uid="{A4267435-D295-44C3-B51E-0D1F4DD5C78B}" name="nett id">
-      <calculatedColumnFormula>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{DC7B96FF-EAB7-4E6B-8DE8-85902CDECD19}" name="gateway">
-      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{1D8E9334-405A-4906-8238-47E036EC7609}" name="mask"/>
-    <tableColumn id="7" xr3:uid="{B5F525F7-1C0B-4D5D-BD37-F7614B933163}" name="address min">
-      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{BB245EF9-E497-4445-9E11-811371F6669C}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{8BE1DAE2-2DC3-4655-8CD3-ACB1B1D4A0F3}" name="antall-res" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{7934A4A2-4EDA-4DF0-9DAF-BA3DD0375EC2}" name="pri-afxx"/>
-    <tableColumn id="11" xr3:uid="{D8ADAB0C-E2D6-490F-A501-86D8C692367E}" name="pri-1-10"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3B6A134F-5EA0-448A-B9C1-D15432398AB5}" name="Tabell7715" displayName="Tabell7715" ref="A11:C16">
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FA02FDEA-9585-4542-97E7-C1202764FFEC}" name="vrf"/>
-    <tableColumn id="3" xr3:uid="{840408ED-7E47-4F28-B0EB-9EDF05B3AEB2}" name="loopback"/>
-    <tableColumn id="4" xr3:uid="{FCE403FB-283B-4BF0-B99C-780D900D988D}" name="laddr">
-      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabell6" displayName="Tabell6" ref="A4:K9">
   <tableColumns count="11">
@@ -1581,7 +1087,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="64"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="33"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1611,7 +1117,7 @@
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="63">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="32">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -1625,48 +1131,48 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="31">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="30">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{A8B916C7-04E3-4A58-909F-34F3F1BEB3E4}" name="erspan_destination" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{A8B916C7-04E3-4A58-909F-34F3F1BEB3E4}" name="erspan_destination" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:L30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:L29" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="22">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="51">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="20">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="50">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="19">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="49">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="18">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="48"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="43">
-      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR($G$26="ERSPAN",$G$26="SPAN",$G$26="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="12">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN", UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F45C6C35-68DB-43FE-9CBF-B6A2844A42CD}" name="MONITORING ip" dataDxfId="42">
+    <tableColumn id="12" xr3:uid="{F45C6C35-68DB-43FE-9CBF-B6A2844A42CD}" name="MONITORING ip" dataDxfId="11">
       <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1675,59 +1181,59 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:I2" dataDxfId="110">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:I2" dataDxfId="68">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="108"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="107"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="106"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="105"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="104"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="103"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="102">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="60">
       <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="101"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="100">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="58">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="tunnel id" dataDxfId="99"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="vrf" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="ip address" dataDxfId="97">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="tunnel id" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="vrf" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="ip address" dataDxfId="55">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="mask" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="source" dataDxfId="95">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="mask" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="source" dataDxfId="53">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="destination" dataDxfId="94"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="gre mode" dataDxfId="93"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="network-id" dataDxfId="92"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="ipsec" dataDxfId="91"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="ipsec key" dataDxfId="90"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="destination" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="gre mode" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="network-id" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0800-000009000000}" name="ipsec" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0800-00000A000000}" name="ipsec key" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:H26" dataDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:H26" dataDxfId="47">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="site" dataDxfId="88">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="site" dataDxfId="46">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="brukernavn" dataDxfId="87"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="passord" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="vty_lines" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="secret" dataDxfId="84"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="etherchan_num" dataDxfId="83"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="span_mode" dataDxfId="82"/>
-    <tableColumn id="8" xr3:uid="{BFD011F6-587B-466E-BAE0-BEEA0A83891E}" name="erspan_destination" dataDxfId="81"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="brukernavn" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="passord" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="vty_lines" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="secret" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="etherchan_num" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="span_mode" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{BFD011F6-587B-466E-BAE0-BEEA0A83891E}" name="erspan_destination" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1928,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1005"/>
+  <dimension ref="A1:L1004"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -2213,7 +1719,7 @@
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="9">
         <v>50</v>
@@ -2315,7 +1821,7 @@
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" s="8">
         <v>50</v>
@@ -2476,10 +1982,10 @@
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" s="8" t="str">
         <f t="shared" ref="C23" si="12">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H23+$A$2)</f>
@@ -2536,7 +2042,7 @@
         <v>49</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2557,25 +2063,25 @@
         <v>12</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="C28" s="15" t="s">
         <v>52</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>20</v>
@@ -2584,25 +2090,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="H28" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="I28" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>57</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>1</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2626,72 +2132,28 @@
         <v>255.255.0.0</v>
       </c>
       <c r="F29" s="8">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="11">
-        <v>3</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>59</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I29" s="8"/>
       <c r="J29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K29" s="2">
         <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN", UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" ref="L29:L30" si="13">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
+        <f t="shared" ref="L29" si="13">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
         <v>10.51.0.2</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="17">
-        <v>2</v>
-      </c>
-      <c r="B30" s="17">
-        <v>10</v>
-      </c>
-      <c r="C30" s="17" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A30)</f>
-        <v>10.11.0.3</v>
-      </c>
-      <c r="D30" s="17" t="str">
-        <f>$E$5</f>
-        <v>10.11.0.1</v>
-      </c>
-      <c r="E30" s="17" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F30" s="17">
-        <v>24</v>
-      </c>
-      <c r="G30" s="17">
-        <v>1</v>
-      </c>
-      <c r="H30" s="17">
-        <v>0</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="K30" s="2">
-        <f>IF($A30=1,F30-G30-H30*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F30-G30-(1+H30)*$F$26-1)</f>
-        <v>20</v>
-      </c>
-      <c r="L30" t="str">
-        <f t="shared" si="13"/>
-        <v>10.51.0.3</v>
-      </c>
-    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3666,14 +3128,13 @@
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29:I30" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="G26" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3962,7 +3423,7 @@
     </row>
     <row r="9" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="9">
         <v>50</v>
@@ -4113,7 +3574,7 @@
     </row>
     <row r="16" spans="1:11" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" s="8">
         <v>50</v>
@@ -4281,35 +3742,35 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="18" t="str">
+      <c r="A23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="16" t="str">
         <f t="shared" si="5"/>
         <v>172.16.0.52</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="18" t="str">
+      <c r="E23" s="16" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18" t="s">
+      <c r="F23" s="16"/>
+      <c r="G23" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="16">
         <v>50</v>
       </c>
       <c r="I23" s="14" t="b">
         <f>'Site 1 (HUB)'!I23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="19"/>
+      <c r="J23" s="17"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4335,7 +3796,7 @@
         <v>49</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4356,25 +3817,25 @@
         <v>12</v>
       </c>
       <c r="F26" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="C28" s="15" t="s">
         <v>52</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>20</v>
@@ -4383,28 +3844,28 @@
         <v>21</v>
       </c>
       <c r="F28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="H28" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="I28" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>57</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>1</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <f>(ROW())-(ROW()-1)</f>
         <v>1</v>
@@ -4425,26 +3886,24 @@
         <v>255.255.0.0</v>
       </c>
       <c r="F29" s="8">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="11">
         <v>0</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>59</v>
-      </c>
+      <c r="I29" s="8"/>
       <c r="J29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="2">
-        <f>IF($A29=1,F29-G29-H29*$F$26-2,F29-G29-(1+H29)*$F$26-1)</f>
+      <c r="K29" s="2" cm="1">
+        <f t="array" ref="K29">[1]!Tabell161824282532[num_port_ledig]</f>
         <v>21</v>
       </c>
       <c r="L29" t="str">
-        <f>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
+        <f t="shared" ref="L29" si="6">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
         <v>10.52.0.2</v>
       </c>
     </row>
@@ -5419,7 +4878,7 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{D2AD5624-A156-47D7-A0C6-A47F59F949C5}">
       <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="G26" xr:uid="{00000000-0002-0000-0100-000001000000}">
@@ -5436,799 +4895,4 @@
     <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="75.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="75.85546875" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="58.7109375" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="14">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="14" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="14" t="str">
-        <f>'Site 1 (HUB)'!H2</f>
-        <v>TACACS-KEY</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-    </row>
-    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-    </row>
-    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="9">
-        <v>10</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8" t="str">
-        <f>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
-        <v>10.13.0.0</v>
-      </c>
-      <c r="E5" s="8" t="str">
-        <f>LEFT(D5,LEN(D5)-1)&amp;"1"</f>
-        <v>10.13.0.1</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="8" t="str">
-        <f t="shared" ref="G5:G9" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
-        <v>10.13.0.1</v>
-      </c>
-      <c r="H5" s="8" t="str">
-        <f>LEFT(D5,FIND(".",D5,FIND(".",D5)+1)-1)&amp;".255.254"</f>
-        <v>10.13.255.254</v>
-      </c>
-      <c r="I5" s="8">
-        <v>10</v>
-      </c>
-      <c r="J5" s="10">
-        <v>21</v>
-      </c>
-      <c r="K5" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="9">
-        <v>20</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8" t="str">
-        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;(B6+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
-        <v>10.23.0.0</v>
-      </c>
-      <c r="E6" s="8" t="str">
-        <f t="shared" ref="E6:E9" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
-        <v>10.23.0.1</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>10.23.0.1</v>
-      </c>
-      <c r="H6" s="8" t="str">
-        <f>LEFT(D6,FIND(".",D6,FIND(".",D6)+1)-1)&amp;".255.254"</f>
-        <v>10.23.255.254</v>
-      </c>
-      <c r="I6" s="8">
-        <v>10</v>
-      </c>
-      <c r="J6" s="10">
-        <v>11</v>
-      </c>
-      <c r="K6" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="9">
-        <v>30</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>10.33.0.0</v>
-      </c>
-      <c r="E7" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>10.33.0.1</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>10.33.0.1</v>
-      </c>
-      <c r="H7" s="8" t="str">
-        <f>LEFT(D7,FIND(".",D7,FIND(".",D7)+1)-1)&amp;".255.254"</f>
-        <v>10.33.255.254</v>
-      </c>
-      <c r="I7" s="8">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>42</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="9">
-        <v>40</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>10.43.0.0</v>
-      </c>
-      <c r="E8" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>10.43.0.1</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>10.43.0.1</v>
-      </c>
-      <c r="H8" s="8" t="str">
-        <f>LEFT(D8,FIND(".",D8,FIND(".",D8)+1)-1)&amp;".255.254"</f>
-        <v>10.43.255.254</v>
-      </c>
-      <c r="I8" s="8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>41</v>
-      </c>
-      <c r="K8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="9">
-        <v>50</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>10.53.0.0</v>
-      </c>
-      <c r="E9" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>10.53.0.1</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>10.53.0.1</v>
-      </c>
-      <c r="H9" s="8" t="str">
-        <f>LEFT(D9,FIND(".",D9,FIND(".",D9)+1)-1)&amp;".0.254"</f>
-        <v>10.53.0.254</v>
-      </c>
-      <c r="I9" s="8">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>43</v>
-      </c>
-      <c r="K9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="8">
-        <v>10</v>
-      </c>
-      <c r="C12" s="8" t="str">
-        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
-        <v>3.3.3.10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="8">
-        <v>20</v>
-      </c>
-      <c r="C13" s="8" t="str">
-        <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B13)</f>
-        <v>3.3.3.20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="8">
-        <v>30</v>
-      </c>
-      <c r="C14" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>3.3.3.30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="8">
-        <v>40</v>
-      </c>
-      <c r="C15" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>3.3.3.40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="8">
-        <v>50</v>
-      </c>
-      <c r="C16" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>3.3.3.50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-    </row>
-    <row r="18" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" s="14"/>
-    </row>
-    <row r="19" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="14" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</f>
-        <v>172.16.0.13</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="14" t="str">
-        <f t="shared" ref="E19:E23" si="4">$C$2</f>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="14">
-        <v>10</v>
-      </c>
-      <c r="I19" s="14">
-        <f t="array" ref="I19">'Site 1 (HUB)'!I19</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-    </row>
-    <row r="20" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="14" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
-        <v>172.16.0.23</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="14">
-        <v>20</v>
-      </c>
-      <c r="I20" s="14" cm="1">
-        <f t="array" ref="I20">'Site 1 (HUB)'!I20</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-    </row>
-    <row r="21" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="14" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H21+$A$2)</f>
-        <v>172.16.0.33</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="14">
-        <v>30</v>
-      </c>
-      <c r="I21" s="14" t="b">
-        <f>'Site 1 (HUB)'!I21</f>
-        <v>1</v>
-      </c>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-    </row>
-    <row r="22" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="14" t="str">
-        <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H22+$A$2)</f>
-        <v>172.16.0.43</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="14">
-        <v>40</v>
-      </c>
-      <c r="I22" s="14" t="b">
-        <f>'Site 1 (HUB)'!I22</f>
-        <v>1</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-    </row>
-    <row r="23" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="18" t="str">
-        <f t="shared" si="5"/>
-        <v>172.16.0.53</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="18">
-        <v>50</v>
-      </c>
-      <c r="I23" s="14" t="b">
-        <f>'Site 1 (HUB)'!I23</f>
-        <v>1</v>
-      </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="14"/>
-    </row>
-    <row r="24" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-    </row>
-    <row r="25" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-    </row>
-    <row r="26" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A26" s="14">
-        <f>A2</f>
-        <v>3</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="14">
-        <v>2</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-    </row>
-    <row r="27" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-    </row>
-    <row r="28" spans="1:12" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="L28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
-        <f>(ROW())-(ROW()-1)</f>
-        <v>1</v>
-      </c>
-      <c r="B29" s="8">
-        <v>10</v>
-      </c>
-      <c r="C29" s="8" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</f>
-        <v>10.13.0.2</v>
-      </c>
-      <c r="D29" s="8" t="str">
-        <f>$E$5</f>
-        <v>10.13.0.1</v>
-      </c>
-      <c r="E29" s="8" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F29" s="8">
-        <v>24</v>
-      </c>
-      <c r="G29" s="8">
-        <v>1</v>
-      </c>
-      <c r="H29" s="11">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K29" s="2">
-        <f>IF($A29=1,F29-G29-H29*$F$26-2,F29-G29-(1+H29)*$F$26-1)</f>
-        <v>21</v>
-      </c>
-      <c r="L29" t="str">
-        <f>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
-        <v>10.53.0.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{7287270F-FA36-42B0-936E-CB6AE119A013}">
-      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="G26" xr:uid="{96B8245A-DA04-4B17-A070-977D41BECEDD}">
-      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="6">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64F6F03-3C24-48D5-AAD3-1CE8B27A124A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C26C3D-14AF-49AC-99A9-26AD3CE7C752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28440" yWindow="0" windowWidth="23265" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,9 +978,9 @@
       <sheetName val="Site 3"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3898,9 +3898,9 @@
       <c r="J29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="2" cm="1">
+      <c r="K29" s="2" t="e" cm="1">
         <f t="array" ref="K29">[1]!Tabell161824282532[num_port_ledig]</f>
-        <v>21</v>
+        <v>#REF!</v>
       </c>
       <c r="L29" t="str">
         <f t="shared" ref="L29" si="6">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\test\NO_MPLS_SAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AF2A12-1773-46C7-932E-3ECF2103B4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125B278D-439A-463B-812B-7B41AC6F3185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -354,7 +354,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -442,6 +442,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -478,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -496,7 +507,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -554,11 +564,428 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="76">
+  <dxfs count="78">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -572,6 +999,189 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color auto="1"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <strike val="0"/>
@@ -581,595 +1191,6 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color auto="1"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
@@ -1188,7 +1209,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:M2" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:M2" headerRowDxfId="77">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="site"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="intf_prefix"/>
@@ -1196,13 +1217,13 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{1034F7EE-3D03-457B-B6E1-EC9EB8A68ABA}" name="tacacs_server_ip" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{17F5A604-6C04-47C4-886F-C1FB4C0FC7CA}" name="syslog_server_ip" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{3D895677-0966-4D0C-9B84-8565AE7DC140}" name="urpf_mode" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="75"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{1034F7EE-3D03-457B-B6E1-EC9EB8A68ABA}" name="tacacs_server_ip" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{17F5A604-6C04-47C4-886F-C1FB4C0FC7CA}" name="syslog_server_ip" dataDxfId="71"/>
+    <tableColumn id="13" xr3:uid="{3D895677-0966-4D0C-9B84-8565AE7DC140}" name="urpf_mode" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1211,25 +1232,25 @@
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A28:L30" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="17">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="14">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="15">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="12">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="14">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="11">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="13">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="10">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="7">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="4">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="MONITORING ip">
@@ -1257,7 +1278,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="3"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1297,14 +1318,21 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="interface"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id">
-      <calculatedColumnFormula>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="2">
+      <calculatedColumnFormula>10&amp;"."&amp;($A$2)&amp;"."&amp;$B5&amp;"."&amp;0</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="gateway"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="0">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
+_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
+_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
+_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="1"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1334,7 +1362,7 @@
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="70">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="69">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -1348,18 +1376,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="68">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="68">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="67">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Column1" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Column1" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1368,28 +1396,28 @@
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:L29" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="60">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="59">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="58">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="57">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="57">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="56">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="56">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="55">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="55"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="53"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="50">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="54"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="49">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="49">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="48">
       <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1398,65 +1426,65 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:L2" headerRowDxfId="0" dataDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:L2" headerRowDxfId="47" dataDxfId="46">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="40">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="38">
       <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="38">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="36">
       <calculatedColumnFormula>'Site 1 (HUB)'!K2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="37">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="35">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{B53F3502-BEF9-4409-9767-9784EC3E3C30}" name="urpf_mode" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{B53F3502-BEF9-4409-9767-9784EC3E3C30}" name="urpf_mode" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="33">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="30">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="31">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="28">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:G26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:G26" dataDxfId="22">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="21">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1675,43 +1703,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="28" t="s">
+      <c r="M1" s="27" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1744,16 +1772,16 @@
       <c r="I2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="L2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="24" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1766,6 +1794,8 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
@@ -1795,121 +1825,140 @@
       <c r="I4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>10</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>0</v>
       </c>
-      <c r="D5" s="8" t="str">
-        <f>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
-        <v>10.11.0.0</v>
-      </c>
-      <c r="E5" s="8" t="str">
+      <c r="D5" s="7" t="str">
+        <f>10&amp;"."&amp;($A$2)&amp;"."&amp;B5&amp;"."&amp;0</f>
+        <v>10.1.10.0</v>
+      </c>
+      <c r="E5" s="7" t="str">
         <f>LEFT(D5,LEN(D5)-1)&amp;"1"</f>
-        <v>10.11.0.1</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="8" t="str">
-        <f t="shared" ref="G5:G7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
-        <v>10.11.0.1</v>
-      </c>
-      <c r="H5" s="8" t="str">
-        <f>LEFT(D5,FIND(".",D5,FIND(".",D5)+1)-1)&amp;".255.254"</f>
-        <v>10.11.255.254</v>
-      </c>
-      <c r="I5" s="8">
+        <v>10.1.10.1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="7" t="str" cm="1">
+        <f t="array" ref="G5">_xlfn.LET(
+_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
+_xlpm.addr,_xlpm.net+1,
+_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
+)</f>
+        <v>10.1.10.1</v>
+      </c>
+      <c r="H5" s="7" t="str" cm="1">
+        <f t="array" ref="H5">_xlfn.LET(
+_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
+_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
+_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
+_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
+)</f>
+        <v>10.1.10.254</v>
+      </c>
+      <c r="I5" s="7">
         <v>40</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <v>21</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>20</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>0</v>
       </c>
-      <c r="D6" s="8" t="str">
-        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;(B6+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
-        <v>10.21.0.0</v>
-      </c>
-      <c r="E6" s="8" t="str">
-        <f t="shared" ref="E6:E7" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
-        <v>10.21.0.1</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="8" t="str">
+      <c r="D6" s="7" t="str">
+        <f t="shared" ref="D6:D9" si="0">10&amp;"."&amp;($A$2)&amp;"."&amp;$B6&amp;"."&amp;0</f>
+        <v>10.1.20.0</v>
+      </c>
+      <c r="E6" s="7" t="str">
+        <f t="shared" ref="E6:E7" si="1">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
+        <v>10.1.20.1</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <f t="shared" ref="G5:G7" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
+        <v>10.1.20.1</v>
+      </c>
+      <c r="H6" s="7" t="str" cm="1">
+        <f t="array" ref="H6">_xlfn.LET(
+_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
+_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
+_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
+_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
+)</f>
+        <v>10.1.20.254</v>
+      </c>
+      <c r="I6" s="7">
+        <v>40</v>
+      </c>
+      <c r="J6" s="9">
+        <v>11</v>
+      </c>
+      <c r="K6" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="8">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>10.21.0.1</v>
-      </c>
-      <c r="H6" s="8" t="str">
-        <f>LEFT(D6,FIND(".",D6,FIND(".",D6)+1)-1)&amp;".255.254"</f>
-        <v>10.21.255.254</v>
-      </c>
-      <c r="I6" s="8">
-        <v>40</v>
-      </c>
-      <c r="J6" s="10">
-        <v>11</v>
-      </c>
-      <c r="K6" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="9">
-        <v>30</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="str">
+        <v>10.1.30.0</v>
+      </c>
+      <c r="E7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>10.31.0.0</v>
-      </c>
-      <c r="E7" s="8" t="str">
+        <v>10.1.30.1</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>10.31.0.1</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>10.31.0.1</v>
-      </c>
-      <c r="H7" s="8" t="str">
-        <f>LEFT(D7,FIND(".",D7,FIND(".",D7)+1)-1)&amp;".255.254"</f>
-        <v>10.31.255.254</v>
-      </c>
-      <c r="I7" s="8">
+        <v>10.1.30.1</v>
+      </c>
+      <c r="H7" s="7" t="str" cm="1">
+        <f t="array" ref="H7">_xlfn.LET(
+_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
+_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
+_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
+_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
+)</f>
+        <v>10.1.30.254</v>
+      </c>
+      <c r="I7" s="7">
         <v>40</v>
       </c>
       <c r="J7">
@@ -1920,35 +1969,40 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>40</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>0</v>
       </c>
-      <c r="D8" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>10.41.0.0</v>
-      </c>
-      <c r="E8" s="8" t="str">
+      <c r="D8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.1.40.0</v>
+      </c>
+      <c r="E8" s="7" t="str">
         <f t="shared" ref="E8" si="3">LEFT(D8,LEN(D8)-1)&amp;"1"</f>
-        <v>10.41.0.1</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="8" t="str">
+        <v>10.1.40.1</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="7" t="str">
         <f t="shared" ref="G8" si="4">LEFT(D8,LEN(D8)-1)&amp;"1"</f>
-        <v>10.41.0.1</v>
-      </c>
-      <c r="H8" s="8" t="str">
-        <f>LEFT(D8,FIND(".",D8,FIND(".",D8)+1)-1)&amp;".255.254"</f>
-        <v>10.41.255.254</v>
-      </c>
-      <c r="I8" s="8">
+        <v>10.1.40.1</v>
+      </c>
+      <c r="H8" s="7" t="str" cm="1">
+        <f t="array" ref="H8">_xlfn.LET(
+_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
+_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
+_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
+_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
+)</f>
+        <v>10.1.40.254</v>
+      </c>
+      <c r="I8" s="7">
         <v>40</v>
       </c>
       <c r="J8">
@@ -1959,35 +2013,40 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>50</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>0</v>
       </c>
-      <c r="D9" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>10.51.0.0</v>
-      </c>
-      <c r="E9" s="8" t="str">
+      <c r="D9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.1.50.0</v>
+      </c>
+      <c r="E9" s="7" t="str">
         <f t="shared" ref="E9" si="5">LEFT(D9,LEN(D9)-1)&amp;"1"</f>
-        <v>10.51.0.1</v>
-      </c>
-      <c r="F9" s="8" t="s">
+        <v>10.1.50.1</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="8" t="str">
+      <c r="G9" s="7" t="str">
         <f t="shared" ref="G9" si="6">LEFT(D9,LEN(D9)-1)&amp;"1"</f>
-        <v>10.51.0.1</v>
-      </c>
-      <c r="H9" s="8" t="str">
-        <f>LEFT(D9,FIND(".",D9,FIND(".",D9)+1)-1)&amp;".0.254"</f>
-        <v>10.51.0.254</v>
-      </c>
-      <c r="I9" s="8">
+        <v>10.1.50.1</v>
+      </c>
+      <c r="H9" s="7" t="str" cm="1">
+        <f t="array" ref="H9">_xlfn.LET(
+_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
+_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
+_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
+_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
+)</f>
+        <v>10.1.50.254</v>
+      </c>
+      <c r="I9" s="7">
         <v>40</v>
       </c>
       <c r="J9">
@@ -2013,61 +2072,61 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="8" t="str">
+      <c r="C12" s="7" t="str">
         <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
         <v>1.1.1.10</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>20</v>
       </c>
-      <c r="C13" s="8" t="str">
+      <c r="C13" s="7" t="str">
         <f t="shared" ref="C13:C15" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B13)</f>
         <v>1.1.1.20</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>30</v>
       </c>
-      <c r="C14" s="8" t="str">
+      <c r="C14" s="7" t="str">
         <f t="shared" si="7"/>
         <v>1.1.1.30</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>40</v>
       </c>
-      <c r="C15" s="8" t="str">
+      <c r="C15" s="7" t="str">
         <f t="shared" si="7"/>
         <v>1.1.1.40</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>50</v>
       </c>
-      <c r="C16" s="8" t="str">
+      <c r="C16" s="7" t="str">
         <f t="shared" ref="C16" si="8">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B16)</f>
         <v>1.1.1.50</v>
       </c>
@@ -2106,25 +2165,25 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="8" t="str">
+      <c r="C19" s="7" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</f>
         <v>172.16.0.11</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="8" t="str">
+      <c r="E19" s="7" t="str">
         <f t="shared" ref="E19:E23" si="9">$C$2</f>
         <v>1.1.1.0</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8" t="s">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H19" s="2">
@@ -2134,25 +2193,25 @@
       <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="8" t="str">
+      <c r="C20" s="7" t="str">
         <f t="shared" ref="C20:C21" si="10">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
         <v>172.16.0.21</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="8" t="str">
+      <c r="E20" s="7" t="str">
         <f t="shared" si="9"/>
         <v>1.1.1.0</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8" t="s">
+      <c r="F20" s="7"/>
+      <c r="G20" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H20" s="2">
@@ -2162,25 +2221,25 @@
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="8" t="str">
+      <c r="C21" s="7" t="str">
         <f t="shared" si="10"/>
         <v>172.16.0.31</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="8" t="str">
+      <c r="E21" s="7" t="str">
         <f t="shared" si="9"/>
         <v>1.1.1.0</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="7"/>
+      <c r="G21" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H21" s="2">
@@ -2192,25 +2251,25 @@
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="8" t="str">
+      <c r="C22" s="7" t="str">
         <f t="shared" ref="C22" si="11">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H22+$A$2)</f>
         <v>172.16.0.41</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="8" t="str">
+      <c r="E22" s="7" t="str">
         <f t="shared" si="9"/>
         <v>1.1.1.0</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H22" s="2">
@@ -2222,25 +2281,25 @@
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="8" t="str">
+      <c r="C23" s="7" t="str">
         <f t="shared" ref="C23" si="12">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H23+$A$2)</f>
         <v>172.16.0.51</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="8" t="str">
+      <c r="E23" s="7" t="str">
         <f t="shared" si="9"/>
         <v>1.1.1.0</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8" t="s">
+      <c r="F23" s="7"/>
+      <c r="G23" s="7" t="s">
         <v>48</v>
       </c>
       <c r="H23" s="2">
@@ -2252,13 +2311,13 @@
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -2309,77 +2368,77 @@
       <c r="G26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H26" s="18"/>
+      <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="J28" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L28" s="30" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
+      <c r="A29" s="7">
         <f>(ROW())-(ROW()-1)</f>
         <v>1</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>10</v>
       </c>
-      <c r="C29" s="8" t="str">
+      <c r="C29" s="7" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</f>
-        <v>10.11.0.2</v>
-      </c>
-      <c r="D29" s="8" t="str">
+        <v>10.1.10.2</v>
+      </c>
+      <c r="D29" s="7" t="str">
         <f>$E$5</f>
-        <v>10.11.0.1</v>
-      </c>
-      <c r="E29" s="8" t="str">
+        <v>10.1.10.1</v>
+      </c>
+      <c r="E29" s="7" t="str">
         <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F29" s="8">
+        <v>255.255.255.0</v>
+      </c>
+      <c r="F29" s="7">
         <v>4</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="7">
         <v>0</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="10">
         <v>0</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="7" t="s">
         <v>66</v>
       </c>
       <c r="J29" s="2" t="s">
@@ -2391,7 +2450,7 @@
       </c>
       <c r="L29" t="str">
         <f t="shared" ref="L29" si="13">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
-        <v>10.51.0.2</v>
+        <v>10.1.50.2</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3398,99 +3457,99 @@
   <dimension ref="A1:M998"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="13" style="14" customWidth="1"/>
-    <col min="3" max="3" width="75.85546875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="75.85546875" style="14" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="75.85546875" style="14" customWidth="1"/>
-    <col min="8" max="8" width="22" style="14" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" style="14" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" style="14" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="13" style="13" customWidth="1"/>
+    <col min="3" max="3" width="75.85546875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="75.85546875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="13" customWidth="1"/>
+    <col min="7" max="7" width="75.85546875" style="13" customWidth="1"/>
+    <col min="8" max="8" width="22" style="13" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" style="13" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="13" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="16384" width="12.5703125" style="14"/>
+    <col min="14" max="16384" width="12.5703125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="L1" s="27" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14">
+      <c r="A2" s="13">
         <v>2</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="14" t="str">
+      <c r="C2" s="13" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>2.2.2.0</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="14" t="str">
+      <c r="H2" s="13" t="str">
         <f>'Site 1 (HUB)'!H2</f>
         <v>TACACS-KEY</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="19" t="str">
+      <c r="J2" s="18" t="str">
         <f>'Site 1 (HUB)'!K2</f>
         <v>10.11.0.10</v>
       </c>
-      <c r="K2" s="19" t="str">
+      <c r="K2" s="18" t="str">
         <f>'Site 1 (HUB)'!L2</f>
         <v>10.11.0.10</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="25" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3520,124 +3579,124 @@
       <c r="H4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>10</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>0</v>
       </c>
-      <c r="D5" s="8" t="str">
+      <c r="D5" s="7" t="str">
         <f>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.12.0.0</v>
       </c>
-      <c r="E5" s="8" t="str">
+      <c r="E5" s="7" t="str">
         <f>LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="8" t="str">
+      <c r="G5" s="7" t="str">
         <f t="shared" ref="G5:G9" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="H5" s="8" t="str">
+      <c r="H5" s="7" t="str">
         <f>LEFT(D5,FIND(".",D5,FIND(".",D5)+1)-1)&amp;".255.254"</f>
         <v>10.12.255.254</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>40</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <v>21</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>20</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>0</v>
       </c>
-      <c r="D6" s="8" t="str">
+      <c r="D6" s="7" t="str">
         <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;(B6+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
         <v>10.22.0.0</v>
       </c>
-      <c r="E6" s="8" t="str">
+      <c r="E6" s="7" t="str">
         <f t="shared" ref="E6:E9" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
         <v>10.22.0.1</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="8" t="str">
+      <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>10.22.0.1</v>
       </c>
-      <c r="H6" s="8" t="str">
+      <c r="H6" s="7" t="str">
         <f>LEFT(D6,FIND(".",D6,FIND(".",D6)+1)-1)&amp;".255.254"</f>
         <v>10.22.255.254</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>40</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>11</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>30</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>0</v>
       </c>
-      <c r="D7" s="8" t="str">
+      <c r="D7" s="7" t="str">
         <f t="shared" si="1"/>
         <v>10.32.0.0</v>
       </c>
-      <c r="E7" s="8" t="str">
+      <c r="E7" s="7" t="str">
         <f t="shared" si="2"/>
         <v>10.32.0.1</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="8" t="str">
+      <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>10.32.0.1</v>
       </c>
-      <c r="H7" s="8" t="str">
+      <c r="H7" s="7" t="str">
         <f>LEFT(D7,FIND(".",D7,FIND(".",D7)+1)-1)&amp;".255.254"</f>
         <v>10.32.255.254</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <v>40</v>
       </c>
       <c r="J7">
@@ -3648,35 +3707,35 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>40</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>0</v>
       </c>
-      <c r="D8" s="8" t="str">
+      <c r="D8" s="7" t="str">
         <f t="shared" si="1"/>
         <v>10.42.0.0</v>
       </c>
-      <c r="E8" s="8" t="str">
+      <c r="E8" s="7" t="str">
         <f t="shared" si="2"/>
         <v>10.42.0.1</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="8" t="str">
+      <c r="G8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>10.42.0.1</v>
       </c>
-      <c r="H8" s="8" t="str">
+      <c r="H8" s="7" t="str">
         <f>LEFT(D8,FIND(".",D8,FIND(".",D8)+1)-1)&amp;".255.254"</f>
         <v>10.42.255.254</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>40</v>
       </c>
       <c r="J8">
@@ -3685,38 +3744,38 @@
       <c r="K8">
         <v>10</v>
       </c>
-      <c r="L8" s="14"/>
+      <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>50</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>0</v>
       </c>
-      <c r="D9" s="8" t="str">
+      <c r="D9" s="7" t="str">
         <f t="shared" si="1"/>
         <v>10.52.0.0</v>
       </c>
-      <c r="E9" s="8" t="str">
+      <c r="E9" s="7" t="str">
         <f t="shared" si="2"/>
         <v>10.52.0.1</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="8" t="str">
+      <c r="G9" s="7" t="str">
         <f t="shared" si="0"/>
         <v>10.52.0.1</v>
       </c>
-      <c r="H9" s="8" t="str">
+      <c r="H9" s="7" t="str">
         <f>LEFT(D9,FIND(".",D9,FIND(".",D9)+1)-1)&amp;".0.254"</f>
         <v>10.52.0.254</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <v>40</v>
       </c>
       <c r="J9">
@@ -3725,7 +3784,7 @@
       <c r="K9">
         <v>10</v>
       </c>
-      <c r="L9" s="14"/>
+      <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
@@ -3739,7 +3798,7 @@
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
-      <c r="L10" s="14"/>
+      <c r="L10" s="13"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
@@ -3759,16 +3818,16 @@
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
-      <c r="L11" s="14"/>
+      <c r="L11" s="13"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="8" t="str">
+      <c r="C12" s="7" t="str">
         <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
         <v>2.2.2.10</v>
       </c>
@@ -3780,16 +3839,16 @@
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
-      <c r="L12" s="14"/>
+      <c r="L12" s="13"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>20</v>
       </c>
-      <c r="C13" s="8" t="str">
+      <c r="C13" s="7" t="str">
         <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B13)</f>
         <v>2.2.2.20</v>
       </c>
@@ -3801,16 +3860,16 @@
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
-      <c r="L13" s="14"/>
+      <c r="L13" s="13"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>30</v>
       </c>
-      <c r="C14" s="8" t="str">
+      <c r="C14" s="7" t="str">
         <f t="shared" si="3"/>
         <v>2.2.2.30</v>
       </c>
@@ -3822,16 +3881,16 @@
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
-      <c r="L14" s="14"/>
+      <c r="L14" s="13"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>40</v>
       </c>
-      <c r="C15" s="8" t="str">
+      <c r="C15" s="7" t="str">
         <f t="shared" si="3"/>
         <v>2.2.2.40</v>
       </c>
@@ -3843,16 +3902,16 @@
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
-      <c r="L15" s="14"/>
+      <c r="L15" s="13"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>50</v>
       </c>
-      <c r="C16" s="8" t="str">
+      <c r="C16" s="7" t="str">
         <f t="shared" si="3"/>
         <v>2.2.2.50</v>
       </c>
@@ -3864,206 +3923,206 @@
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
-      <c r="L16" s="14"/>
+      <c r="L16" s="13"/>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J18" s="13" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="14" t="str">
+      <c r="C19" s="13" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</f>
         <v>172.16.0.12</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="14" t="str">
+      <c r="E19" s="13" t="str">
         <f t="shared" ref="E19:E23" si="4">$C$2</f>
         <v>2.2.2.0</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>10</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <f t="array" ref="I19">'Site 1 (HUB)'!I19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="14" t="str">
+      <c r="C20" s="13" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
         <v>172.16.0.22</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="14" t="str">
+      <c r="E20" s="13" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>20</v>
       </c>
-      <c r="I20" s="14" cm="1">
+      <c r="I20" s="13" cm="1">
         <f t="array" ref="I20">'Site 1 (HUB)'!I20</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="14" t="str">
+      <c r="C21" s="13" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H21+$A$2)</f>
         <v>172.16.0.32</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="14" t="str">
+      <c r="E21" s="13" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>30</v>
       </c>
-      <c r="I21" s="14" t="b">
+      <c r="I21" s="13" t="b">
         <f>'Site 1 (HUB)'!I21</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="14" t="str">
+      <c r="C22" s="13" t="str">
         <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H22+$A$2)</f>
         <v>172.16.0.42</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="14" t="str">
+      <c r="E22" s="13" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>40</v>
       </c>
-      <c r="I22" s="14" t="b">
+      <c r="I22" s="13" t="b">
         <f>'Site 1 (HUB)'!I22</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="16" t="str">
+      <c r="C23" s="15" t="str">
         <f t="shared" si="5"/>
         <v>172.16.0.52</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="16" t="str">
+      <c r="E23" s="15" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16" t="s">
+      <c r="F23" s="15"/>
+      <c r="G23" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="15">
         <v>50</v>
       </c>
-      <c r="I23" s="14" t="b">
+      <c r="I23" s="13" t="b">
         <f>'Site 1 (HUB)'!I23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="17"/>
+      <c r="J23" s="16"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="13" t="s">
         <v>53</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -4072,99 +4131,99 @@
       <c r="H25"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="14">
+      <c r="A26" s="13">
         <f>A2</f>
         <v>2</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="13">
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H26" s="18"/>
+      <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="J28" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L28" s="30" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
+      <c r="A29" s="7">
         <f>(ROW())-(ROW()-1)</f>
         <v>1</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>10</v>
       </c>
-      <c r="C29" s="8" t="str">
+      <c r="C29" s="7" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</f>
         <v>10.12.0.2</v>
       </c>
-      <c r="D29" s="8" t="str">
+      <c r="D29" s="7" t="str">
         <f>$E$5</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="E29" s="8" t="str">
+      <c r="E29" s="7" t="str">
         <f>$F$5</f>
         <v>255.255.0.0</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="7">
         <v>24</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="7">
         <v>0</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="10">
         <v>3</v>
       </c>
-      <c r="I29" s="8"/>
+      <c r="I29" s="7"/>
       <c r="J29" s="2" t="s">
         <v>12</v>
       </c>
@@ -4178,34 +4237,34 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
+      <c r="A30" s="7">
         <v>2</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="7">
         <v>10</v>
       </c>
-      <c r="C30" s="8" t="str">
+      <c r="C30" s="7" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A30)</f>
         <v>10.12.0.3</v>
       </c>
-      <c r="D30" s="8" t="str">
+      <c r="D30" s="7" t="str">
         <f>$E$5</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="E30" s="8" t="str">
+      <c r="E30" s="7" t="str">
         <f>$F$5</f>
         <v>255.255.0.0</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="7">
         <v>24</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="7">
         <v>0</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="7">
         <v>3</v>
       </c>
-      <c r="I30" s="20" t="s">
+      <c r="I30" s="19" t="s">
         <v>67</v>
       </c>
       <c r="J30" s="2" t="s">
@@ -5227,277 +5286,277 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="21">
         <v>67</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="23" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="23" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>67</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="23" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>53</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="23" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>53</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="23" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>80</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="23" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>443</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="23" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>67</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="21" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="21" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>67</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="21" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="21" t="s">
         <v>76</v>
       </c>
     </row>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125B278D-439A-463B-812B-7B41AC6F3185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19E71B7-CEE4-4A47-BE89-C66DF3F89514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,19 +573,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="78">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1114,6 +1102,21 @@
       <font>
         <color theme="1"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1209,7 +1212,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:M2" headerRowDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:M2" headerRowDxfId="78">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="site"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="intf_prefix"/>
@@ -1217,13 +1220,13 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="76"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="75"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="74"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{1034F7EE-3D03-457B-B6E1-EC9EB8A68ABA}" name="tacacs_server_ip" dataDxfId="72"/>
-    <tableColumn id="12" xr3:uid="{17F5A604-6C04-47C4-886F-C1FB4C0FC7CA}" name="syslog_server_ip" dataDxfId="71"/>
-    <tableColumn id="13" xr3:uid="{3D895677-0966-4D0C-9B84-8565AE7DC140}" name="urpf_mode" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="77"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="76"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="75"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="74"/>
+    <tableColumn id="11" xr3:uid="{1034F7EE-3D03-457B-B6E1-EC9EB8A68ABA}" name="tacacs_server_ip" dataDxfId="73"/>
+    <tableColumn id="12" xr3:uid="{17F5A604-6C04-47C4-886F-C1FB4C0FC7CA}" name="syslog_server_ip" dataDxfId="72"/>
+    <tableColumn id="13" xr3:uid="{3D895677-0966-4D0C-9B84-8565AE7DC140}" name="urpf_mode" dataDxfId="71"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1232,25 +1235,25 @@
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A28:L30" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="12">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="10">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="11">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="9">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="8">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="4">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="2">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="MONITORING ip">
@@ -1278,7 +1281,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="1"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1318,13 +1321,13 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="interface"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="70">
       <calculatedColumnFormula>10&amp;"."&amp;($A$2)&amp;"."&amp;$B5&amp;"."&amp;0</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="gateway"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="69">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
 _xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
@@ -1332,7 +1335,7 @@
 _xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="68"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1358,11 +1361,11 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="tunnel id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="vrf"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address" dataDxfId="0">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;$H19&amp;"."&amp;($A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="69">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="67">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -1376,18 +1379,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="66">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="67">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="65">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Column1" dataDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Column1" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1396,28 +1399,28 @@
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:L29" totalsRowShown="0">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="59">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="57">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="57">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="55">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="56">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="54">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="55">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="53">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="54"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="49">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="47">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="48">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="46">
       <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1426,65 +1429,65 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:L2" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:L2" headerRowDxfId="45" dataDxfId="44">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="38">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="36">
       <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="36">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="34">
       <calculatedColumnFormula>'Site 1 (HUB)'!K2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="35">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="33">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{B53F3502-BEF9-4409-9767-9784EC3E3C30}" name="urpf_mode" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{B53F3502-BEF9-4409-9767-9784EC3E3C30}" name="urpf_mode" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="31">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="28">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="28">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="26">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:G26" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:G26" dataDxfId="20">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="19">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1902,7 +1905,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="7" t="str">
-        <f t="shared" ref="G5:G7" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
+        <f t="shared" ref="G6:G7" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
         <v>10.1.20.1</v>
       </c>
       <c r="H6" s="7" t="str" cm="1">
@@ -2172,14 +2175,14 @@
         <v>30</v>
       </c>
       <c r="C19" s="7" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</f>
-        <v>172.16.0.11</v>
+        <f t="shared" ref="C19:C23" si="9">172&amp;"."&amp;16&amp;"."&amp;$H19&amp;"."&amp;($A$2)</f>
+        <v>172.16.10.1</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E19" s="7" t="str">
-        <f t="shared" ref="E19:E23" si="9">$C$2</f>
+        <f t="shared" ref="E19:E23" si="10">$C$2</f>
         <v>1.1.1.0</v>
       </c>
       <c r="F19" s="7"/>
@@ -2200,14 +2203,14 @@
         <v>32</v>
       </c>
       <c r="C20" s="7" t="str">
-        <f t="shared" ref="C20:C21" si="10">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
-        <v>172.16.0.21</v>
+        <f t="shared" si="9"/>
+        <v>172.16.20.1</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E20" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1.0</v>
       </c>
       <c r="F20" s="7"/>
@@ -2228,14 +2231,14 @@
         <v>33</v>
       </c>
       <c r="C21" s="7" t="str">
-        <f t="shared" si="10"/>
-        <v>172.16.0.31</v>
+        <f t="shared" si="9"/>
+        <v>172.16.30.1</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E21" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1.0</v>
       </c>
       <c r="F21" s="7"/>
@@ -2258,14 +2261,14 @@
         <v>34</v>
       </c>
       <c r="C22" s="7" t="str">
-        <f t="shared" ref="C22" si="11">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H22+$A$2)</f>
-        <v>172.16.0.41</v>
+        <f t="shared" si="9"/>
+        <v>172.16.40.1</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E22" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1.0</v>
       </c>
       <c r="F22" s="7"/>
@@ -2288,14 +2291,14 @@
         <v>35</v>
       </c>
       <c r="C23" s="7" t="str">
-        <f t="shared" ref="C23" si="12">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H23+$A$2)</f>
-        <v>172.16.0.51</v>
+        <f t="shared" si="9"/>
+        <v>172.16.50.1</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E23" s="7" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1.0</v>
       </c>
       <c r="F23" s="7"/>
@@ -2449,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" ref="L29" si="13">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
+        <f t="shared" ref="L29" si="11">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
         <v>10.1.50.2</v>
       </c>
     </row>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\NO_MPLS_SAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\test\NO_MPLS_SAD_COMPAT_snmp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19E71B7-CEE4-4A47-BE89-C66DF3F89514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C1BB00-3E46-4169-9F88-8B2BE438F102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="128">
   <si>
     <t>site</t>
   </si>
@@ -80,6 +80,9 @@
     <t>secret</t>
   </si>
   <si>
+    <t>ISP-VLAN</t>
+  </si>
+  <si>
     <t>tacacs_key</t>
   </si>
   <si>
@@ -95,6 +98,42 @@
     <t>syslog_server_ip</t>
   </si>
   <si>
+    <t>urpf_mode</t>
+  </si>
+  <si>
+    <t>radius_server_ip</t>
+  </si>
+  <si>
+    <t>radius_key</t>
+  </si>
+  <si>
+    <t>dmvpn_phase</t>
+  </si>
+  <si>
+    <t>tacacs_syntax</t>
+  </si>
+  <si>
+    <t>radius_syntax</t>
+  </si>
+  <si>
+    <t>dot1x_syntax</t>
+  </si>
+  <si>
+    <t>eigrp_syntax</t>
+  </si>
+  <si>
+    <t>vrf_syntax</t>
+  </si>
+  <si>
+    <t>ike_version</t>
+  </si>
+  <si>
+    <t>secret_type</t>
+  </si>
+  <si>
+    <t>trunk_encapsulation</t>
+  </si>
+  <si>
     <t>g0/</t>
   </si>
   <si>
@@ -104,7 +143,7 @@
     <t>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</t>
   </si>
   <si>
-    <t>0 - 15</t>
+    <t>0 - 4</t>
   </si>
   <si>
     <t>TACACS-KEY</t>
@@ -113,7 +152,31 @@
     <t>192.168.255.1</t>
   </si>
   <si>
-    <t>10.11.0.10</t>
+    <t>10.1.10.10</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>RADIUS-KEY</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>AUTH</t>
+  </si>
+  <si>
+    <t>NAMED</t>
+  </si>
+  <si>
+    <t>OLD</t>
+  </si>
+  <si>
+    <t>IKEV2</t>
+  </si>
+  <si>
+    <t>AUTO</t>
   </si>
   <si>
     <t>vrf</t>
@@ -152,7 +215,7 @@
     <t>MGMT</t>
   </si>
   <si>
-    <t>255.255.0.0</t>
+    <t>255.255.255.0</t>
   </si>
   <si>
     <t>INET</t>
@@ -167,9 +230,6 @@
     <t>MONITORING</t>
   </si>
   <si>
-    <t>255.255.255.0</t>
-  </si>
-  <si>
     <t>loopback</t>
   </si>
   <si>
@@ -224,10 +284,10 @@
     <t>span_mode</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>ERSPAN</t>
+    <t>dot1x_vlans</t>
+  </si>
+  <si>
+    <t>20,30</t>
   </si>
   <si>
     <t>SW</t>
@@ -257,16 +317,13 @@
     <t>MONITORING ip</t>
   </si>
   <si>
-    <t>20.0-40.0-30.0</t>
-  </si>
-  <si>
-    <t>30.1-20.10-40.4</t>
-  </si>
-  <si>
-    <t>urpf_mode</t>
-  </si>
-  <si>
-    <t>OFF</t>
+    <t>20.1-200.1</t>
+  </si>
+  <si>
+    <t>DOT1Q_CMD</t>
+  </si>
+  <si>
+    <t>30.1-20.1</t>
   </si>
   <si>
     <t>protocol</t>
@@ -305,7 +362,7 @@
     <t>VRF-navn</t>
   </si>
   <si>
-    <t>Destination=MGMT/INET/UNET/PA betyr alle kjente nett og VRF-loopbacks i den VRF-en på tvers av sites.</t>
+    <t>Destination=MGMT/INET/UNET/PA betyr kjente LAN-nett i VRF-en på tvers av sites. MGMT inkluderer også MGMT-loopbacks for administrasjon.</t>
   </si>
   <si>
     <t>INTERNET/ANY</t>
@@ -348,13 +405,49 @@
   </si>
   <si>
     <t>Endre radene i A:E til den faktiske tjenestematrisen. Bare sources som finnes i policyen får en generert ingress-ACL.</t>
+  </si>
+  <si>
+    <t>RADIUS</t>
+  </si>
+  <si>
+    <t>Destination=RADIUS kan brukes som symbolsk mål og slår opp radius_server_ip fra site-metadata.</t>
+  </si>
+  <si>
+    <t>802.1X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dot1x_vlans i switch-metadata styrer hvilke klient-VLAN som får 802.1X på accessportene. </t>
+  </si>
+  <si>
+    <t>snmpv3_enabled</t>
+  </si>
+  <si>
+    <t>snmp_server_ip</t>
+  </si>
+  <si>
+    <t>snmp_user</t>
+  </si>
+  <si>
+    <t>snmp_auth_password</t>
+  </si>
+  <si>
+    <t>snmp_priv_password</t>
+  </si>
+  <si>
+    <t>nmsuser</t>
+  </si>
+  <si>
+    <t>SNMP-AUTH-KEY</t>
+  </si>
+  <si>
+    <t>SNMP-PRIV-KEY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -434,27 +527,36 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,8 +578,23 @@
         <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EAD55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EAD55"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -485,11 +602,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="7"/>
+      </right>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="7"/>
+      </right>
+      <top style="thin">
+        <color theme="7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -537,9 +676,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -569,16 +705,190 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="79">
-    <dxf>
+  <dxfs count="111">
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <u val="none"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
@@ -588,24 +898,494 @@
     </dxf>
     <dxf>
       <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
         <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
       </font>
     </dxf>
     <dxf>
@@ -655,405 +1435,7 @@
     </dxf>
     <dxf>
       <font>
-        <u val="none"/>
-        <sz val="11"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
       </font>
     </dxf>
     <dxf>
@@ -1107,6 +1489,9 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <font>
         <u val="none"/>
         <sz val="11"/>
@@ -1186,14 +1571,108 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
+        <u val="none"/>
         <sz val="10"/>
-        <color auto="1"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
@@ -1211,54 +1690,93 @@
 </styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:M2" headerRowDxfId="78">
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:AD2">
+  <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="site"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="intf_prefix"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="router-id"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="77"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="76"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="75"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="74"/>
-    <tableColumn id="11" xr3:uid="{1034F7EE-3D03-457B-B6E1-EC9EB8A68ABA}" name="tacacs_server_ip" dataDxfId="73"/>
-    <tableColumn id="12" xr3:uid="{17F5A604-6C04-47C4-886F-C1FB4C0FC7CA}" name="syslog_server_ip" dataDxfId="72"/>
-    <tableColumn id="13" xr3:uid="{3D895677-0966-4D0C-9B84-8565AE7DC140}" name="urpf_mode" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="110"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ISP-VLAN" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="tacacs_server_ip" dataDxfId="105"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="syslog_server_ip" dataDxfId="104"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="urpf_mode" dataDxfId="103"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="radius_server_ip" dataDxfId="102"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="radius_key" dataDxfId="101"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="dmvpn_phase" dataDxfId="100"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="tacacs_syntax" dataDxfId="99"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="radius_syntax" dataDxfId="98"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="dot1x_syntax" dataDxfId="97"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="eigrp_syntax" dataDxfId="96"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="vrf_syntax" dataDxfId="95"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ike_version" dataDxfId="94"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="secret_type" dataDxfId="93"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="trunk_encapsulation" dataDxfId="92"/>
+    <tableColumn id="26" xr3:uid="{7A70CB3D-3E69-4511-AFC7-833193219BEB}" name="snmpv3_enabled" dataDxfId="9"/>
+    <tableColumn id="27" xr3:uid="{209B66CE-CA9A-4100-AF1F-D365CF1FFE1D}" name="snmp_server_ip" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{35546B6C-3A4D-4CB1-960A-7557AC2139AF}" name="snmp_user" dataDxfId="7"/>
+    <tableColumn id="29" xr3:uid="{EEE156DA-8F56-4FDB-B5BD-E05593FB26D6}" name="snmp_auth_password" dataDxfId="6"/>
+    <tableColumn id="30" xr3:uid="{C5D4501A-8EFA-4918-A4F1-64D389B519DA}" name="snmp_priv_password" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A28:L30" totalsRowShown="0">
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A28:Q29" totalsRowShown="0">
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="21">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="19">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="18">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="17">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="11">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="MONITORING ip">
       <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0900-00000D000000}" name="tacacs_syntax"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="radius_syntax"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="dot1x_syntax"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0900-000010000000}" name="secret_type"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0900-000011000000}" name="trunk_encapsulation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1281,7 +1799,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="10"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1321,13 +1839,13 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="interface"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="70">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="91">
       <calculatedColumnFormula>10&amp;"."&amp;($A$2)&amp;"."&amp;$B5&amp;"."&amp;0</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="gateway"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="69">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="90">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
 _xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
@@ -1335,7 +1853,7 @@
 _xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="89"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1361,11 +1879,11 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="tunnel id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="vrf"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address" dataDxfId="88">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;$H19&amp;"."&amp;($A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="67">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="87">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -1379,115 +1897,137 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:H26" dataDxfId="66">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:I26" dataDxfId="86">
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="85">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="60"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Column1" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="82"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="77">
+      <calculatedColumnFormula array="1">Tabell5[ISP-VLAN]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:L29" totalsRowShown="0">
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:Q29" totalsRowShown="0">
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="76">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="55">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="74">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="54">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="73">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="53">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="72">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="47">
-      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="71"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="69"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="66"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="65">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$9&amp;"."&amp;(A29+1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="46">
-      <calculatedColumnFormula>LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="tacacs_syntax"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="radius_syntax"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="dot1x_syntax"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0500-000010000000}" name="secret_type"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0500-000011000000}" name="trunk_encapsulation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:L2" headerRowDxfId="45" dataDxfId="44">
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="36">
-      <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:AA2" dataDxfId="64">
+  <tableColumns count="27">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="56">
+      <calculatedColumnFormula>'Site 1 (HUB)'!I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="34">
-      <calculatedColumnFormula>'Site 1 (HUB)'!K2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="33">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="54">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{B53F3502-BEF9-4409-9767-9784EC3E3C30}" name="urpf_mode" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="53">
+      <calculatedColumnFormula>'Site 1 (HUB)'!M2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="urpf_mode" dataDxfId="52"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="radius_server_ip" dataDxfId="51"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="radius_key" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="tacacs_syntax" dataDxfId="49"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" name="radius_syntax" dataDxfId="48"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" name="dot1x_syntax" dataDxfId="47"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" name="eigrp_syntax" dataDxfId="46"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" name="vrf_syntax" dataDxfId="45"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" name="ike_version" dataDxfId="44"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" name="secret_type" dataDxfId="43"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" name="trunk_encapsulation" dataDxfId="42"/>
+    <tableColumn id="23" xr3:uid="{96BFD35F-5B86-4563-AD71-9BEE692F259E}" name="snmpv3_enabled" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{B32071E9-38D7-497D-8D05-9C277245ED7D}" name="snmp_server_ip" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{A51FD30E-2A50-4B3C-B10C-DC9965677024}" name="snmp_user" dataDxfId="2"/>
+    <tableColumn id="26" xr3:uid="{E35869A0-05B2-4390-88E0-3DB67D32BD41}" name="snmp_auth_password" dataDxfId="1"/>
+    <tableColumn id="27" xr3:uid="{962D48F4-6B6F-4976-A32F-AFCF203A4E6E}" name="snmp_priv_password" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A18:J23" dataDxfId="41">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="38">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="26">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="36">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:G26" dataDxfId="20">
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A25:H26" dataDxfId="30">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="29">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="dot1x_vlans" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1688,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1004"/>
+  <dimension ref="A1:AD1004"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -1701,94 +2241,200 @@
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="25.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="11" max="24" width="18" customWidth="1"/>
+    <col min="26" max="26" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:30" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA1" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB1" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC1" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD1" s="40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>1.1.1.0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="b">
+        <v>27</v>
+      </c>
+      <c r="H2" s="39">
+        <v>200</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="23">
+        <v>3</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB2" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC2" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD2" s="42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="4"/>
@@ -1797,47 +2443,47 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+    </row>
+    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B5" s="8">
         <v>10</v>
@@ -1846,31 +2492,22 @@
         <v>0</v>
       </c>
       <c r="D5" s="7" t="str">
-        <f>10&amp;"."&amp;($A$2)&amp;"."&amp;B5&amp;"."&amp;0</f>
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".0"</f>
         <v>10.1.10.0</v>
       </c>
       <c r="E5" s="7" t="str">
-        <f>LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".1"</f>
         <v>10.1.10.1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G5" s="7" t="str" cm="1">
-        <f t="array" ref="G5">_xlfn.LET(
-_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
-_xlpm.addr,_xlpm.net+1,
-_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
-)</f>
+        <f>VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
         <v>10.1.10.1</v>
       </c>
       <c r="H5" s="7" t="str" cm="1">
-        <f t="array" ref="H5">_xlfn.LET(
-_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
-_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
-_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
-_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
-)</f>
+        <f>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</f>
         <v>10.1.10.254</v>
       </c>
       <c r="I5" s="7">
@@ -1883,9 +2520,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B6" s="8">
         <v>20</v>
@@ -1894,27 +2531,22 @@
         <v>0</v>
       </c>
       <c r="D6" s="7" t="str">
-        <f t="shared" ref="D6:D9" si="0">10&amp;"."&amp;($A$2)&amp;"."&amp;$B6&amp;"."&amp;0</f>
+        <f t="shared" ref="D6:D9" si="0">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
         <v>10.1.20.0</v>
       </c>
       <c r="E6" s="7" t="str">
-        <f t="shared" ref="E6:E7" si="1">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
+        <f t="shared" ref="E6:E7" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
         <v>10.1.20.1</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G6" s="7" t="str">
-        <f t="shared" ref="G6:G7" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
+        <f t="shared" ref="G6:G7" si="2">VALUE(LEFT(D6,FIND(".",D6)-1))&amp;"."&amp;VALUE(MID(D6,FIND(".",D6)+1,FIND(".",D6,FIND(".",D6)+1)-FIND(".",D6)-1))&amp;"."&amp;VALUE(MID(D6,FIND(".",D6,FIND(".",D6)+1)+1,FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)-FIND(".",D6,FIND(".",D6)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D6,LEN(D6)-FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)))+1)</f>
         <v>10.1.20.1</v>
       </c>
       <c r="H6" s="7" t="str" cm="1">
-        <f t="array" ref="H6">_xlfn.LET(
-_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
-_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
-_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
-_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
-)</f>
+        <f>(VALUE(LEFT(D6,FIND(".",D6)-1))+255-VALUE(LEFT(F6,FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6)+1,FIND(".",D6,FIND(".",D6)+1)-FIND(".",D6)-1))+255-VALUE(MID(F6,FIND(".",F6)+1,FIND(".",F6,FIND(".",F6)+1)-FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6,FIND(".",D6)+1)+1,FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)-FIND(".",D6,FIND(".",D6)+1)-1))+255-VALUE(MID(F6,FIND(".",F6,FIND(".",F6)+1)+1,FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)-FIND(".",F6,FIND(".",F6)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D6,LEN(D6)-FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)))+255-VALUE(RIGHT(F6,LEN(F6)-FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)))-1)</f>
         <v>10.1.20.254</v>
       </c>
       <c r="I6" s="7">
@@ -1927,9 +2559,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B7" s="8">
         <v>30</v>
@@ -1946,19 +2578,14 @@
         <v>10.1.30.1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="2"/>
         <v>10.1.30.1</v>
       </c>
       <c r="H7" s="7" t="str" cm="1">
-        <f t="array" ref="H7">_xlfn.LET(
-_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
-_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
-_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
-_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
-)</f>
+        <f>(VALUE(LEFT(D7,FIND(".",D7)-1))+255-VALUE(LEFT(F7,FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7)+1,FIND(".",D7,FIND(".",D7)+1)-FIND(".",D7)-1))+255-VALUE(MID(F7,FIND(".",F7)+1,FIND(".",F7,FIND(".",F7)+1)-FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7,FIND(".",D7)+1)+1,FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)-FIND(".",D7,FIND(".",D7)+1)-1))+255-VALUE(MID(F7,FIND(".",F7,FIND(".",F7)+1)+1,FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)-FIND(".",F7,FIND(".",F7)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D7,LEN(D7)-FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)))+255-VALUE(RIGHT(F7,LEN(F7)-FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)))-1)</f>
         <v>10.1.30.254</v>
       </c>
       <c r="I7" s="7">
@@ -1971,9 +2598,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B8" s="8">
         <v>40</v>
@@ -1986,23 +2613,18 @@
         <v>10.1.40.0</v>
       </c>
       <c r="E8" s="7" t="str">
-        <f t="shared" ref="E8" si="3">LEFT(D8,LEN(D8)-1)&amp;"1"</f>
+        <f t="shared" ref="E8" si="3">10&amp;"."&amp;$A$2&amp;"."&amp;B8&amp;".1"</f>
         <v>10.1.40.1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="str">
-        <f t="shared" ref="G8" si="4">LEFT(D8,LEN(D8)-1)&amp;"1"</f>
+        <f t="shared" ref="G8" si="4">VALUE(LEFT(D8,FIND(".",D8)-1))&amp;"."&amp;VALUE(MID(D8,FIND(".",D8)+1,FIND(".",D8,FIND(".",D8)+1)-FIND(".",D8)-1))&amp;"."&amp;VALUE(MID(D8,FIND(".",D8,FIND(".",D8)+1)+1,FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)-FIND(".",D8,FIND(".",D8)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D8,LEN(D8)-FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)))+1)</f>
         <v>10.1.40.1</v>
       </c>
-      <c r="H8" s="7" t="str" cm="1">
-        <f t="array" ref="H8">_xlfn.LET(
-_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
-_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
-_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
-_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
-)</f>
+      <c r="H8" s="7" t="str">
+        <f>(VALUE(LEFT(D8,FIND(".",D8)-1))+255-VALUE(LEFT(F8,FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8)+1,FIND(".",D8,FIND(".",D8)+1)-FIND(".",D8)-1))+255-VALUE(MID(F8,FIND(".",F8)+1,FIND(".",F8,FIND(".",F8)+1)-FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8,FIND(".",D8)+1)+1,FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)-FIND(".",D8,FIND(".",D8)+1)-1))+255-VALUE(MID(F8,FIND(".",F8,FIND(".",F8)+1)+1,FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)-FIND(".",F8,FIND(".",F8)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D8,LEN(D8)-FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)))+255-VALUE(RIGHT(F8,LEN(F8)-FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)))-1)</f>
         <v>10.1.40.254</v>
       </c>
       <c r="I8" s="7">
@@ -2015,9 +2637,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B9" s="8">
         <v>50</v>
@@ -2030,23 +2652,18 @@
         <v>10.1.50.0</v>
       </c>
       <c r="E9" s="7" t="str">
-        <f t="shared" ref="E9" si="5">LEFT(D9,LEN(D9)-1)&amp;"1"</f>
+        <f t="shared" ref="E9" si="5">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".1"</f>
         <v>10.1.50.1</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G9" s="7" t="str">
-        <f t="shared" ref="G9" si="6">LEFT(D9,LEN(D9)-1)&amp;"1"</f>
+        <f t="shared" ref="G9" si="6">VALUE(LEFT(D9,FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+1)</f>
         <v>10.1.50.1</v>
       </c>
       <c r="H9" s="7" t="str" cm="1">
-        <f t="array" ref="H9">_xlfn.LET(
-_xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
-_xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
-_xlpm.addr,_xlpm.net+(4294967295-_xlpm.mask)-1,
-_xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
-)</f>
+        <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
         <v>10.1.50.254</v>
       </c>
       <c r="I9" s="7">
@@ -2059,48 +2676,48 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B12" s="7">
         <v>10</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
         <v>1.1.1.10</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7">
         <v>20</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f t="shared" ref="C13:C15" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B13)</f>
+        <f t="shared" ref="C13:C15" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
         <v>1.1.1.20</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B14" s="7">
         <v>30</v>
@@ -2110,9 +2727,9 @@
         <v>1.1.1.30</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7">
         <v>40</v>
@@ -2122,64 +2739,64 @@
         <v>1.1.1.40</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7">
         <v>50</v>
       </c>
       <c r="C16" s="7" t="str">
-        <f t="shared" ref="C16" si="8">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B16)</f>
+        <f t="shared" ref="C16" si="8">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B16</f>
         <v>1.1.1.50</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C19" s="7" t="str">
-        <f t="shared" ref="C19:C23" si="9">172&amp;"."&amp;16&amp;"."&amp;$H19&amp;"."&amp;($A$2)</f>
+        <f t="shared" ref="C19:C23" si="9">172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
         <v>172.16.10.1</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E19" s="7" t="str">
         <f t="shared" ref="E19:E23" si="10">$C$2</f>
@@ -2187,27 +2804,29 @@
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H19" s="2">
         <v>10</v>
       </c>
-      <c r="I19" s="2"/>
+      <c r="I19" s="32" t="b">
+        <v>1</v>
+      </c>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C20" s="7" t="str">
         <f t="shared" si="9"/>
         <v>172.16.20.1</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E20" s="7" t="str">
         <f t="shared" si="10"/>
@@ -2215,27 +2834,29 @@
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H20" s="2">
         <v>20</v>
       </c>
-      <c r="I20" s="2"/>
+      <c r="I20" s="32" t="b">
+        <v>0</v>
+      </c>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C21" s="7" t="str">
         <f t="shared" si="9"/>
         <v>172.16.30.1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E21" s="7" t="str">
         <f t="shared" si="10"/>
@@ -2243,29 +2864,29 @@
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H21" s="2">
         <v>30</v>
       </c>
-      <c r="I21" s="2" t="b">
+      <c r="I21" s="32" t="b">
         <v>1</v>
       </c>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C22" s="7" t="str">
         <f t="shared" si="9"/>
         <v>172.16.40.1</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E22" s="7" t="str">
         <f t="shared" si="10"/>
@@ -2273,29 +2894,29 @@
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H22" s="2">
         <v>40</v>
       </c>
-      <c r="I22" s="2" t="b">
+      <c r="I22" s="32" t="b">
         <v>1</v>
       </c>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C23" s="7" t="str">
         <f t="shared" si="9"/>
         <v>172.16.50.1</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E23" s="7" t="str">
         <f t="shared" si="10"/>
@@ -2303,17 +2924,17 @@
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H23" s="2">
         <v>50</v>
       </c>
-      <c r="I23" s="2" t="b">
+      <c r="I23" s="32" t="b">
         <v>1</v>
       </c>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2322,7 +2943,7 @@
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -2339,89 +2960,116 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <f>A2</f>
+        <f>$A$2</f>
         <v>1</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>14</v>
+      <c r="B26" s="2" t="str">
+        <f>$D$2</f>
+        <v>admin</v>
+      </c>
+      <c r="C26" s="2" t="str">
+        <f>$E$2</f>
+        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f>$F$2</f>
+        <v>0 - 4</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f>$G$2</f>
+        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26" s="17"/>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G26" s="2"/>
+      <c r="H26" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" s="39" cm="1">
+        <f t="array" ref="I26">Tabell5[ISP-VLAN]</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="J28" s="14" t="s">
         <v>1</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L28" s="30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="L28" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
-        <f>(ROW())-(ROW()-1)</f>
+        <f>ROW()-28</f>
         <v>1</v>
       </c>
       <c r="B29" s="7">
+        <f>$B$5</f>
         <v>10</v>
       </c>
       <c r="C29" s="7" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</f>
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</f>
         <v>10.1.10.2</v>
       </c>
       <c r="D29" s="7" t="str">
@@ -2442,55 +3090,246 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K29" s="2">
-        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF($K$2&lt;&gt;$L$2,1,0)-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
-        <v>1</v>
+        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <v>2</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" ref="L29" si="11">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$9&amp;"."&amp;(A29+1)</f>
         <v>10.1.50.2</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+    </row>
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+    </row>
+    <row r="33" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+    </row>
+    <row r="34" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+    </row>
+    <row r="35" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+    </row>
+    <row r="36" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
+    </row>
+    <row r="37" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+    </row>
+    <row r="38" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35"/>
+    </row>
+    <row r="39" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35"/>
+    </row>
+    <row r="40" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M40" s="35"/>
+      <c r="N40" s="35"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+    </row>
+    <row r="41" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="35"/>
+    </row>
+    <row r="42" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M42" s="35"/>
+      <c r="N42" s="35"/>
+      <c r="O42" s="35"/>
+      <c r="P42" s="35"/>
+      <c r="Q42" s="35"/>
+    </row>
+    <row r="43" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="35"/>
+    </row>
+    <row r="44" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
+    </row>
+    <row r="45" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M45" s="35"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
+    </row>
+    <row r="46" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+    </row>
+    <row r="47" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+    </row>
+    <row r="48" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M48" s="35"/>
+      <c r="N48" s="35"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="35"/>
+    </row>
+    <row r="49" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M49" s="35"/>
+      <c r="N49" s="35"/>
+      <c r="O49" s="35"/>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="35"/>
+    </row>
+    <row r="50" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M50" s="35"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="35"/>
+    </row>
+    <row r="51" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M51" s="35"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+    </row>
+    <row r="52" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+    </row>
+    <row r="53" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+    </row>
+    <row r="54" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="35"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+    </row>
+    <row r="55" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M55" s="35"/>
+      <c r="N55" s="35"/>
+      <c r="O55" s="35"/>
+      <c r="P55" s="35"/>
+      <c r="Q55" s="35"/>
+    </row>
+    <row r="56" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+    </row>
+    <row r="57" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
+      <c r="Q57" s="35"/>
+    </row>
+    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M58" s="35"/>
+      <c r="N58" s="35"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="35"/>
+      <c r="Q58" s="35"/>
+    </row>
+    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="35"/>
+      <c r="Q59" s="35"/>
+    </row>
+    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M60" s="35"/>
+      <c r="N60" s="35"/>
+      <c r="O60" s="35"/>
+      <c r="P60" s="35"/>
+      <c r="Q60" s="35"/>
+    </row>
+    <row r="61" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3432,15 +4271,36 @@
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="10">
     <dataValidation type="list" sqref="G26" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M2" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="N2" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"OFF,STRICT,LOOSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="Q2" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>"2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="M29:N60 V2 R2:S2" xr:uid="{00000000-0002-0000-0000-000004000000}">
+      <formula1>"OLD,NEW"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="T2 O29:O60" xr:uid="{00000000-0002-0000-0000-000005000000}">
+      <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="U2" xr:uid="{00000000-0002-0000-0000-000006000000}">
+      <formula1>"CLASSIC,NAMED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="W2" xr:uid="{00000000-0002-0000-0000-000007000000}">
+      <formula1>"IKEV1,IKEV2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="X2 P29:P60" xr:uid="{00000000-0002-0000-0000-000008000000}">
+      <formula1>"AUTO,5,8,9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="Y2 Q29:Q60" xr:uid="{00000000-0002-0000-0000-000009000000}">
+      <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3457,144 +4317,243 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M998"/>
+  <dimension ref="A1:AA998"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="13" style="13" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="13" customWidth="1"/>
     <col min="3" max="3" width="75.85546875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="13" customWidth="1"/>
     <col min="5" max="5" width="75.85546875" style="13" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" style="13" customWidth="1"/>
     <col min="7" max="7" width="75.85546875" style="13" customWidth="1"/>
-    <col min="8" max="8" width="22" style="13" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="13" customWidth="1"/>
     <col min="10" max="10" width="16.140625" style="13" customWidth="1"/>
     <col min="11" max="11" width="16.85546875" style="13" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="16384" width="12.5703125" style="13"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="13" max="14" width="18" style="13" customWidth="1"/>
+    <col min="15" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="19.5703125" customWidth="1"/>
+    <col min="18" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" style="13" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" customWidth="1"/>
+    <col min="25" max="25" width="9.42578125" customWidth="1"/>
+    <col min="26" max="27" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:27" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="26" t="s">
+      <c r="H1" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="J1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K1" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="X1" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y1" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z1" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA1" s="37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13">
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C2" s="13" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
         <v>2.2.2.0</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H2" s="13" t="str">
-        <f>'Site 1 (HUB)'!H2</f>
+        <f>'Site 1 (HUB)'!I2</f>
         <v>TACACS-KEY</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J2" s="18" t="str">
-        <f>'Site 1 (HUB)'!K2</f>
-        <v>10.11.0.10</v>
+        <f>'Site 1 (HUB)'!L2</f>
+        <v>10.1.10.10</v>
       </c>
       <c r="K2" s="18" t="str">
-        <f>'Site 1 (HUB)'!L2</f>
-        <v>10.11.0.10</v>
-      </c>
-      <c r="L2" s="25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+        <f>'Site 1 (HUB)'!M2</f>
+        <v>10.1.10.10</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="34" t="str">
+        <f>'Site 1 (HUB)'!O2</f>
+        <v>10.1.10.10</v>
+      </c>
+      <c r="N2" s="34" t="str">
+        <f>'Site 1 (HUB)'!P2</f>
+        <v>RADIUS-KEY</v>
+      </c>
+      <c r="O2" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" s="38">
+        <v>9</v>
+      </c>
+      <c r="V2" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" s="43" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y2" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z2" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA2" s="44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B5" s="8">
         <v>10</v>
@@ -3603,23 +4562,23 @@
         <v>0</v>
       </c>
       <c r="D5" s="7" t="str">
-        <f>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
-        <v>10.12.0.0</v>
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".0"</f>
+        <v>10.2.10.0</v>
       </c>
       <c r="E5" s="7" t="str">
-        <f>LEFT(D5,LEN(D5)-1)&amp;"1"</f>
-        <v>10.12.0.1</v>
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".1"</f>
+        <v>10.2.10.1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" ref="G5:G9" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
-        <v>10.12.0.1</v>
+        <f t="shared" ref="G5:G9" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
+        <v>10.2.10.1</v>
       </c>
       <c r="H5" s="7" t="str">
-        <f>LEFT(D5,FIND(".",D5,FIND(".",D5)+1)-1)&amp;".255.254"</f>
-        <v>10.12.255.254</v>
+        <f>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</f>
+        <v>10.2.10.254</v>
       </c>
       <c r="I5" s="7">
         <v>40</v>
@@ -3631,9 +4590,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B6" s="8">
         <v>20</v>
@@ -3642,23 +4601,23 @@
         <v>0</v>
       </c>
       <c r="D6" s="7" t="str">
-        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;(B6+$A$2)&amp;"."&amp;0&amp;"."&amp;0</f>
-        <v>10.22.0.0</v>
+        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
+        <v>10.2.20.0</v>
       </c>
       <c r="E6" s="7" t="str">
-        <f t="shared" ref="E6:E9" si="2">LEFT(D6,LEN(D6)-1)&amp;"1"</f>
-        <v>10.22.0.1</v>
+        <f t="shared" ref="E6:E9" si="2">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
+        <v>10.2.20.1</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>10.22.0.1</v>
+        <v>10.2.20.1</v>
       </c>
       <c r="H6" s="7" t="str">
-        <f>LEFT(D6,FIND(".",D6,FIND(".",D6)+1)-1)&amp;".255.254"</f>
-        <v>10.22.255.254</v>
+        <f>(VALUE(LEFT(D6,FIND(".",D6)-1))+255-VALUE(LEFT(F6,FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6)+1,FIND(".",D6,FIND(".",D6)+1)-FIND(".",D6)-1))+255-VALUE(MID(F6,FIND(".",F6)+1,FIND(".",F6,FIND(".",F6)+1)-FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6,FIND(".",D6)+1)+1,FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)-FIND(".",D6,FIND(".",D6)+1)-1))+255-VALUE(MID(F6,FIND(".",F6,FIND(".",F6)+1)+1,FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)-FIND(".",F6,FIND(".",F6)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D6,LEN(D6)-FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)))+255-VALUE(RIGHT(F6,LEN(F6)-FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)))-1)</f>
+        <v>10.2.20.254</v>
       </c>
       <c r="I6" s="7">
         <v>40</v>
@@ -3670,9 +4629,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B7" s="8">
         <v>30</v>
@@ -3682,22 +4641,22 @@
       </c>
       <c r="D7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>10.32.0.0</v>
+        <v>10.2.30.0</v>
       </c>
       <c r="E7" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>10.32.0.1</v>
+        <v>10.2.30.1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>10.32.0.1</v>
+        <v>10.2.30.1</v>
       </c>
       <c r="H7" s="7" t="str">
-        <f>LEFT(D7,FIND(".",D7,FIND(".",D7)+1)-1)&amp;".255.254"</f>
-        <v>10.32.255.254</v>
+        <f>(VALUE(LEFT(D7,FIND(".",D7)-1))+255-VALUE(LEFT(F7,FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7)+1,FIND(".",D7,FIND(".",D7)+1)-FIND(".",D7)-1))+255-VALUE(MID(F7,FIND(".",F7)+1,FIND(".",F7,FIND(".",F7)+1)-FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7,FIND(".",D7)+1)+1,FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)-FIND(".",D7,FIND(".",D7)+1)-1))+255-VALUE(MID(F7,FIND(".",F7,FIND(".",F7)+1)+1,FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)-FIND(".",F7,FIND(".",F7)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D7,LEN(D7)-FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)))+255-VALUE(RIGHT(F7,LEN(F7)-FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)))-1)</f>
+        <v>10.2.30.254</v>
       </c>
       <c r="I7" s="7">
         <v>40</v>
@@ -3709,9 +4668,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B8" s="8">
         <v>40</v>
@@ -3721,22 +4680,22 @@
       </c>
       <c r="D8" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>10.42.0.0</v>
+        <v>10.2.40.0</v>
       </c>
       <c r="E8" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>10.42.0.1</v>
+        <v>10.2.40.1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>10.42.0.1</v>
+        <v>10.2.40.1</v>
       </c>
       <c r="H8" s="7" t="str">
-        <f>LEFT(D8,FIND(".",D8,FIND(".",D8)+1)-1)&amp;".255.254"</f>
-        <v>10.42.255.254</v>
+        <f>(VALUE(LEFT(D8,FIND(".",D8)-1))+255-VALUE(LEFT(F8,FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8)+1,FIND(".",D8,FIND(".",D8)+1)-FIND(".",D8)-1))+255-VALUE(MID(F8,FIND(".",F8)+1,FIND(".",F8,FIND(".",F8)+1)-FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8,FIND(".",D8)+1)+1,FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)-FIND(".",D8,FIND(".",D8)+1)-1))+255-VALUE(MID(F8,FIND(".",F8,FIND(".",F8)+1)+1,FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)-FIND(".",F8,FIND(".",F8)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D8,LEN(D8)-FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)))+255-VALUE(RIGHT(F8,LEN(F8)-FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)))-1)</f>
+        <v>10.2.40.254</v>
       </c>
       <c r="I8" s="7">
         <v>40</v>
@@ -3749,9 +4708,9 @@
       </c>
       <c r="L8" s="13"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B9" s="8">
         <v>50</v>
@@ -3761,22 +4720,22 @@
       </c>
       <c r="D9" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>10.52.0.0</v>
+        <v>10.2.50.0</v>
       </c>
       <c r="E9" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>10.52.0.1</v>
+        <v>10.2.50.1</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G9" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>10.52.0.1</v>
+        <v>10.2.50.1</v>
       </c>
       <c r="H9" s="7" t="str">
-        <f>LEFT(D9,FIND(".",D9,FIND(".",D9)+1)-1)&amp;".0.254"</f>
-        <v>10.52.0.254</v>
+        <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
+        <v>10.2.50.254</v>
       </c>
       <c r="I9" s="7">
         <v>40</v>
@@ -3789,7 +4748,7 @@
       </c>
       <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10"/>
@@ -3803,15 +4762,15 @@
       <c r="K10"/>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -3823,15 +4782,15 @@
       <c r="K11"/>
       <c r="L11" s="13"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="B12" s="7">
         <v>10</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</f>
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
         <v>2.2.2.10</v>
       </c>
       <c r="D12"/>
@@ -3844,15 +4803,15 @@
       <c r="K12"/>
       <c r="L12" s="13"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7">
         <v>20</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B13)</f>
+        <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
         <v>2.2.2.20</v>
       </c>
       <c r="D13"/>
@@ -3865,9 +4824,9 @@
       <c r="K13"/>
       <c r="L13" s="13"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B14" s="7">
         <v>30</v>
@@ -3886,9 +4845,9 @@
       <c r="K14"/>
       <c r="L14" s="13"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7">
         <v>40</v>
@@ -3907,9 +4866,9 @@
       <c r="K15"/>
       <c r="L15" s="13"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7">
         <v>50</v>
@@ -3928,168 +4887,176 @@
       <c r="K16"/>
       <c r="L16" s="13"/>
     </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C19" s="13" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H19+$A$2)</f>
-        <v>172.16.0.12</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
+        <v>172.16.10.2</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E19" s="13" t="str">
         <f t="shared" ref="E19:E23" si="4">$C$2</f>
         <v>2.2.2.0</v>
       </c>
+      <c r="F19"/>
       <c r="G19" s="13" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H19" s="13">
         <v>10</v>
       </c>
-      <c r="I19" s="13">
-        <f t="array" ref="I19">'Site 1 (HUB)'!I19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I19" s="33" t="b">
+        <f>'Site 1 (HUB)'!I19</f>
+        <v>1</v>
+      </c>
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C20" s="13" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H20+$A$2)</f>
-        <v>172.16.0.22</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
+        <v>172.16.20.2</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E20" s="13" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
+      <c r="F20"/>
       <c r="G20" s="13" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H20" s="13">
         <v>20</v>
       </c>
-      <c r="I20" s="13" cm="1">
-        <f t="array" ref="I20">'Site 1 (HUB)'!I20</f>
+      <c r="I20" s="33" t="b" cm="1">
+        <f>'Site 1 (HUB)'!I20</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C21" s="13" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H21+$A$2)</f>
-        <v>172.16.0.32</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;H21&amp;"."&amp;$A$2</f>
+        <v>172.16.30.2</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E21" s="13" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
+      <c r="F21"/>
       <c r="G21" s="13" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H21" s="13">
         <v>30</v>
       </c>
-      <c r="I21" s="13" t="b">
+      <c r="I21" s="33" t="b">
         <f>'Site 1 (HUB)'!I21</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C22" s="13" t="str">
-        <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H22+$A$2)</f>
-        <v>172.16.0.42</v>
+        <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;H22&amp;"."&amp;$A$2</f>
+        <v>172.16.40.2</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E22" s="13" t="str">
         <f t="shared" si="4"/>
         <v>2.2.2.0</v>
       </c>
+      <c r="F22"/>
       <c r="G22" s="13" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H22" s="13">
         <v>40</v>
       </c>
-      <c r="I22" s="13" t="b">
+      <c r="I22" s="33" t="b">
         <f>'Site 1 (HUB)'!I22</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C23" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>172.16.0.52</v>
+        <v>172.16.50.2</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E23" s="15" t="str">
         <f t="shared" si="4"/>
@@ -4097,19 +5064,19 @@
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="H23" s="15">
         <v>50</v>
       </c>
-      <c r="I23" s="13" t="b">
+      <c r="I23" s="33" t="b">
         <f>'Site 1 (HUB)'!I23</f>
         <v>1</v>
       </c>
       <c r="J23" s="16"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>0</v>
       </c>
@@ -4126,196 +5093,369 @@
         <v>6</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25"/>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13">
-        <f>A2</f>
+        <f>$A$2</f>
         <v>2</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>14</v>
+      <c r="B26" s="13" t="str">
+        <f>$D$2</f>
+        <v>admin</v>
+      </c>
+      <c r="C26" s="13" t="str">
+        <f>$E$2</f>
+        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
+      </c>
+      <c r="D26" s="13" t="str">
+        <f>$F$2</f>
+        <v>0 - 4</v>
+      </c>
+      <c r="E26" s="13" t="str">
+        <f>$G$2</f>
+        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
       <c r="F26" s="13">
-        <v>2</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26" s="17"/>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="J28" s="14" t="s">
         <v>1</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="L28" s="30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="L28" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
-        <f>(ROW())-(ROW()-1)</f>
+        <f>ROW()-28</f>
         <v>1</v>
       </c>
       <c r="B29" s="7">
+        <f>$B$5</f>
         <v>10</v>
       </c>
       <c r="C29" s="7" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</f>
-        <v>10.12.0.2</v>
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</f>
+        <v>10.2.10.2</v>
       </c>
       <c r="D29" s="7" t="str">
         <f>$E$5</f>
-        <v>10.12.0.1</v>
+        <v>10.2.10.1</v>
       </c>
       <c r="E29" s="7" t="str">
         <f>$F$5</f>
-        <v>255.255.0.0</v>
+        <v>255.255.255.0</v>
       </c>
       <c r="F29" s="7">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G29" s="7">
         <v>0</v>
       </c>
       <c r="H29" s="10">
-        <v>3</v>
-      </c>
-      <c r="I29" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="J29" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K29" s="2">
         <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" ref="L29" si="6">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A29)</f>
-        <v>10.52.0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7">
-        <v>2</v>
-      </c>
-      <c r="B30" s="7">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7" t="str">
-        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A30)</f>
-        <v>10.12.0.3</v>
-      </c>
-      <c r="D30" s="7" t="str">
-        <f>$E$5</f>
-        <v>10.12.0.1</v>
-      </c>
-      <c r="E30" s="7" t="str">
-        <f>$F$5</f>
-        <v>255.255.0.0</v>
-      </c>
-      <c r="F30" s="7">
-        <v>24</v>
-      </c>
-      <c r="G30" s="7">
-        <v>0</v>
-      </c>
-      <c r="H30" s="7">
-        <v>3</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K30" s="2">
-        <f>IF($A30=1,F30-G30-H30*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F30-G30-(1+H30)*$F$26-1)</f>
-        <v>15</v>
-      </c>
-      <c r="L30" t="str">
-        <f t="shared" ref="L30" si="7">LEFT($G$9,LEN($G$9)-1)&amp;(RIGHT($G$9,1)+A30)</f>
-        <v>10.52.0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+        <f t="shared" ref="L29" si="6">10&amp;"."&amp;$A$2&amp;"."&amp;$B$9&amp;"."&amp;(A29+1)</f>
+        <v>10.2.50.2</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+    </row>
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+    </row>
+    <row r="33" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+    </row>
+    <row r="34" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+    </row>
+    <row r="35" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+    </row>
+    <row r="36" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
+    </row>
+    <row r="37" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+    </row>
+    <row r="38" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35"/>
+    </row>
+    <row r="39" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35"/>
+    </row>
+    <row r="40" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M40" s="35"/>
+      <c r="N40" s="35"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+    </row>
+    <row r="41" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="35"/>
+    </row>
+    <row r="42" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M42" s="35"/>
+      <c r="N42" s="35"/>
+      <c r="O42" s="35"/>
+      <c r="P42" s="35"/>
+      <c r="Q42" s="35"/>
+    </row>
+    <row r="43" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="35"/>
+    </row>
+    <row r="44" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
+    </row>
+    <row r="45" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M45" s="35"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
+    </row>
+    <row r="46" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+    </row>
+    <row r="47" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+    </row>
+    <row r="48" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M48" s="35"/>
+      <c r="N48" s="35"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="35"/>
+    </row>
+    <row r="49" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M49" s="35"/>
+      <c r="N49" s="35"/>
+      <c r="O49" s="35"/>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="35"/>
+    </row>
+    <row r="50" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M50" s="35"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="35"/>
+    </row>
+    <row r="51" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M51" s="35"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+    </row>
+    <row r="52" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+    </row>
+    <row r="53" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+    </row>
+    <row r="54" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="35"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+    </row>
+    <row r="55" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M55" s="35"/>
+      <c r="N55" s="35"/>
+      <c r="O55" s="35"/>
+      <c r="P55" s="35"/>
+      <c r="Q55" s="35"/>
+    </row>
+    <row r="56" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+    </row>
+    <row r="57" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
+      <c r="Q57" s="35"/>
+    </row>
+    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M58" s="35"/>
+      <c r="N58" s="35"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="35"/>
+      <c r="Q58" s="35"/>
+    </row>
+    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="35"/>
+      <c r="Q59" s="35"/>
+    </row>
+    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M60" s="35"/>
+      <c r="N60" s="35"/>
+      <c r="O60" s="35"/>
+      <c r="P60" s="35"/>
+      <c r="Q60" s="35"/>
+    </row>
+    <row r="61" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5251,15 +6391,33 @@
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29:I30" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="9">
+    <dataValidation type="list" sqref="G26" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{00000000-0002-0000-0100-000001000000}">
+      <formula1>"OFF,STRICT,LOOSE"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G26" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
+    <dataValidation type="list" sqref="M29:N60 S2 O2:P2" xr:uid="{00000000-0002-0000-0100-000003000000}">
+      <formula1>"OLD,NEW"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2" xr:uid="{00000000-0002-0000-0100-000002000000}">
-      <formula1>"OFF,STRICT,LOOSE"</formula1>
+    <dataValidation type="list" sqref="Q2 O29:O60" xr:uid="{00000000-0002-0000-0100-000004000000}">
+      <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="R2" xr:uid="{00000000-0002-0000-0100-000005000000}">
+      <formula1>"CLASSIC,NAMED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="T2" xr:uid="{00000000-0002-0000-0100-000006000000}">
+      <formula1>"IKEV1,IKEV2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="U2 P29:P60" xr:uid="{00000000-0002-0000-0100-000007000000}">
+      <formula1>"AUTO,5,8,9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="V2 Q29:Q60" xr:uid="{00000000-0002-0000-0100-000008000000}">
+      <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5276,7 +6434,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -5289,278 +6447,294 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>74</v>
+      <c r="A1" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="21">
+      <c r="A2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="20">
         <v>67</v>
       </c>
-      <c r="E2" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="21" t="s">
+      <c r="E2" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="20">
+        <v>67</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="20">
+        <v>53</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="20">
+        <v>53</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="20">
         <v>80</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="21">
+      <c r="E8" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="20">
+        <v>443</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="20">
         <v>67</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="H4" s="23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="21">
-        <v>53</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="21">
-        <v>53</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="21">
-        <v>80</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="23" t="s">
+      <c r="E10" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="21">
-        <v>443</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="23" t="s">
+      <c r="D12" s="20">
+        <v>67</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="21">
-        <v>67</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="21">
-        <v>67</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>76</v>
+      <c r="A13" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE23B823-7E55-4F59-B2C9-8E579AD40862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA5B63B-E193-4241-8F21-E15771FD22E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="132">
   <si>
     <t>site</t>
   </si>
@@ -3016,7 +3016,9 @@
       <c r="I26" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="J26" s="2"/>
+      <c r="J26" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="K26" s="2">
         <f>IF($A26=1,F26-G26-H26*$F$23-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="ERSPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</f>
         <v>21</v>
@@ -4950,7 +4952,7 @@
         <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
       <c r="F23" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="30" t="s">
@@ -5039,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>130</v>
@@ -5049,7 +5051,7 @@
       </c>
       <c r="K26" s="2">
         <f>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</f>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M26" s="31"/>
       <c r="N26" s="31"/>
@@ -5095,7 +5097,7 @@
       </c>
       <c r="K27" s="43">
         <f>IF($A27=1,F27-G27-H27*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F27-G27-(1+H27)*$F$23-1)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M27" s="31"/>
       <c r="N27" s="31"/>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA5B63B-E193-4241-8F21-E15771FD22E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FDC081-0AE7-480A-A5CE-BDBCEDF0E338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
-    <sheet name="Site 2" sheetId="2" r:id="rId2"/>
-    <sheet name="FLOW_POLICY" sheetId="3" r:id="rId3"/>
+    <sheet name="Site 2" sheetId="4" r:id="rId2"/>
+    <sheet name="Site 3" sheetId="2" r:id="rId3"/>
+    <sheet name="FLOW_POLICY" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="132">
   <si>
     <t>site</t>
   </si>
@@ -146,9 +147,6 @@
     <t>TACACS-KEY</t>
   </si>
   <si>
-    <t>192.168.255.1</t>
-  </si>
-  <si>
     <t>10.1.10.10</t>
   </si>
   <si>
@@ -453,6 +451,9 @@
   </si>
   <si>
     <t>20.2-30.2-40.2</t>
+  </si>
+  <si>
+    <t>8.8.8.8, 1.1.1.1</t>
   </si>
 </sst>
 </file>
@@ -631,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -749,30 +750,119 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="111">
-    <dxf>
-      <font>
-        <sz val="11"/>
+  <dxfs count="177">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -790,6 +880,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -845,6 +936,487 @@
       <font>
         <u val="none"/>
         <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -852,14 +1424,504 @@
     </dxf>
     <dxf>
       <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
         <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -909,487 +1971,6 @@
     <dxf>
       <font>
         <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
     </dxf>
     <dxf>
@@ -1720,71 +2301,231 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="110"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ISP-VLAN" dataDxfId="109"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="107"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="106"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="tacacs_server_ip" dataDxfId="105"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="syslog_server_ip" dataDxfId="104"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="urpf_mode" dataDxfId="103"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="radius_server_ip" dataDxfId="102"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="radius_key" dataDxfId="101"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="dmvpn_phase" dataDxfId="100"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="tacacs_syntax" dataDxfId="99"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="radius_syntax" dataDxfId="98"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="dot1x_syntax" dataDxfId="97"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="eigrp_syntax" dataDxfId="96"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="vrf_syntax" dataDxfId="95"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ike_version" dataDxfId="94"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="secret_type" dataDxfId="93"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="trunk_encapsulation" dataDxfId="92"/>
-    <tableColumn id="26" xr3:uid="{7A70CB3D-3E69-4511-AFC7-833193219BEB}" name="snmpv3_enabled" dataDxfId="91"/>
-    <tableColumn id="27" xr3:uid="{209B66CE-CA9A-4100-AF1F-D365CF1FFE1D}" name="snmp_server_ip" dataDxfId="90"/>
-    <tableColumn id="28" xr3:uid="{35546B6C-3A4D-4CB1-960A-7557AC2139AF}" name="snmp_user" dataDxfId="89"/>
-    <tableColumn id="29" xr3:uid="{EEE156DA-8F56-4FDB-B5BD-E05593FB26D6}" name="snmp_auth_password" dataDxfId="88"/>
-    <tableColumn id="30" xr3:uid="{C5D4501A-8EFA-4918-A4F1-64D389B519DA}" name="snmp_priv_password" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="176"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ISP-VLAN" dataDxfId="175"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="174"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="173"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="172"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="tacacs_server_ip" dataDxfId="171"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="syslog_server_ip" dataDxfId="170"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="urpf_mode" dataDxfId="169"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="radius_server_ip" dataDxfId="168"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="radius_key" dataDxfId="167"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="dmvpn_phase" dataDxfId="166"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="tacacs_syntax" dataDxfId="165"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="radius_syntax" dataDxfId="164"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="dot1x_syntax" dataDxfId="163"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="eigrp_syntax" dataDxfId="162"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="vrf_syntax" dataDxfId="161"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ike_version" dataDxfId="160"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="secret_type" dataDxfId="159"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="trunk_encapsulation" dataDxfId="158"/>
+    <tableColumn id="26" xr3:uid="{7A70CB3D-3E69-4511-AFC7-833193219BEB}" name="snmpv3_enabled" dataDxfId="157"/>
+    <tableColumn id="27" xr3:uid="{209B66CE-CA9A-4100-AF1F-D365CF1FFE1D}" name="snmp_server_ip" dataDxfId="156"/>
+    <tableColumn id="28" xr3:uid="{35546B6C-3A4D-4CB1-960A-7557AC2139AF}" name="snmp_user" dataDxfId="155"/>
+    <tableColumn id="29" xr3:uid="{EEE156DA-8F56-4FDB-B5BD-E05593FB26D6}" name="snmp_auth_password" dataDxfId="154"/>
+    <tableColumn id="30" xr3:uid="{C5D4501A-8EFA-4918-A4F1-64D389B519DA}" name="snmp_priv_password" dataDxfId="153"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A25:Q27" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D32D18C4-0B05-425E-B28E-67E8EEF86C01}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A25:Q27" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{3D2619F9-8A27-48B4-BBAD-F8DAD24B7058}" name="SW" dataDxfId="28">
       <calculatedColumnFormula>ROW()-25</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="21">
-      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{79D48293-3CC1-4FC8-B959-C76EC31AF05A}" name="MGMT Vlan" dataDxfId="27">
+      <calculatedColumnFormula>$B$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="20">
+    <tableColumn id="3" xr3:uid="{636012CC-2311-45D4-B0A3-CBE1DDB288EA}" name="MGMT ip" dataDxfId="26">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A26+1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{57B036DD-2EC2-46AB-BA82-15C2E4251EE3}" name="gateway" dataDxfId="25">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="19">
+    <tableColumn id="5" xr3:uid="{6D16308A-64E5-4F82-9997-B8BD8FE03B86}" name="mask" dataDxfId="24">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="14">
+    <tableColumn id="10" xr3:uid="{10263F16-185C-4388-8A92-6BC4CA0E07C5}" name="num_ports_tot" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{337036FB-EC4A-4A8B-A2D4-886EF58ACF98}" name="skiped_ports" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{75ED65B8-97AC-498A-9CF3-0A234BF7E9F1}" name="num_downlink" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{D2EB23FE-1E37-4D17-B4EC-11CAC9B6F0DC}" name="vlan-antall" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{0815D94A-1C82-4867-98BC-98ABBA28ECDE}" name="intf_prefix" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{CDF41783-F241-44AB-837D-97EDFE6911D4}" name="num_port_ledig" dataDxfId="18">
       <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="MONITORING ip"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0900-00000D000000}" name="tacacs_syntax"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="radius_syntax"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="dot1x_syntax"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0900-000010000000}" name="secret_type"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0900-000011000000}" name="trunk_encapsulation"/>
+    <tableColumn id="12" xr3:uid="{AACD1EB8-91AF-4962-8481-F05F6073247E}" name="MONITORING ip"/>
+    <tableColumn id="13" xr3:uid="{7E243D0A-E644-41FD-A148-B1875C00196D}" name="tacacs_syntax"/>
+    <tableColumn id="14" xr3:uid="{DBC0EF9C-754A-4F1A-AD0C-3A999D538347}" name="radius_syntax"/>
+    <tableColumn id="15" xr3:uid="{73F5C42E-D3FF-4AEB-8766-FB4C6E26C2E1}" name="dot1x_syntax"/>
+    <tableColumn id="16" xr3:uid="{3DF3E91F-29DF-42B7-8BE4-9457278406A4}" name="secret_type"/>
+    <tableColumn id="17" xr3:uid="{2CFEA8EA-3D50-4B84-A069-434F906C1876}" name="trunk_encapsulation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{0B8E17A8-D111-4A2F-8101-D45B05AD0BB5}" name="Tabell6214" displayName="Tabell6214" ref="A4:K8">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{CC1AA328-A218-4F84-A0AF-9F021BDC546B}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{B69DA7F6-D441-4D1F-9BD5-0FFD34DC7968}" name="vlan"/>
+    <tableColumn id="3" xr3:uid="{F6DCB80F-2B53-40DA-A53C-9EEF0E850482}" name="interface"/>
+    <tableColumn id="4" xr3:uid="{8DBFFE92-3B45-4122-819E-272FF8FEED1E}" name="nett id">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".0"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{1A76ECB4-477D-43BD-933D-CA839E86FEE1}" name="gateway">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{643E4998-713D-4F39-993A-B5B110F8184B}" name="mask"/>
+    <tableColumn id="7" xr3:uid="{9403EEA1-4392-41BF-9502-87C3A1CF28BE}" name="address min">
+      <calculatedColumnFormula>VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{09FF5408-B542-4803-BB81-19C6D96455ED}" name="address max">
+      <calculatedColumnFormula>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{1C2CE40E-C587-4306-B04C-05E7E830B912}" name="antall-res" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{062A0975-F29C-4725-993D-1C745C38968F}" name="pri-afxx"/>
+    <tableColumn id="11" xr3:uid="{E9F272DB-833F-4003-8FE1-C3489DCBD223}" name="pri-1-10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{137249B9-B569-4AB4-A5F4-44E14EC73E12}" name="Tabell7715" displayName="Tabell7715" ref="A10:C14">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3A3EB178-6BB6-4F25-BFF2-BC4D427D60C7}" name="vrf"/>
+    <tableColumn id="3" xr3:uid="{00063F96-3CCE-4FBF-AEA1-0FEA482EE82B}" name="loopback"/>
+    <tableColumn id="4" xr3:uid="{068346AF-14A6-4C4B-94E5-C3159DB837E3}" name="laddr">
+      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B11</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:AA2" dataDxfId="125">
+  <tableColumns count="27">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="124"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="123"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="122"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="121"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="120"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="119"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="118"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="117">
+      <calculatedColumnFormula>'Site 1 (HUB)'!I2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="116"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="115">
+      <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="114">
+      <calculatedColumnFormula>'Site 1 (HUB)'!M2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="urpf_mode" dataDxfId="113"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="radius_server_ip" dataDxfId="112"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="radius_key" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="tacacs_syntax" dataDxfId="110"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" name="radius_syntax" dataDxfId="109"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" name="dot1x_syntax" dataDxfId="108"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" name="eigrp_syntax" dataDxfId="107"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" name="vrf_syntax" dataDxfId="106"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" name="ike_version" dataDxfId="105"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" name="secret_type" dataDxfId="104"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" name="trunk_encapsulation" dataDxfId="103"/>
+    <tableColumn id="23" xr3:uid="{96BFD35F-5B86-4563-AD71-9BEE692F259E}" name="snmpv3_enabled" dataDxfId="102"/>
+    <tableColumn id="24" xr3:uid="{B32071E9-38D7-497D-8D05-9C277245ED7D}" name="snmp_server_ip" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{A51FD30E-2A50-4B3C-B10C-DC9965677024}" name="snmp_user" dataDxfId="100"/>
+    <tableColumn id="26" xr3:uid="{E35869A0-05B2-4390-88E0-3DB67D32BD41}" name="snmp_auth_password" dataDxfId="99"/>
+    <tableColumn id="27" xr3:uid="{962D48F4-6B6F-4976-A32F-AFCF203A4E6E}" name="snmp_priv_password" dataDxfId="98"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A16:J20" dataDxfId="97">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="94">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="92">
+      <calculatedColumnFormula>$C$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="91"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="90"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="89"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="87"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A22:H23" dataDxfId="86">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="85">
+      <calculatedColumnFormula>A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="dot1x_vlans" dataDxfId="78"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A25:Q26" totalsRowShown="0" dataDxfId="0">
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="16">
+      <calculatedColumnFormula>ROW()-25</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="15">
+      <calculatedColumnFormula>$B$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="14">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A26+1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="13">
+      <calculatedColumnFormula>$E$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="12">
+      <calculatedColumnFormula>$F$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="6">
+      <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="MONITORING ip"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0900-00000D000000}" name="tacacs_syntax" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="radius_syntax" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="dot1x_syntax" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0900-000010000000}" name="secret_type" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0900-000011000000}" name="trunk_encapsulation" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabell62" displayName="Tabell62" ref="A4:K8">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="vrf"/>
@@ -1801,7 +2542,7 @@
       <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="77"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1809,7 +2550,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell77" displayName="Tabell77" ref="A10:C14">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="vrf"/>
@@ -1822,7 +2563,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="FlowPolicyTable" displayName="FlowPolicyTable" ref="A1:E13" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="source"/>
@@ -1841,13 +2582,13 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="interface"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="86">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="152">
       <calculatedColumnFormula>10&amp;"."&amp;($A$2)&amp;"."&amp;$B5&amp;"."&amp;0</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="gateway"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="85">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="151">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
 _xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
@@ -1855,7 +2596,7 @@
 _xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="150"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -1881,11 +2622,11 @@
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="tunnel id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="vrf"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address" dataDxfId="83">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address" dataDxfId="149">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;$H17&amp;"."&amp;($A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="82">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="148">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -1899,19 +2640,19 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A22:I23" dataDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A22:I23" dataDxfId="147">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="80">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="146">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="75"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="72">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="145"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="144"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="142"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="141"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="140"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="139"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="138">
       <calculatedColumnFormula array="1">Tabell5[ISP-VLAN]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1922,28 +2663,28 @@
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A25:Q26" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="137">
       <calculatedColumnFormula>ROW()-25</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="136"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="135">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="134">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="133">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="132"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="131"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="130"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="129"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="128"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="127">
       <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="ERSPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="126"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="tacacs_syntax"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="radius_syntax"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="dot1x_syntax"/>
@@ -1955,81 +2696,97 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:AA2" dataDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51BF1746-4E83-4B5C-8E47-1B33E5F0C823}" name="Tabell18" displayName="Tabell18" ref="A1:AA2" dataDxfId="76">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="63">
+    <tableColumn id="1" xr3:uid="{F301071E-AB49-411D-B862-3D5F1A8652F4}" name="site" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{28087ADC-D839-428A-B3B6-5D33053FC989}" name="intf_prefix" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{E07A6BD4-5C25-4907-8DBF-B7CD7A55F1D8}" name="router-id" dataDxfId="73">
+      <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{E5D534F2-DADF-4E06-844E-EFC868A109BF}" name="brukernavn" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{8E37AE50-BD24-4C9E-97D1-6B548927DBB7}" name="passord" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{0A3407AA-8EBE-4074-85F9-778319C50E4E}" name="vty_lines" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{0E482BA6-C79D-40DB-B45E-FDC671702D74}" name="secret" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{C39694E5-0D09-45FB-A48D-8E9A8C91CA0E}" name="tacacs_key" dataDxfId="68">
       <calculatedColumnFormula>'Site 1 (HUB)'!I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="61">
+    <tableColumn id="9" xr3:uid="{44EB3B31-5D13-48ED-A202-643DB3DE780D}" name="dns_servers" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{97E12567-6CA3-4115-A196-2529D7160615}" name="tacacs_server_ip" dataDxfId="66">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="60">
+    <tableColumn id="11" xr3:uid="{0346B8E5-A202-466C-AB4B-67EDD69B81A1}" name="syslog_server_ip" dataDxfId="65">
       <calculatedColumnFormula>'Site 1 (HUB)'!M2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="urpf_mode" dataDxfId="59"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="radius_server_ip" dataDxfId="58"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="radius_key" dataDxfId="57"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="tacacs_syntax" dataDxfId="56"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" name="radius_syntax" dataDxfId="55"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" name="dot1x_syntax" dataDxfId="54"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" name="eigrp_syntax" dataDxfId="53"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" name="vrf_syntax" dataDxfId="52"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" name="ike_version" dataDxfId="51"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" name="secret_type" dataDxfId="50"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" name="trunk_encapsulation" dataDxfId="49"/>
-    <tableColumn id="23" xr3:uid="{96BFD35F-5B86-4563-AD71-9BEE692F259E}" name="snmpv3_enabled" dataDxfId="48"/>
-    <tableColumn id="24" xr3:uid="{B32071E9-38D7-497D-8D05-9C277245ED7D}" name="snmp_server_ip" dataDxfId="47"/>
-    <tableColumn id="25" xr3:uid="{A51FD30E-2A50-4B3C-B10C-DC9965677024}" name="snmp_user" dataDxfId="46"/>
-    <tableColumn id="26" xr3:uid="{E35869A0-05B2-4390-88E0-3DB67D32BD41}" name="snmp_auth_password" dataDxfId="45"/>
-    <tableColumn id="27" xr3:uid="{962D48F4-6B6F-4976-A32F-AFCF203A4E6E}" name="snmp_priv_password" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{EE86801E-B0D0-4B58-832A-86AC77A7EC9A}" name="urpf_mode" dataDxfId="64"/>
+    <tableColumn id="14" xr3:uid="{5AAC65E5-8130-4C09-99B3-54C834DEE5C1}" name="radius_server_ip" dataDxfId="63">
+      <calculatedColumnFormula>'Site 1 (HUB)'!O2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{1C900422-8FD8-4B49-B19A-47F4CE877466}" name="radius_key" dataDxfId="62">
+      <calculatedColumnFormula>'Site 1 (HUB)'!P2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{AD662EC0-7940-4F3A-8F56-38E0BAEE7E2B}" name="tacacs_syntax" dataDxfId="61"/>
+    <tableColumn id="16" xr3:uid="{103CB279-D718-4AF9-A977-B976A8B36356}" name="radius_syntax" dataDxfId="60"/>
+    <tableColumn id="17" xr3:uid="{3496AD74-0539-4463-997F-A1CA64512F54}" name="dot1x_syntax" dataDxfId="59"/>
+    <tableColumn id="18" xr3:uid="{F8B1DCD1-84B0-4090-BDAB-AD6FA5328F3C}" name="eigrp_syntax" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{E8281F74-01EE-4CFD-8DF1-C429390E1E04}" name="vrf_syntax" dataDxfId="57"/>
+    <tableColumn id="20" xr3:uid="{9FA158AF-3041-42DD-9BB3-CA83FCDE6CA1}" name="ike_version" dataDxfId="56"/>
+    <tableColumn id="21" xr3:uid="{045B3C14-6117-44CA-9A5A-D8BA1860F47E}" name="secret_type" dataDxfId="55"/>
+    <tableColumn id="22" xr3:uid="{3829C8E8-1959-4691-AF37-5B45456BC812}" name="trunk_encapsulation" dataDxfId="54"/>
+    <tableColumn id="23" xr3:uid="{4CE3B16C-67F6-4DC2-9BB2-F8E09C5C8D74}" name="snmpv3_enabled" dataDxfId="53"/>
+    <tableColumn id="24" xr3:uid="{7E57634C-C61D-454F-83A9-CCC1D7A3E9A7}" name="snmp_server_ip" dataDxfId="52"/>
+    <tableColumn id="25" xr3:uid="{DA892339-1F60-44AE-B105-D466545319B6}" name="snmp_user" dataDxfId="51"/>
+    <tableColumn id="26" xr3:uid="{10EE6F10-8503-4A58-9CA0-8FB438354050}" name="snmp_auth_password" dataDxfId="50"/>
+    <tableColumn id="27" xr3:uid="{66121011-59AB-4D41-BDF5-22B7624358BE}" name="snmp_priv_password" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A16:J20" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A99B9E14-0F60-413C-83C8-281F7E727FAD}" name="Tabell49" displayName="Tabell49" ref="A16:J20" dataDxfId="48">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="40">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{C939C381-1121-4153-B4EA-3E9AC4EFD622}" name="tunnel id" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{402267D7-3F42-4106-963C-A00D2C73C6A3}" name="vrf" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{4204F352-886B-4432-BF55-0DB72CCEC230}" name="ip address" dataDxfId="45">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;H17&amp;"."&amp;$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="38">
+    <tableColumn id="4" xr3:uid="{E652E851-68C8-44CC-A804-D4A898A26E6B}" name="mask" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{1B6660E8-062A-4243-A879-B9BBE79D61B2}" name="source" dataDxfId="43">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="37"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="35"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="34"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{31E83213-6808-4B06-B3A2-334B8AEA93A6}" name="destination" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{548BE719-FE15-47C2-BD8C-E15155610E6F}" name="gre mode" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{AC2699E3-BB2E-4992-9A64-D04428D784DC}" name="network-id" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{911A5F49-374E-494E-9F87-E559E2AEA74A}" name="ipsec" dataDxfId="39">
+      <calculatedColumnFormula>'Site 1 (HUB)'!I17</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{F9EF835F-35E0-4DBE-9B12-F79414F650B4}" name="ipsec key" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A22:H23" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DA31B441-D218-45B2-B01A-A4BBC8BD7979}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A22:H23" dataDxfId="37">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="31">
-      <calculatedColumnFormula>A2</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{F434D49E-3876-49A2-911F-716DB0E46944}" name="site" dataDxfId="36">
+      <calculatedColumnFormula>$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="dot1x_vlans" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{96C6D5FD-CBC3-49D8-AFD4-9E1E09633C5A}" name="brukernavn" dataDxfId="35">
+      <calculatedColumnFormula>$D$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{038EE345-4494-4999-88D7-0BF36304D24C}" name="passord" dataDxfId="34">
+      <calculatedColumnFormula>$E$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{770D33D1-BE1F-45C0-8F6C-2E9C2A15365F}" name="vty_lines" dataDxfId="33">
+      <calculatedColumnFormula>$F$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{87FFB71D-3185-4317-BD65-911279FF4E36}" name="secret" dataDxfId="32">
+      <calculatedColumnFormula>$G$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{13F65231-00AD-4279-9566-BCCC6B905C94}" name="etherchan_num" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{32F614C6-376B-4371-8715-7B2614BB4DBC}" name="span_mode" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{70D4C587-3B90-40C4-BB6C-9CC884BED451}" name="dot1x_vlans" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2329,19 +3086,19 @@
         <v>24</v>
       </c>
       <c r="Z1" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA1" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="AA1" s="36" t="s">
+      <c r="AB1" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="AB1" s="36" t="s">
+      <c r="AC1" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="AC1" s="36" t="s">
+      <c r="AD1" s="36" t="s">
         <v>119</v>
-      </c>
-      <c r="AD1" s="36" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2362,7 +3119,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>27</v>
@@ -2377,64 +3134,64 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L2" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="19" t="s">
+      <c r="O2" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="Q2" s="19">
         <v>3</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="Y2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z2" s="37" t="b">
         <v>1</v>
       </c>
       <c r="AA2" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB2" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC2" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="AC2" s="38" t="s">
+      <c r="AD2" s="38" t="s">
         <v>122</v>
-      </c>
-      <c r="AD2" s="38" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2451,42 +3208,42 @@
     </row>
     <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="K4" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="K4" s="27" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="8">
         <v>10</v>
@@ -2503,7 +3260,7 @@
         <v>10.1.10.1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" s="7" t="str" cm="1">
         <f>VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
@@ -2525,7 +3282,7 @@
     </row>
     <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="8">
         <v>20</v>
@@ -2542,7 +3299,7 @@
         <v>10.1.20.1</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" ref="G6:G7" si="1">VALUE(LEFT(D6,FIND(".",D6)-1))&amp;"."&amp;VALUE(MID(D6,FIND(".",D6)+1,FIND(".",D6,FIND(".",D6)+1)-FIND(".",D6)-1))&amp;"."&amp;VALUE(MID(D6,FIND(".",D6,FIND(".",D6)+1)+1,FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)-FIND(".",D6,FIND(".",D6)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D6,LEN(D6)-FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)))+1)</f>
@@ -2564,7 +3321,7 @@
     </row>
     <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="8">
         <v>30</v>
@@ -2581,7 +3338,7 @@
         <v>10.1.30.1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="1"/>
@@ -2603,7 +3360,7 @@
     </row>
     <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="8">
         <v>40</v>
@@ -2620,7 +3377,7 @@
         <v>10.1.40.1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="7" t="str">
         <f t="shared" ref="G8" si="3">VALUE(LEFT(D8,FIND(".",D8)-1))&amp;"."&amp;VALUE(MID(D8,FIND(".",D8)+1,FIND(".",D8,FIND(".",D8)+1)-FIND(".",D8)-1))&amp;"."&amp;VALUE(MID(D8,FIND(".",D8,FIND(".",D8)+1)+1,FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)-FIND(".",D8,FIND(".",D8)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D8,LEN(D8)-FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)))+1)</f>
@@ -2646,18 +3403,18 @@
     </row>
     <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="7">
         <v>10</v>
@@ -2669,7 +3426,7 @@
     </row>
     <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="7">
         <v>20</v>
@@ -2681,7 +3438,7 @@
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7">
         <v>30</v>
@@ -2693,7 +3450,7 @@
     </row>
     <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7">
         <v>40</v>
@@ -2706,49 +3463,49 @@
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="H16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C17" s="7" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H17&amp;"."&amp;$A$2</f>
         <v>172.16.10.1</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E17" s="7" t="str">
         <f>$C$2</f>
@@ -2756,7 +3513,7 @@
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H17" s="2">
         <v>10</v>
@@ -2768,17 +3525,17 @@
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="7" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H18&amp;"."&amp;$A$2</f>
         <v>172.16.20.1</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" s="7" t="str">
         <f>$C$2</f>
@@ -2786,7 +3543,7 @@
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H18" s="2">
         <v>20</v>
@@ -2798,17 +3555,17 @@
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="7" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
         <v>172.16.30.1</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="7" t="str">
         <f>$C$2</f>
@@ -2816,7 +3573,7 @@
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H19" s="2">
         <v>30</v>
@@ -2828,17 +3585,17 @@
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="7" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
         <v>172.16.40.1</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" s="7" t="str">
         <f>$C$2</f>
@@ -2846,7 +3603,7 @@
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H20" s="2">
         <v>40</v>
@@ -2882,13 +3639,13 @@
         <v>6</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>7</v>
@@ -2919,10 +3676,10 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="44" t="s">
-        <v>129</v>
+        <v>125</v>
+      </c>
+      <c r="H23" s="42" t="s">
+        <v>128</v>
       </c>
       <c r="I23" s="35" cm="1">
         <f t="array" ref="I23">Tabell5[ISP-VLAN]</f>
@@ -2932,40 +3689,40 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="C25" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="13" t="s">
+      <c r="G25" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="H25" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="I25" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="J25" s="13" t="s">
         <v>1</v>
       </c>
       <c r="K25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L25" s="25" t="s">
         <v>82</v>
-      </c>
-      <c r="L25" s="25" t="s">
-        <v>83</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>17</v>
@@ -3014,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>25</v>
@@ -4236,7 +4993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B45EDC77-8BBB-4908-955E-B9316A6BE4D3}">
   <dimension ref="A1:AA995"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4331,19 +5088,19 @@
         <v>24</v>
       </c>
       <c r="W1" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="X1" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="X1" s="33" t="s">
+      <c r="Y1" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="Y1" s="33" t="s">
+      <c r="Z1" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="Z1" s="33" t="s">
+      <c r="AA1" s="33" t="s">
         <v>119</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4364,7 +5121,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>27</v>
@@ -4374,7 +5131,7 @@
         <v>TACACS-KEY</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="J2" s="14" t="str">
         <f>'Site 1 (HUB)'!L2</f>
@@ -4385,7 +5142,7 @@
         <v>10.1.10.10</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M2" s="30" t="str">
         <f>'Site 1 (HUB)'!O2</f>
@@ -4396,84 +5153,84 @@
         <v>RADIUS-KEY</v>
       </c>
       <c r="O2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="34" t="s">
+      <c r="R2" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="34" t="s">
+      <c r="S2" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="34" t="s">
+      <c r="T2" s="34" t="s">
         <v>36</v>
-      </c>
-      <c r="T2" s="34" t="s">
-        <v>37</v>
       </c>
       <c r="U2" s="34">
         <v>9</v>
       </c>
       <c r="V2" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W2" s="39" t="b">
         <v>1</v>
       </c>
       <c r="X2" s="40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z2" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="Z2" s="40" t="s">
+      <c r="AA2" s="40" t="s">
         <v>122</v>
-      </c>
-      <c r="AA2" s="40" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="J4" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="K4" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="K4" s="27" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="8">
         <v>10</v>
@@ -4490,7 +5247,7 @@
         <v>10.2.10.1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" s="7" t="str">
         <f t="shared" ref="G5:G8" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
@@ -4512,7 +5269,7 @@
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="8">
         <v>20</v>
@@ -4529,7 +5286,7 @@
         <v>10.2.20.1</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4551,7 +5308,7 @@
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="8">
         <v>30</v>
@@ -4568,7 +5325,7 @@
         <v>10.2.30.1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4590,7 +5347,7 @@
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="8">
         <v>40</v>
@@ -4607,7 +5364,7 @@
         <v>10.2.40.1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="7" t="str">
         <f t="shared" si="0"/>
@@ -4644,13 +5401,13 @@
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -4664,7 +5421,7 @@
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="7">
         <v>10</v>
@@ -4685,7 +5442,7 @@
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="7">
         <v>20</v>
@@ -4706,7 +5463,7 @@
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="7">
         <v>30</v>
@@ -4727,7 +5484,7 @@
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7">
         <v>40</v>
@@ -4749,49 +5506,49 @@
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="12" t="s">
+      <c r="F16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="G16" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="H16" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="I16" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="J16" s="12" t="s">
         <v>64</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C17" s="12" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H17&amp;"."&amp;$A$2</f>
         <v>172.16.10.2</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E17" s="12" t="str">
         <f t="shared" ref="E17:E20" si="4">$C$2</f>
@@ -4799,7 +5556,7 @@
       </c>
       <c r="F17"/>
       <c r="G17" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H17" s="12">
         <v>10</v>
@@ -4812,17 +5569,17 @@
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="12" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H18&amp;"."&amp;$A$2</f>
         <v>172.16.20.2</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" s="12" t="str">
         <f t="shared" si="4"/>
@@ -4830,7 +5587,7 @@
       </c>
       <c r="F18"/>
       <c r="G18" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H18" s="12">
         <v>20</v>
@@ -4843,17 +5600,17 @@
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="12" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
         <v>172.16.30.2</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="12" t="str">
         <f t="shared" si="4"/>
@@ -4861,7 +5618,7 @@
       </c>
       <c r="F19"/>
       <c r="G19" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H19" s="12">
         <v>30</v>
@@ -4874,17 +5631,17 @@
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="12" t="str">
         <f t="shared" ref="C20" si="5">172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
         <v>172.16.40.2</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" s="12" t="str">
         <f t="shared" si="4"/>
@@ -4892,7 +5649,7 @@
       </c>
       <c r="F20"/>
       <c r="G20" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H20" s="12">
         <v>40</v>
@@ -4921,13 +5678,13 @@
         <v>6</v>
       </c>
       <c r="F22" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4956,46 +5713,46 @@
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="C25" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="13" t="s">
+      <c r="G25" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="H25" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="I25" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="J25" s="13" t="s">
         <v>1</v>
       </c>
       <c r="K25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L25" s="25" t="s">
         <v>82</v>
-      </c>
-      <c r="L25" s="25" t="s">
-        <v>83</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>17</v>
@@ -5044,10 +5801,10 @@
         <v>1</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K26" s="2">
         <f>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</f>
@@ -5068,11 +5825,11 @@
         <f>$B$5</f>
         <v>10</v>
       </c>
-      <c r="C27" s="41" t="str">
+      <c r="C27" s="7" t="str">
         <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A27+1)</f>
         <v>10.2.10.3</v>
       </c>
-      <c r="D27" s="41" t="str">
+      <c r="D27" s="7" t="str">
         <f>$E$5</f>
         <v>10.2.10.1</v>
       </c>
@@ -5089,13 +5846,13 @@
       <c r="H27" s="7">
         <v>0</v>
       </c>
-      <c r="I27" s="42" t="s">
-        <v>131</v>
+      <c r="I27" s="41" t="s">
+        <v>130</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K27" s="43">
+      <c r="K27" s="2">
         <f>IF($A27=1,F27-G27-H27*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F27-G27-(1+H27)*$F$23-1)</f>
         <v>7</v>
       </c>
@@ -6255,32 +7012,32 @@
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" sqref="G23" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
+    <dataValidation type="list" sqref="V2 Q26:Q57" xr:uid="{39D8B1B3-368B-4AC5-A514-11645F40D89B}">
+      <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="U2 P26:P57" xr:uid="{40E87254-C5D0-4454-8C47-5100945ED78A}">
+      <formula1>"AUTO,5,8,9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="T2" xr:uid="{D82DFD41-8835-4B4F-94E1-F31DD76B81DE}">
+      <formula1>"IKEV1,IKEV2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="R2" xr:uid="{F047568E-0FF5-4EA3-A7BF-468F3B62A5DC}">
+      <formula1>"CLASSIC,NAMED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="Q2 O26:O57" xr:uid="{8398B055-E1AD-474F-AA4B-7C530D80F4B4}">
+      <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="O2:P2 S2 M26:N57" xr:uid="{3BA14544-E617-4EAB-8056-F1ADFAEBFA4A}">
+      <formula1>"OLD,NEW"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26:I27" xr:uid="{5FB8B7A2-FDEC-49C6-A037-9F36974649E1}">
+      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{1CFE3BAF-8D34-4CA8-BE94-49E44A9437C4}">
       <formula1>"OFF,STRICT,LOOSE"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26:I27" xr:uid="{6050EE6B-A0D6-483D-B963-EC3B425AE0E5}">
-      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="O2:P2 S2 M26:N57" xr:uid="{00000000-0002-0000-0100-000003000000}">
-      <formula1>"OLD,NEW"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="Q2 O26:O57" xr:uid="{00000000-0002-0000-0100-000004000000}">
-      <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="R2" xr:uid="{00000000-0002-0000-0100-000005000000}">
-      <formula1>"CLASSIC,NAMED"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="T2" xr:uid="{00000000-0002-0000-0100-000006000000}">
-      <formula1>"IKEV1,IKEV2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="U2 P26:P57" xr:uid="{00000000-0002-0000-0100-000007000000}">
-      <formula1>"AUTO,5,8,9"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="V2 Q26:Q57" xr:uid="{00000000-0002-0000-0100-000008000000}">
-      <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
+    <dataValidation type="list" sqref="G23" xr:uid="{194DE05B-70E4-4CED-BEE9-B1A159236E6A}">
+      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6296,6 +7053,2020 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AA994"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.44140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="75.88671875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="75.88671875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="75.88671875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="12" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" style="12" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" style="12" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="13" max="14" width="18" style="12" customWidth="1"/>
+    <col min="15" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="19.5546875" customWidth="1"/>
+    <col min="18" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.109375" style="12" customWidth="1"/>
+    <col min="24" max="24" width="13.44140625" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="27" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="X1" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y1" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z1" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA1" s="33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>3</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="12" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="12" t="str">
+        <f>'Site 1 (HUB)'!I2</f>
+        <v>TACACS-KEY</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="J2" s="14" t="str">
+        <f>'Site 1 (HUB)'!L2</f>
+        <v>10.1.10.10</v>
+      </c>
+      <c r="K2" s="14" t="str">
+        <f>'Site 1 (HUB)'!M2</f>
+        <v>10.1.10.10</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="30" t="str">
+        <f>'Site 1 (HUB)'!O2</f>
+        <v>10.1.10.10</v>
+      </c>
+      <c r="N2" s="30" t="str">
+        <f>'Site 1 (HUB)'!P2</f>
+        <v>RADIUS-KEY</v>
+      </c>
+      <c r="O2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="34">
+        <v>9</v>
+      </c>
+      <c r="V2" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z2" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA2" s="40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="8">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".0"</f>
+        <v>10.3.10.0</v>
+      </c>
+      <c r="E5" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".1"</f>
+        <v>10.3.10.1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <f t="shared" ref="G5:G8" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
+        <v>10.3.10.1</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</f>
+        <v>10.3.10.254</v>
+      </c>
+      <c r="I5" s="7">
+        <v>40</v>
+      </c>
+      <c r="J5" s="9">
+        <v>21</v>
+      </c>
+      <c r="K5" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="8">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <f t="shared" ref="D6:D8" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
+        <v>10.3.20.0</v>
+      </c>
+      <c r="E6" s="7" t="str">
+        <f t="shared" ref="E6:E8" si="2">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
+        <v>10.3.20.1</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.3.20.1</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f>(VALUE(LEFT(D6,FIND(".",D6)-1))+255-VALUE(LEFT(F6,FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6)+1,FIND(".",D6,FIND(".",D6)+1)-FIND(".",D6)-1))+255-VALUE(MID(F6,FIND(".",F6)+1,FIND(".",F6,FIND(".",F6)+1)-FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6,FIND(".",D6)+1)+1,FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)-FIND(".",D6,FIND(".",D6)+1)-1))+255-VALUE(MID(F6,FIND(".",F6,FIND(".",F6)+1)+1,FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)-FIND(".",F6,FIND(".",F6)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D6,LEN(D6)-FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)))+255-VALUE(RIGHT(F6,LEN(F6)-FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)))-1)</f>
+        <v>10.3.20.254</v>
+      </c>
+      <c r="I6" s="7">
+        <v>40</v>
+      </c>
+      <c r="J6" s="9">
+        <v>11</v>
+      </c>
+      <c r="K6" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="8">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>10.3.30.0</v>
+      </c>
+      <c r="E7" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>10.3.30.1</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.3.30.1</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f>(VALUE(LEFT(D7,FIND(".",D7)-1))+255-VALUE(LEFT(F7,FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7)+1,FIND(".",D7,FIND(".",D7)+1)-FIND(".",D7)-1))+255-VALUE(MID(F7,FIND(".",F7)+1,FIND(".",F7,FIND(".",F7)+1)-FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7,FIND(".",D7)+1)+1,FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)-FIND(".",D7,FIND(".",D7)+1)-1))+255-VALUE(MID(F7,FIND(".",F7,FIND(".",F7)+1)+1,FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)-FIND(".",F7,FIND(".",F7)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D7,LEN(D7)-FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)))+255-VALUE(RIGHT(F7,LEN(F7)-FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)))-1)</f>
+        <v>10.3.30.254</v>
+      </c>
+      <c r="I7" s="7">
+        <v>40</v>
+      </c>
+      <c r="J7">
+        <v>42</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="8">
+        <v>40</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>10.3.40.0</v>
+      </c>
+      <c r="E8" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>10.3.40.1</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.3.40.1</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f>(VALUE(LEFT(D8,FIND(".",D8)-1))+255-VALUE(LEFT(F8,FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8)+1,FIND(".",D8,FIND(".",D8)+1)-FIND(".",D8)-1))+255-VALUE(MID(F8,FIND(".",F8)+1,FIND(".",F8,FIND(".",F8)+1)-FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8,FIND(".",D8)+1)+1,FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)-FIND(".",D8,FIND(".",D8)+1)-1))+255-VALUE(MID(F8,FIND(".",F8,FIND(".",F8)+1)+1,FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)-FIND(".",F8,FIND(".",F8)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D8,LEN(D8)-FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)))+255-VALUE(RIGHT(F8,LEN(F8)-FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)))-1)</f>
+        <v>10.3.40.254</v>
+      </c>
+      <c r="I8" s="7">
+        <v>40</v>
+      </c>
+      <c r="J8">
+        <v>41</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="7">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="str">
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B11</f>
+        <v>3.3.3.10</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11" s="12"/>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="7">
+        <v>20</v>
+      </c>
+      <c r="C12" s="7" t="str">
+        <f t="shared" ref="C12:C14" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
+        <v>3.3.3.20</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="7">
+        <v>30</v>
+      </c>
+      <c r="C13" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>3.3.3.30</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="7">
+        <v>40</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>3.3.3.40</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14" s="12"/>
+    </row>
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="12" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H17&amp;"."&amp;$A$2</f>
+        <v>172.16.10.3</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="12" t="str">
+        <f t="shared" ref="E17:E20" si="4">$C$2</f>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="12">
+        <v>10</v>
+      </c>
+      <c r="I17" s="29" t="b">
+        <f>'Site 1 (HUB)'!I17</f>
+        <v>1</v>
+      </c>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="12" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H18&amp;"."&amp;$A$2</f>
+        <v>172.16.20.3</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="12">
+        <v>20</v>
+      </c>
+      <c r="I18" s="29" t="b" cm="1">
+        <f>'Site 1 (HUB)'!I18</f>
+        <v>0</v>
+      </c>
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="12" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
+        <v>172.16.30.3</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="12">
+        <v>30</v>
+      </c>
+      <c r="I19" s="29" t="b">
+        <f>'Site 1 (HUB)'!I19</f>
+        <v>1</v>
+      </c>
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="12" t="str">
+        <f t="shared" ref="C20" si="5">172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
+        <v>172.16.40.3</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="12">
+        <v>40</v>
+      </c>
+      <c r="I20" s="29" t="b">
+        <f>'Site 1 (HUB)'!I20</f>
+        <v>1</v>
+      </c>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <f>$A$2</f>
+        <v>3</v>
+      </c>
+      <c r="B23" s="12" t="str">
+        <f>$D$2</f>
+        <v>admin</v>
+      </c>
+      <c r="C23" s="12" t="str">
+        <f>$E$2</f>
+        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
+      </c>
+      <c r="D23" s="12" t="str">
+        <f>$F$2</f>
+        <v>0 - 15</v>
+      </c>
+      <c r="E23" s="12" t="str">
+        <f>$G$2</f>
+        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
+      </c>
+      <c r="F23" s="12">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L25" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <f>ROW()-25</f>
+        <v>1</v>
+      </c>
+      <c r="B26" s="7">
+        <f>$B$5</f>
+        <v>10</v>
+      </c>
+      <c r="C26" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A26+1)</f>
+        <v>10.3.10.2</v>
+      </c>
+      <c r="D26" s="7" t="str">
+        <f>$E$5</f>
+        <v>10.3.10.1</v>
+      </c>
+      <c r="E26" s="7" t="str">
+        <f>$F$5</f>
+        <v>255.255.255.0</v>
+      </c>
+      <c r="F26" s="7">
+        <v>49</v>
+      </c>
+      <c r="G26" s="7">
+        <v>1</v>
+      </c>
+      <c r="H26" s="10">
+        <v>1</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K26" s="2">
+        <f>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</f>
+        <v>44</v>
+      </c>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M27" s="31"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+    </row>
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+    </row>
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+    </row>
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+    </row>
+    <row r="33" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+    </row>
+    <row r="34" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+    </row>
+    <row r="35" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="31"/>
+      <c r="Q35" s="31"/>
+    </row>
+    <row r="36" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M36" s="31"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="31"/>
+    </row>
+    <row r="37" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+    </row>
+    <row r="38" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M38" s="31"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="31"/>
+      <c r="Q38" s="31"/>
+    </row>
+    <row r="39" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M39" s="31"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="31"/>
+      <c r="Q39" s="31"/>
+    </row>
+    <row r="40" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+    </row>
+    <row r="41" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+    </row>
+    <row r="42" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+    </row>
+    <row r="43" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+    </row>
+    <row r="44" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+    </row>
+    <row r="45" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M45" s="31"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="31"/>
+      <c r="Q45" s="31"/>
+    </row>
+    <row r="46" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+    </row>
+    <row r="47" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+    </row>
+    <row r="48" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M48" s="31"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+    </row>
+    <row r="49" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+    </row>
+    <row r="50" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="31"/>
+      <c r="N50" s="31"/>
+      <c r="O50" s="31"/>
+      <c r="P50" s="31"/>
+      <c r="Q50" s="31"/>
+    </row>
+    <row r="51" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M51" s="31"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="31"/>
+    </row>
+    <row r="52" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+    </row>
+    <row r="53" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="31"/>
+      <c r="P53" s="31"/>
+      <c r="Q53" s="31"/>
+    </row>
+    <row r="54" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
+      <c r="P54" s="31"/>
+      <c r="Q54" s="31"/>
+    </row>
+    <row r="55" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+    </row>
+    <row r="56" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M56" s="31"/>
+      <c r="N56" s="31"/>
+      <c r="O56" s="31"/>
+      <c r="P56" s="31"/>
+      <c r="Q56" s="31"/>
+    </row>
+    <row r="57" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <dataValidations count="9">
+    <dataValidation type="list" sqref="G23" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{00000000-0002-0000-0100-000001000000}">
+      <formula1>"OFF,STRICT,LOOSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="O2:P2 S2 M26:N56" xr:uid="{00000000-0002-0000-0100-000003000000}">
+      <formula1>"OLD,NEW"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="Q2 O26:O56" xr:uid="{00000000-0002-0000-0100-000004000000}">
+      <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="R2" xr:uid="{00000000-0002-0000-0100-000005000000}">
+      <formula1>"CLASSIC,NAMED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="T2" xr:uid="{00000000-0002-0000-0100-000006000000}">
+      <formula1>"IKEV1,IKEV2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="U2 P26:P56" xr:uid="{00000000-0002-0000-0100-000007000000}">
+      <formula1>"AUTO,5,8,9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="V2 Q26:Q56" xr:uid="{00000000-0002-0000-0100-000008000000}">
+      <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26" xr:uid="{67E4AE03-2DF0-440B-B572-B891D49BFDE5}">
+      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="6">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -6311,293 +9082,293 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>61</v>
-      </c>
       <c r="C1" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="G1" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="17" t="s">
         <v>88</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" s="16">
         <v>67</v>
       </c>
       <c r="E2" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="H2" s="18" t="s">
         <v>92</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="E3" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="18" t="s">
+      <c r="H3" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" s="16">
         <v>67</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G4" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="18" t="s">
         <v>98</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>95</v>
-      </c>
       <c r="E5" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G5" s="18" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D6" s="16">
         <v>53</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G6" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="18" t="s">
         <v>103</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" s="16">
         <v>53</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G7" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>106</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" s="16">
         <v>80</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" s="16">
         <v>443</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>110</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" s="16">
         <v>67</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>95</v>
-      </c>
       <c r="E11" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" s="16">
         <v>67</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>95</v>
-      </c>
       <c r="E13" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" t="s">
         <v>112</v>
-      </c>
-      <c r="H14" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" t="s">
         <v>114</v>
-      </c>
-      <c r="H15" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FDC081-0AE7-480A-A5CE-BDBCEDF0E338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA63241C-B68F-4D2E-BB77-1D6D48C550D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -7858,7 +7858,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>129</v>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="K26" s="2">
         <f>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M26" s="31"/>
       <c r="N26" s="31"/>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA63241C-B68F-4D2E-BB77-1D6D48C550D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7604A2-3663-42E4-8C01-017B85CE52F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="134">
   <si>
     <t>site</t>
   </si>
@@ -454,13 +454,19 @@
   </si>
   <si>
     <t>8.8.8.8, 1.1.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>tunnel 50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -559,6 +565,25 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -632,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -754,41 +779,42 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="177">
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+  <dxfs count="171">
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
         <color theme="1"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <color theme="1"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -801,7 +827,6 @@
       <font>
         <sz val="11"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -811,7 +836,6 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -821,606 +845,34 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
     </dxf>
     <dxf>
       <font>
         <sz val="11"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="11"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2259,6 +1711,565 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
     </dxf>
@@ -2301,60 +2312,60 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="176"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ISP-VLAN" dataDxfId="175"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="174"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="173"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="172"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="tacacs_server_ip" dataDxfId="171"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="syslog_server_ip" dataDxfId="170"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="urpf_mode" dataDxfId="169"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="radius_server_ip" dataDxfId="168"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="radius_key" dataDxfId="167"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="dmvpn_phase" dataDxfId="166"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="tacacs_syntax" dataDxfId="165"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="radius_syntax" dataDxfId="164"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="dot1x_syntax" dataDxfId="163"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="eigrp_syntax" dataDxfId="162"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="vrf_syntax" dataDxfId="161"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ike_version" dataDxfId="160"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="secret_type" dataDxfId="159"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="trunk_encapsulation" dataDxfId="158"/>
-    <tableColumn id="26" xr3:uid="{7A70CB3D-3E69-4511-AFC7-833193219BEB}" name="snmpv3_enabled" dataDxfId="157"/>
-    <tableColumn id="27" xr3:uid="{209B66CE-CA9A-4100-AF1F-D365CF1FFE1D}" name="snmp_server_ip" dataDxfId="156"/>
-    <tableColumn id="28" xr3:uid="{35546B6C-3A4D-4CB1-960A-7557AC2139AF}" name="snmp_user" dataDxfId="155"/>
-    <tableColumn id="29" xr3:uid="{EEE156DA-8F56-4FDB-B5BD-E05593FB26D6}" name="snmp_auth_password" dataDxfId="154"/>
-    <tableColumn id="30" xr3:uid="{C5D4501A-8EFA-4918-A4F1-64D389B519DA}" name="snmp_priv_password" dataDxfId="153"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="secret" dataDxfId="110"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="ISP-VLAN" dataDxfId="109"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="tacacs_key" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DHCP" dataDxfId="107"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="dns_servers" dataDxfId="106"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="tacacs_server_ip" dataDxfId="105"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="syslog_server_ip" dataDxfId="104"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="urpf_mode" dataDxfId="103"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="radius_server_ip" dataDxfId="102"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="radius_key" dataDxfId="101"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="dmvpn_phase" dataDxfId="100"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="tacacs_syntax" dataDxfId="99"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="radius_syntax" dataDxfId="98"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="dot1x_syntax" dataDxfId="97"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="eigrp_syntax" dataDxfId="96"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="vrf_syntax" dataDxfId="95"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="ike_version" dataDxfId="94"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="secret_type" dataDxfId="93"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="trunk_encapsulation" dataDxfId="92"/>
+    <tableColumn id="26" xr3:uid="{7A70CB3D-3E69-4511-AFC7-833193219BEB}" name="snmpv3_enabled" dataDxfId="91"/>
+    <tableColumn id="27" xr3:uid="{209B66CE-CA9A-4100-AF1F-D365CF1FFE1D}" name="snmp_server_ip" dataDxfId="90"/>
+    <tableColumn id="28" xr3:uid="{35546B6C-3A4D-4CB1-960A-7557AC2139AF}" name="snmp_user" dataDxfId="89"/>
+    <tableColumn id="29" xr3:uid="{EEE156DA-8F56-4FDB-B5BD-E05593FB26D6}" name="snmp_auth_password" dataDxfId="88"/>
+    <tableColumn id="30" xr3:uid="{C5D4501A-8EFA-4918-A4F1-64D389B519DA}" name="snmp_priv_password" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D32D18C4-0B05-425E-B28E-67E8EEF86C01}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A25:Q27" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D32D18C4-0B05-425E-B28E-67E8EEF86C01}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A28:Q30" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{3D2619F9-8A27-48B4-BBAD-F8DAD24B7058}" name="SW" dataDxfId="28">
-      <calculatedColumnFormula>ROW()-25</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{3D2619F9-8A27-48B4-BBAD-F8DAD24B7058}" name="SW" dataDxfId="11">
+      <calculatedColumnFormula>ROW()-28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{79D48293-3CC1-4FC8-B959-C76EC31AF05A}" name="MGMT Vlan" dataDxfId="27">
+    <tableColumn id="2" xr3:uid="{79D48293-3CC1-4FC8-B959-C76EC31AF05A}" name="MGMT Vlan" dataDxfId="10">
       <calculatedColumnFormula>$B$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{636012CC-2311-45D4-B0A3-CBE1DDB288EA}" name="MGMT ip" dataDxfId="26">
-      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A26+1)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{636012CC-2311-45D4-B0A3-CBE1DDB288EA}" name="MGMT ip" dataDxfId="9">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{57B036DD-2EC2-46AB-BA82-15C2E4251EE3}" name="gateway" dataDxfId="25">
+    <tableColumn id="4" xr3:uid="{57B036DD-2EC2-46AB-BA82-15C2E4251EE3}" name="gateway" dataDxfId="8">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D16308A-64E5-4F82-9997-B8BD8FE03B86}" name="mask" dataDxfId="24">
+    <tableColumn id="5" xr3:uid="{6D16308A-64E5-4F82-9997-B8BD8FE03B86}" name="mask" dataDxfId="7">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{10263F16-185C-4388-8A92-6BC4CA0E07C5}" name="num_ports_tot" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{337036FB-EC4A-4A8B-A2D4-886EF58ACF98}" name="skiped_ports" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{75ED65B8-97AC-498A-9CF3-0A234BF7E9F1}" name="num_downlink" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{D2EB23FE-1E37-4D17-B4EC-11CAC9B6F0DC}" name="vlan-antall" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{0815D94A-1C82-4867-98BC-98ABBA28ECDE}" name="intf_prefix" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{CDF41783-F241-44AB-837D-97EDFE6911D4}" name="num_port_ledig" dataDxfId="18">
-      <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{10263F16-185C-4388-8A92-6BC4CA0E07C5}" name="num_ports_tot" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{337036FB-EC4A-4A8B-A2D4-886EF58ACF98}" name="skiped_ports" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{75ED65B8-97AC-498A-9CF3-0A234BF7E9F1}" name="num_downlink" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{D2EB23FE-1E37-4D17-B4EC-11CAC9B6F0DC}" name="vlan-antall" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{0815D94A-1C82-4867-98BC-98ABBA28ECDE}" name="intf_prefix" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{CDF41783-F241-44AB-837D-97EDFE6911D4}" name="num_port_ledig" dataDxfId="1">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{AACD1EB8-91AF-4962-8481-F05F6073247E}" name="MONITORING ip"/>
     <tableColumn id="13" xr3:uid="{7E243D0A-E644-41FD-A148-B1875C00196D}" name="tacacs_syntax"/>
@@ -2386,8 +2397,8 @@
     <tableColumn id="8" xr3:uid="{09FF5408-B542-4803-BB81-19C6D96455ED}" name="address max">
       <calculatedColumnFormula>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1C2CE40E-C587-4306-B04C-05E7E830B912}" name="antall-res" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{062A0975-F29C-4725-993D-1C745C38968F}" name="pri-afxx"/>
+    <tableColumn id="9" xr3:uid="{1C2CE40E-C587-4306-B04C-05E7E830B912}" name="antall-res" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{062A0975-F29C-4725-993D-1C745C38968F}" name=" "/>
     <tableColumn id="11" xr3:uid="{E9F272DB-833F-4003-8FE1-C3489DCBD223}" name="pri-1-10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2395,12 +2406,12 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{137249B9-B569-4AB4-A5F4-44E14EC73E12}" name="Tabell7715" displayName="Tabell7715" ref="A10:C14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{137249B9-B569-4AB4-A5F4-44E14EC73E12}" name="Tabell7715" displayName="Tabell7715" ref="A11:C15">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3A3EB178-6BB6-4F25-BFF2-BC4D427D60C7}" name="vrf"/>
     <tableColumn id="3" xr3:uid="{00063F96-3CCE-4FBF-AEA1-0FEA482EE82B}" name="loopback"/>
     <tableColumn id="4" xr3:uid="{068346AF-14A6-4C4B-94E5-C3159DB837E3}" name="laddr">
-      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B11</calculatedColumnFormula>
+      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2408,155 +2419,173 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabell1" displayName="Tabell1" ref="A1:AA2" dataDxfId="125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C60AC8E-4581-4040-8CC5-F80E674B402C}" name="Tabell182" displayName="Tabell182" ref="A1:AA2" dataDxfId="170">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="site" dataDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="intf_prefix" dataDxfId="123"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="router-id" dataDxfId="122"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="brukernavn" dataDxfId="121"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="passord" dataDxfId="120"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="vty_lines" dataDxfId="119"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="secret" dataDxfId="118"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="tacacs_key" dataDxfId="117">
+    <tableColumn id="1" xr3:uid="{DFCE91FF-608A-44ED-A5CB-ACD8B514AF73}" name="site" dataDxfId="169"/>
+    <tableColumn id="2" xr3:uid="{5DF854F6-DD6B-482C-B348-01B229D7B185}" name="intf_prefix" dataDxfId="168"/>
+    <tableColumn id="3" xr3:uid="{790C3FB9-3DCF-4CFE-B434-3841F3F4CF2D}" name="router-id" dataDxfId="167">
+      <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{FA3F5E0E-C16D-4EA4-BDD0-AB9FF9D36A22}" name="brukernavn" dataDxfId="166"/>
+    <tableColumn id="5" xr3:uid="{D4D947B6-A29A-4505-A4DA-815913EDDA88}" name="passord" dataDxfId="165"/>
+    <tableColumn id="6" xr3:uid="{7A49D571-9CC6-43ED-B79F-D38304D89536}" name="vty_lines" dataDxfId="164"/>
+    <tableColumn id="7" xr3:uid="{12F1C824-518B-4333-B662-47EC33509F9D}" name="secret" dataDxfId="163"/>
+    <tableColumn id="8" xr3:uid="{0DDBDB15-F6E1-4438-8FA4-CBDC7F940431}" name="tacacs_key" dataDxfId="162">
       <calculatedColumnFormula>'Site 1 (HUB)'!I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="dns_servers" dataDxfId="116"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="tacacs_server_ip" dataDxfId="115">
+    <tableColumn id="9" xr3:uid="{DCAD99D0-D61D-4F08-8352-0D7B17728799}" name="dns_servers" dataDxfId="161"/>
+    <tableColumn id="10" xr3:uid="{B6B56649-3DA3-4CFB-92A6-6719284F2DDA}" name="tacacs_server_ip" dataDxfId="160">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="syslog_server_ip" dataDxfId="114">
+    <tableColumn id="11" xr3:uid="{2734B32E-340C-4B96-8086-D16467942071}" name="syslog_server_ip" dataDxfId="159">
       <calculatedColumnFormula>'Site 1 (HUB)'!M2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="urpf_mode" dataDxfId="113"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="radius_server_ip" dataDxfId="112"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="radius_key" dataDxfId="111"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="tacacs_syntax" dataDxfId="110"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0600-000010000000}" name="radius_syntax" dataDxfId="109"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0600-000011000000}" name="dot1x_syntax" dataDxfId="108"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0600-000012000000}" name="eigrp_syntax" dataDxfId="107"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0600-000013000000}" name="vrf_syntax" dataDxfId="106"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0600-000014000000}" name="ike_version" dataDxfId="105"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0600-000015000000}" name="secret_type" dataDxfId="104"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0600-000016000000}" name="trunk_encapsulation" dataDxfId="103"/>
-    <tableColumn id="23" xr3:uid="{96BFD35F-5B86-4563-AD71-9BEE692F259E}" name="snmpv3_enabled" dataDxfId="102"/>
-    <tableColumn id="24" xr3:uid="{B32071E9-38D7-497D-8D05-9C277245ED7D}" name="snmp_server_ip" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{A51FD30E-2A50-4B3C-B10C-DC9965677024}" name="snmp_user" dataDxfId="100"/>
-    <tableColumn id="26" xr3:uid="{E35869A0-05B2-4390-88E0-3DB67D32BD41}" name="snmp_auth_password" dataDxfId="99"/>
-    <tableColumn id="27" xr3:uid="{962D48F4-6B6F-4976-A32F-AFCF203A4E6E}" name="snmp_priv_password" dataDxfId="98"/>
+    <tableColumn id="12" xr3:uid="{932EA2FA-00C9-4B65-96DE-2A8C7CCC9623}" name="urpf_mode" dataDxfId="158"/>
+    <tableColumn id="14" xr3:uid="{0A05EAA9-4619-4CC8-AF17-9890232CE0A7}" name="radius_server_ip" dataDxfId="157">
+      <calculatedColumnFormula>'Site 1 (HUB)'!O2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{B3F95825-6EF4-4409-B363-0BE17244502B}" name="radius_key" dataDxfId="156">
+      <calculatedColumnFormula>'Site 1 (HUB)'!P2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{58ECFE80-A988-475F-BD24-A26F8EFC7A8D}" name="tacacs_syntax" dataDxfId="155"/>
+    <tableColumn id="16" xr3:uid="{79E9C26B-4DDA-44F0-88A9-BD1FFF65EA6D}" name="radius_syntax" dataDxfId="154"/>
+    <tableColumn id="17" xr3:uid="{45BFC1E5-9227-484E-A609-C4DBCB058F2C}" name="dot1x_syntax" dataDxfId="153"/>
+    <tableColumn id="18" xr3:uid="{DE5CD905-AB0A-4281-96DD-1500626743D4}" name="eigrp_syntax" dataDxfId="152"/>
+    <tableColumn id="19" xr3:uid="{B072AF5E-0DB2-49BB-8F74-FA3249A788FE}" name="vrf_syntax" dataDxfId="151"/>
+    <tableColumn id="20" xr3:uid="{6706F7F4-BF14-4761-9D16-BD6D20F80622}" name="ike_version" dataDxfId="150"/>
+    <tableColumn id="21" xr3:uid="{1A182393-1100-428B-8B4D-9AFB98D01661}" name="secret_type" dataDxfId="149"/>
+    <tableColumn id="22" xr3:uid="{49E7B89A-8DF7-4889-839B-D8838B6390C7}" name="trunk_encapsulation" dataDxfId="148"/>
+    <tableColumn id="23" xr3:uid="{FAA8BF28-43AD-4E66-BF05-ACADD2A986A6}" name="snmpv3_enabled" dataDxfId="147"/>
+    <tableColumn id="24" xr3:uid="{BE8ED0D7-0829-4E21-8670-4897E3ADE322}" name="snmp_server_ip" dataDxfId="146"/>
+    <tableColumn id="25" xr3:uid="{C61E16D6-489B-4639-A0C5-A22F2664CCB2}" name="snmp_user" dataDxfId="145"/>
+    <tableColumn id="26" xr3:uid="{2900EC79-7717-462E-B651-5F02EAEE0440}" name="snmp_auth_password" dataDxfId="144"/>
+    <tableColumn id="27" xr3:uid="{CC2C2D42-240D-452D-B846-BB1DEF70F8D8}" name="snmp_priv_password" dataDxfId="143"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabell4" displayName="Tabell4" ref="A16:J20" dataDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47444F68-52DD-4020-A8C3-121097047CE4}" name="Tabell493" displayName="Tabell493" ref="A18:J22" dataDxfId="142">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="tunnel id" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="vrf" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="ip address" dataDxfId="94">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{55B6356B-AFF1-4386-837E-122F110FE048}" name="tunnel id" dataDxfId="141"/>
+    <tableColumn id="2" xr3:uid="{B5627186-AB74-4D83-9392-91908D53F7BB}" name="vrf" dataDxfId="140"/>
+    <tableColumn id="3" xr3:uid="{5D8B1DCA-3FFB-4C14-9357-5B2911B0414B}" name="ip address" dataDxfId="139">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="92">
+    <tableColumn id="4" xr3:uid="{5E9F71E8-6C96-465D-8829-6F95E415C54C}" name="mask" dataDxfId="138"/>
+    <tableColumn id="5" xr3:uid="{04B93F27-2105-4CD1-8282-A96667B8D048}" name="source" dataDxfId="137">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="gre mode" dataDxfId="90"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="network-id" dataDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="ipsec" dataDxfId="88"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="ipsec key" dataDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{4F9F6E3C-23F1-4807-9408-1055BD20C8BE}" name="destination" dataDxfId="136"/>
+    <tableColumn id="7" xr3:uid="{63AC65C8-779A-43ED-8BCC-861F84A05B7B}" name="gre mode" dataDxfId="135"/>
+    <tableColumn id="8" xr3:uid="{12CFCF68-1AA6-478A-A878-30BEAAD47165}" name="network-id" dataDxfId="134"/>
+    <tableColumn id="9" xr3:uid="{96158AEC-6587-4768-B48B-03A505CBF781}" name="ipsec" dataDxfId="133">
+      <calculatedColumnFormula>'Site 1 (HUB)'!I19</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{8928B759-FF4A-40F1-971D-0C0EE8DD40B4}" name="ipsec key" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tabell13192530" displayName="Tabell13192530" ref="A22:H23" dataDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D4039491-9BC9-46AA-ACDA-873C6CFE06D8}" name="Tabell13192530107" displayName="Tabell13192530107" ref="A25:H26" dataDxfId="131">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="site" dataDxfId="85">
-      <calculatedColumnFormula>A2</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{5FE8027B-1EBD-40FA-9138-BFA1D40F7043}" name="site" dataDxfId="130">
+      <calculatedColumnFormula>$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="brukernavn" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="passord" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="vty_lines" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="secret" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="etherchan_num" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="span_mode" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0800-000008000000}" name="dot1x_vlans" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{328AA2B5-7A14-44F9-B093-0500F8F3797B}" name="brukernavn" dataDxfId="129">
+      <calculatedColumnFormula>$D$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{03DDB2FF-50BB-44A4-9A30-EAB05A418213}" name="passord" dataDxfId="128">
+      <calculatedColumnFormula>$E$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{1297971E-A08E-4A6B-9A9B-6BE6B919F309}" name="vty_lines" dataDxfId="127">
+      <calculatedColumnFormula>$F$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{0C8384C9-AA8F-4EF7-A6C3-F4B2C5EF2EAC}" name="secret" dataDxfId="126">
+      <calculatedColumnFormula>$G$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{2CA86CB3-1D71-42BA-A7B0-DBD5BB2916B6}" name="etherchan_num" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{755D61CE-A84F-47D5-B7F6-717BDFC54940}" name="span_mode" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{D00F4A82-CD6D-4CB8-AE6D-E90F4F86412E}" name="dot1x_vlans" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tabell161824282532" displayName="Tabell161824282532" ref="A25:Q26" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{763708C6-BBA5-4081-A5A6-5F727C0852E6}" name="Tabell1618242825321216" displayName="Tabell1618242825321216" ref="A28:Q30" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="SW" dataDxfId="16">
-      <calculatedColumnFormula>ROW()-25</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{45194AB5-B480-4B1A-B95B-CA50B65B1264}" name="SW" dataDxfId="122">
+      <calculatedColumnFormula>ROW()-28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="MGMT Vlan" dataDxfId="15">
+    <tableColumn id="2" xr3:uid="{E26F807A-4589-44B4-82F1-D4548A0F0070}" name="MGMT Vlan" dataDxfId="121">
       <calculatedColumnFormula>$B$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="MGMT ip" dataDxfId="14">
-      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A26+1)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{6109B699-5B93-4FEA-8E30-9F0B359DB86F}" name="MGMT ip" dataDxfId="120">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="gateway" dataDxfId="13">
+    <tableColumn id="4" xr3:uid="{90803DA6-8268-4AAF-94FC-6CB82C7D1B68}" name="gateway" dataDxfId="119">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="mask" dataDxfId="12">
+    <tableColumn id="5" xr3:uid="{A7E5E398-6D1D-4B22-8003-FDDC8C87876E}" name="mask" dataDxfId="118">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0900-00000A000000}" name="num_ports_tot" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0900-00000B000000}" name="skiped_ports" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="num_downlink" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="vlan-antall" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="intf_prefix" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0900-000009000000}" name="num_port_ledig" dataDxfId="6">
-      <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{B5FC786B-C70A-4E77-B469-9373A58198A2}" name="num_ports_tot" dataDxfId="117"/>
+    <tableColumn id="11" xr3:uid="{A766979F-B52B-4052-9122-D365A4600150}" name="skiped_ports" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{956ED757-3CF2-47A9-83E1-224C04FC15E2}" name="num_downlink" dataDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{AC8CB3C3-95F4-48BC-A5C7-7D1BC47D2896}" name="vlan-antall" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{DFD5F6B7-25A1-4113-847E-63C8C8D1F3A5}" name="intf_prefix" dataDxfId="113"/>
+    <tableColumn id="9" xr3:uid="{6240FEDA-0A81-4D8B-9087-893236958125}" name="num_port_ledig" dataDxfId="112">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0900-00000C000000}" name="MONITORING ip"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0900-00000D000000}" name="tacacs_syntax" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0900-00000E000000}" name="radius_syntax" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0900-00000F000000}" name="dot1x_syntax" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0900-000010000000}" name="secret_type" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0900-000011000000}" name="trunk_encapsulation" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{B80135C7-C94A-4B44-9E4B-48954B72D5AF}" name="MONITORING ip"/>
+    <tableColumn id="13" xr3:uid="{6276821C-D0EE-4B14-B6BC-18D8A797F851}" name="tacacs_syntax"/>
+    <tableColumn id="14" xr3:uid="{70523AF6-8AB5-49B4-900B-C6625C0630A7}" name="radius_syntax"/>
+    <tableColumn id="15" xr3:uid="{88E12463-A527-4624-8BF2-CAD84A51C21F}" name="dot1x_syntax"/>
+    <tableColumn id="16" xr3:uid="{3111D73C-7819-40B1-960B-F86A1AF480F0}" name="secret_type"/>
+    <tableColumn id="17" xr3:uid="{27C0B5EF-CE01-41D7-8229-163F942BEC21}" name="trunk_encapsulation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Tabell62" displayName="Tabell62" ref="A4:K8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{6D95D07F-8F14-4367-9CDF-18F3658439E7}" name="Tabell621417" displayName="Tabell621417" ref="A4:K8">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="vrf"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="vlan"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="interface"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="nett id">
-      <calculatedColumnFormula>10&amp;"."&amp;(B5+$A$2)&amp;"."&amp;0&amp;"."&amp;0</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{384AC9DB-C826-45C1-821C-E57C417EE87F}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{90F3CD07-780D-4875-A850-EAFCF3EE494F}" name="vlan"/>
+    <tableColumn id="3" xr3:uid="{12502B20-F565-40D6-B3B3-45F79DB2A37B}" name="interface"/>
+    <tableColumn id="4" xr3:uid="{484C4C38-4E74-40AB-950E-3E4D903540F6}" name="nett id">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".0"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="gateway">
-      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{6A83FE40-5341-406B-835C-99DA624D36DB}" name="gateway">
+      <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".1"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="mask"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0A00-000007000000}" name="address min">
-      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{A802C697-FC3F-4D7F-882D-434FFFCAB3DD}" name="mask"/>
+    <tableColumn id="7" xr3:uid="{AD7D2426-F2FC-41CE-A62F-ECB9490D07DE}" name="address min">
+      <calculatedColumnFormula>VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0A00-000009000000}" name="antall-res" dataDxfId="77"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0A00-00000A000000}" name="pri-afxx"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0A00-00000B000000}" name="pri-1-10"/>
+    <tableColumn id="8" xr3:uid="{36B80577-2EA1-4CA8-A93B-C744BC10CA3F}" name="address max">
+      <calculatedColumnFormula>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{452A6983-A082-48CF-A21D-B00E01BAEC99}" name="antall-res" dataDxfId="111"/>
+    <tableColumn id="10" xr3:uid="{7CD1C757-50B2-45D7-B177-2458072FF692}" name=" "/>
+    <tableColumn id="11" xr3:uid="{585E7ADE-9615-485F-8639-F60F08837CB8}" name="pri-1-10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabell77" displayName="Tabell77" ref="A10:C14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E7DDB9FD-3F40-4535-A424-3940ECCA451C}" name="Tabell771518" displayName="Tabell771518" ref="A11:C15">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="vrf"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="loopback"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="laddr">
-      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B11)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{0D515D14-BE04-4C0D-9DF8-C59F117A1AB2}" name="vrf"/>
+    <tableColumn id="3" xr3:uid="{79C172D7-5EEE-4026-9E85-C40968702894}" name="loopback"/>
+    <tableColumn id="4" xr3:uid="{4ECDBDF9-7E62-4B0D-9B0C-A4EE2AE0B9E0}" name="laddr">
+      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2564,7 +2593,7 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="FlowPolicyTable" displayName="FlowPolicyTable" ref="A1:E13" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="FlowPolicyTable" displayName="FlowPolicyTable" ref="A1:E14" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="source"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="destination"/>
@@ -2582,13 +2611,13 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="interface"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="152">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="nett id" dataDxfId="86">
       <calculatedColumnFormula>10&amp;"."&amp;($A$2)&amp;"."&amp;$B5&amp;"."&amp;0</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="gateway"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="151">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max" dataDxfId="85">
       <calculatedColumnFormula array="1">_xlfn.LET(
 _xlpm.net,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[nett id]],".")*{16777216,65536,256,1}),
 _xlpm.mask,SUM(--_xlfn.TEXTSPLIT(Tabell6[[#This Row],[mask]],".")*{16777216,65536,256,1}),
@@ -2596,7 +2625,7 @@
 _xlfn.TEXTJOIN(".",TRUE,MOD(QUOTIENT(_xlpm.addr,{16777216,65536,256,1}),256))
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="150"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="antall-res" dataDxfId="84"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="pri-1-10"/>
   </tableColumns>
@@ -2605,12 +2634,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabell7" displayName="Tabell7" ref="A10:C14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabell7" displayName="Tabell7" ref="A11:C15">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="vrf"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="loopback"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="laddr">
-      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B11)</calculatedColumnFormula>
+      <calculatedColumnFormula>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;(B12)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2618,15 +2647,15 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabell8" displayName="Tabell8" ref="A16:J20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabell8" displayName="Tabell8" ref="A18:J22">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="tunnel id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="vrf"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address" dataDxfId="149">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;$H17&amp;"."&amp;($A$2)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="ip address" dataDxfId="83">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;$H19&amp;"."&amp;($A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="148">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="82">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -2640,19 +2669,19 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A22:I23" dataDxfId="147">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabell131921" displayName="Tabell131921" ref="A25:I26" dataDxfId="81">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="146">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="site" dataDxfId="80">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="145"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="144"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="143"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="142"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="141"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="140"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="139"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="138">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="brukernavn" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="passord" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="vty_lines" dataDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="76"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="74"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="72">
       <calculatedColumnFormula array="1">Tabell5[ISP-VLAN]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2661,30 +2690,30 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A25:Q26" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:Q29" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="137">
-      <calculatedColumnFormula>ROW()-25</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="71">
+      <calculatedColumnFormula>ROW()-28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="136"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="135">
-      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A26)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="69">
+      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="134">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="68">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="133">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="67">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="132"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="131"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="130"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="129"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="128"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="127">
-      <calculatedColumnFormula>IF($A26=1,F26-G26-H26*$F$23-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="ERSPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="61">
+      <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="126"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="60"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="tacacs_syntax"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="radius_syntax"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="dot1x_syntax"/>
@@ -2696,97 +2725,97 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51BF1746-4E83-4B5C-8E47-1B33E5F0C823}" name="Tabell18" displayName="Tabell18" ref="A1:AA2" dataDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51BF1746-4E83-4B5C-8E47-1B33E5F0C823}" name="Tabell18" displayName="Tabell18" ref="A1:AA2" dataDxfId="59">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{F301071E-AB49-411D-B862-3D5F1A8652F4}" name="site" dataDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{28087ADC-D839-428A-B3B6-5D33053FC989}" name="intf_prefix" dataDxfId="74"/>
-    <tableColumn id="3" xr3:uid="{E07A6BD4-5C25-4907-8DBF-B7CD7A55F1D8}" name="router-id" dataDxfId="73">
+    <tableColumn id="1" xr3:uid="{F301071E-AB49-411D-B862-3D5F1A8652F4}" name="site" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{28087ADC-D839-428A-B3B6-5D33053FC989}" name="intf_prefix" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{E07A6BD4-5C25-4907-8DBF-B7CD7A55F1D8}" name="router-id" dataDxfId="56">
       <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E5D534F2-DADF-4E06-844E-EFC868A109BF}" name="brukernavn" dataDxfId="72"/>
-    <tableColumn id="5" xr3:uid="{8E37AE50-BD24-4C9E-97D1-6B548927DBB7}" name="passord" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{0A3407AA-8EBE-4074-85F9-778319C50E4E}" name="vty_lines" dataDxfId="70"/>
-    <tableColumn id="7" xr3:uid="{0E482BA6-C79D-40DB-B45E-FDC671702D74}" name="secret" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{C39694E5-0D09-45FB-A48D-8E9A8C91CA0E}" name="tacacs_key" dataDxfId="68">
+    <tableColumn id="4" xr3:uid="{E5D534F2-DADF-4E06-844E-EFC868A109BF}" name="brukernavn" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{8E37AE50-BD24-4C9E-97D1-6B548927DBB7}" name="passord" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{0A3407AA-8EBE-4074-85F9-778319C50E4E}" name="vty_lines" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{0E482BA6-C79D-40DB-B45E-FDC671702D74}" name="secret" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{C39694E5-0D09-45FB-A48D-8E9A8C91CA0E}" name="tacacs_key" dataDxfId="51">
       <calculatedColumnFormula>'Site 1 (HUB)'!I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{44EB3B31-5D13-48ED-A202-643DB3DE780D}" name="dns_servers" dataDxfId="67"/>
-    <tableColumn id="10" xr3:uid="{97E12567-6CA3-4115-A196-2529D7160615}" name="tacacs_server_ip" dataDxfId="66">
+    <tableColumn id="9" xr3:uid="{44EB3B31-5D13-48ED-A202-643DB3DE780D}" name="dns_servers" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{97E12567-6CA3-4115-A196-2529D7160615}" name="tacacs_server_ip" dataDxfId="49">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0346B8E5-A202-466C-AB4B-67EDD69B81A1}" name="syslog_server_ip" dataDxfId="65">
+    <tableColumn id="11" xr3:uid="{0346B8E5-A202-466C-AB4B-67EDD69B81A1}" name="syslog_server_ip" dataDxfId="48">
       <calculatedColumnFormula>'Site 1 (HUB)'!M2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE86801E-B0D0-4B58-832A-86AC77A7EC9A}" name="urpf_mode" dataDxfId="64"/>
-    <tableColumn id="14" xr3:uid="{5AAC65E5-8130-4C09-99B3-54C834DEE5C1}" name="radius_server_ip" dataDxfId="63">
+    <tableColumn id="12" xr3:uid="{EE86801E-B0D0-4B58-832A-86AC77A7EC9A}" name="urpf_mode" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{5AAC65E5-8130-4C09-99B3-54C834DEE5C1}" name="radius_server_ip" dataDxfId="46">
       <calculatedColumnFormula>'Site 1 (HUB)'!O2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1C900422-8FD8-4B49-B19A-47F4CE877466}" name="radius_key" dataDxfId="62">
+    <tableColumn id="15" xr3:uid="{1C900422-8FD8-4B49-B19A-47F4CE877466}" name="radius_key" dataDxfId="45">
       <calculatedColumnFormula>'Site 1 (HUB)'!P2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{AD662EC0-7940-4F3A-8F56-38E0BAEE7E2B}" name="tacacs_syntax" dataDxfId="61"/>
-    <tableColumn id="16" xr3:uid="{103CB279-D718-4AF9-A977-B976A8B36356}" name="radius_syntax" dataDxfId="60"/>
-    <tableColumn id="17" xr3:uid="{3496AD74-0539-4463-997F-A1CA64512F54}" name="dot1x_syntax" dataDxfId="59"/>
-    <tableColumn id="18" xr3:uid="{F8B1DCD1-84B0-4090-BDAB-AD6FA5328F3C}" name="eigrp_syntax" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{E8281F74-01EE-4CFD-8DF1-C429390E1E04}" name="vrf_syntax" dataDxfId="57"/>
-    <tableColumn id="20" xr3:uid="{9FA158AF-3041-42DD-9BB3-CA83FCDE6CA1}" name="ike_version" dataDxfId="56"/>
-    <tableColumn id="21" xr3:uid="{045B3C14-6117-44CA-9A5A-D8BA1860F47E}" name="secret_type" dataDxfId="55"/>
-    <tableColumn id="22" xr3:uid="{3829C8E8-1959-4691-AF37-5B45456BC812}" name="trunk_encapsulation" dataDxfId="54"/>
-    <tableColumn id="23" xr3:uid="{4CE3B16C-67F6-4DC2-9BB2-F8E09C5C8D74}" name="snmpv3_enabled" dataDxfId="53"/>
-    <tableColumn id="24" xr3:uid="{7E57634C-C61D-454F-83A9-CCC1D7A3E9A7}" name="snmp_server_ip" dataDxfId="52"/>
-    <tableColumn id="25" xr3:uid="{DA892339-1F60-44AE-B105-D466545319B6}" name="snmp_user" dataDxfId="51"/>
-    <tableColumn id="26" xr3:uid="{10EE6F10-8503-4A58-9CA0-8FB438354050}" name="snmp_auth_password" dataDxfId="50"/>
-    <tableColumn id="27" xr3:uid="{66121011-59AB-4D41-BDF5-22B7624358BE}" name="snmp_priv_password" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{AD662EC0-7940-4F3A-8F56-38E0BAEE7E2B}" name="tacacs_syntax" dataDxfId="44"/>
+    <tableColumn id="16" xr3:uid="{103CB279-D718-4AF9-A977-B976A8B36356}" name="radius_syntax" dataDxfId="43"/>
+    <tableColumn id="17" xr3:uid="{3496AD74-0539-4463-997F-A1CA64512F54}" name="dot1x_syntax" dataDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{F8B1DCD1-84B0-4090-BDAB-AD6FA5328F3C}" name="eigrp_syntax" dataDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{E8281F74-01EE-4CFD-8DF1-C429390E1E04}" name="vrf_syntax" dataDxfId="40"/>
+    <tableColumn id="20" xr3:uid="{9FA158AF-3041-42DD-9BB3-CA83FCDE6CA1}" name="ike_version" dataDxfId="39"/>
+    <tableColumn id="21" xr3:uid="{045B3C14-6117-44CA-9A5A-D8BA1860F47E}" name="secret_type" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{3829C8E8-1959-4691-AF37-5B45456BC812}" name="trunk_encapsulation" dataDxfId="37"/>
+    <tableColumn id="23" xr3:uid="{4CE3B16C-67F6-4DC2-9BB2-F8E09C5C8D74}" name="snmpv3_enabled" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{7E57634C-C61D-454F-83A9-CCC1D7A3E9A7}" name="snmp_server_ip" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{DA892339-1F60-44AE-B105-D466545319B6}" name="snmp_user" dataDxfId="34"/>
+    <tableColumn id="26" xr3:uid="{10EE6F10-8503-4A58-9CA0-8FB438354050}" name="snmp_auth_password" dataDxfId="33"/>
+    <tableColumn id="27" xr3:uid="{66121011-59AB-4D41-BDF5-22B7624358BE}" name="snmp_priv_password" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A99B9E14-0F60-413C-83C8-281F7E727FAD}" name="Tabell49" displayName="Tabell49" ref="A16:J20" dataDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A99B9E14-0F60-413C-83C8-281F7E727FAD}" name="Tabell49" displayName="Tabell49" ref="A18:J22" dataDxfId="31">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C939C381-1121-4153-B4EA-3E9AC4EFD622}" name="tunnel id" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{402267D7-3F42-4106-963C-A00D2C73C6A3}" name="vrf" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{4204F352-886B-4432-BF55-0DB72CCEC230}" name="ip address" dataDxfId="45">
-      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;H17&amp;"."&amp;$A$2</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{C939C381-1121-4153-B4EA-3E9AC4EFD622}" name="tunnel id" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{402267D7-3F42-4106-963C-A00D2C73C6A3}" name="vrf" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{4204F352-886B-4432-BF55-0DB72CCEC230}" name="ip address" dataDxfId="28">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E652E851-68C8-44CC-A804-D4A898A26E6B}" name="mask" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{1B6660E8-062A-4243-A879-B9BBE79D61B2}" name="source" dataDxfId="43">
+    <tableColumn id="4" xr3:uid="{E652E851-68C8-44CC-A804-D4A898A26E6B}" name="mask" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{1B6660E8-062A-4243-A879-B9BBE79D61B2}" name="source" dataDxfId="26">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{31E83213-6808-4B06-B3A2-334B8AEA93A6}" name="destination" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{548BE719-FE15-47C2-BD8C-E15155610E6F}" name="gre mode" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{AC2699E3-BB2E-4992-9A64-D04428D784DC}" name="network-id" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{911A5F49-374E-494E-9F87-E559E2AEA74A}" name="ipsec" dataDxfId="39">
-      <calculatedColumnFormula>'Site 1 (HUB)'!I17</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{31E83213-6808-4B06-B3A2-334B8AEA93A6}" name="destination" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{548BE719-FE15-47C2-BD8C-E15155610E6F}" name="gre mode" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{AC2699E3-BB2E-4992-9A64-D04428D784DC}" name="network-id" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{911A5F49-374E-494E-9F87-E559E2AEA74A}" name="ipsec" dataDxfId="22">
+      <calculatedColumnFormula>'Site 1 (HUB)'!I19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F9EF835F-35E0-4DBE-9B12-F79414F650B4}" name="ipsec key" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{F9EF835F-35E0-4DBE-9B12-F79414F650B4}" name="ipsec key" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DA31B441-D218-45B2-B01A-A4BBC8BD7979}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A22:H23" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DA31B441-D218-45B2-B01A-A4BBC8BD7979}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="20">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F434D49E-3876-49A2-911F-716DB0E46944}" name="site" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{F434D49E-3876-49A2-911F-716DB0E46944}" name="site" dataDxfId="19">
       <calculatedColumnFormula>$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96C6D5FD-CBC3-49D8-AFD4-9E1E09633C5A}" name="brukernavn" dataDxfId="35">
+    <tableColumn id="4" xr3:uid="{96C6D5FD-CBC3-49D8-AFD4-9E1E09633C5A}" name="brukernavn" dataDxfId="18">
       <calculatedColumnFormula>$D$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{038EE345-4494-4999-88D7-0BF36304D24C}" name="passord" dataDxfId="34">
+    <tableColumn id="5" xr3:uid="{038EE345-4494-4999-88D7-0BF36304D24C}" name="passord" dataDxfId="17">
       <calculatedColumnFormula>$E$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{770D33D1-BE1F-45C0-8F6C-2E9C2A15365F}" name="vty_lines" dataDxfId="33">
+    <tableColumn id="3" xr3:uid="{770D33D1-BE1F-45C0-8F6C-2E9C2A15365F}" name="vty_lines" dataDxfId="16">
       <calculatedColumnFormula>$F$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{87FFB71D-3185-4317-BD65-911279FF4E36}" name="secret" dataDxfId="32">
+    <tableColumn id="2" xr3:uid="{87FFB71D-3185-4317-BD65-911279FF4E36}" name="secret" dataDxfId="15">
       <calculatedColumnFormula>$G$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{13F65231-00AD-4279-9566-BCCC6B905C94}" name="etherchan_num" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{32F614C6-376B-4371-8715-7B2614BB4DBC}" name="span_mode" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{70D4C587-3B90-40C4-BB6C-9CC884BED451}" name="dot1x_vlans" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{13F65231-00AD-4279-9566-BCCC6B905C94}" name="etherchan_num" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{32F614C6-376B-4371-8715-7B2614BB4DBC}" name="span_mode" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{70D4C587-3B90-40C4-BB6C-9CC884BED451}" name="dot1x_vlans" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2987,19 +3016,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD1001"/>
+  <dimension ref="A1:AD1004"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
-    <col min="3" max="3" width="66" customWidth="1"/>
+    <col min="3" max="3" width="72.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="66" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="66" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="25.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" customWidth="1"/>
     <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="24" width="18" customWidth="1"/>
     <col min="26" max="26" width="16.44140625" bestFit="1" customWidth="1"/>
@@ -3398,171 +3427,162 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="8">
+        <v>40</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".0"</f>
+        <v>10.1.40.0</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <f t="shared" ref="E9" si="4">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".1"</f>
+        <v>10.1.40.1</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f t="shared" ref="G9" si="5">VALUE(LEFT(D9,FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+1)</f>
+        <v>10.1.40.1</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
+        <v>10.1.40.254</v>
+      </c>
+      <c r="I9" s="7">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="7">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7" t="str">
-        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B11</f>
-        <v>1.1.1.10</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" s="7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f t="shared" ref="C12:C14" si="4">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
-        <v>1.1.1.20</v>
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
+        <v>1.1.1.10</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1.30</v>
+        <f t="shared" ref="C13:C15" si="6">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
+        <v>1.1.1.20</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="7">
+        <v>30</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>1.1.1.30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B15" s="7">
         <v>40</v>
       </c>
-      <c r="C14" s="7" t="str">
-        <f t="shared" si="4"/>
+      <c r="C15" s="7" t="str">
+        <f t="shared" si="6"/>
         <v>1.1.1.40</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="7">
+        <v>40</v>
+      </c>
+      <c r="C16" s="7" t="str">
+        <f t="shared" ref="C16" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B16</f>
+        <v>1.1.1.40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="7" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H17&amp;"."&amp;$A$2</f>
-        <v>172.16.10.1</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="7" t="str">
-        <f>$C$2</f>
-        <v>1.1.1.0</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="2">
-        <v>10</v>
-      </c>
-      <c r="I17" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="7" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H18&amp;"."&amp;$A$2</f>
-        <v>172.16.20.1</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="7" t="str">
-        <f>$C$2</f>
-        <v>1.1.1.0</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="2">
-        <v>20</v>
-      </c>
-      <c r="I18" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" s="7" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
-        <v>172.16.30.1</v>
+        <v>172.16.10.1</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>50</v>
@@ -3576,7 +3596,7 @@
         <v>66</v>
       </c>
       <c r="H19" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I19" s="28" t="b">
         <v>1</v>
@@ -3585,14 +3605,14 @@
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="7" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
-        <v>172.16.40.1</v>
+        <v>172.16.20.1</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>50</v>
@@ -3606,201 +3626,270 @@
         <v>66</v>
       </c>
       <c r="H20" s="2">
+        <v>20</v>
+      </c>
+      <c r="I20" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="7" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H21&amp;"."&amp;$A$2</f>
+        <v>172.16.30.1</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="7" t="str">
+        <f>$C$2</f>
+        <v>1.1.1.0</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="2">
+        <v>30</v>
+      </c>
+      <c r="I21" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="7" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H22&amp;"."&amp;$A$2</f>
+        <v>172.16.40.1</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="7" t="str">
+        <f>$C$2</f>
+        <v>1.1.1.0</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="2">
         <v>40</v>
       </c>
-      <c r="I20" s="28" t="b">
+      <c r="I22" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-    </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="7" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H23&amp;"."&amp;$A$2</f>
+        <v>172.16.40.1</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="7" t="str">
+        <f>$C$2</f>
+        <v>1.1.1.0</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="2">
+        <v>40</v>
+      </c>
+      <c r="I23" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="28.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="26" spans="1:17" ht="28.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <f>$A$2</f>
         <v>1</v>
       </c>
-      <c r="B23" s="2" t="str">
+      <c r="B26" s="2" t="str">
         <f>$D$2</f>
         <v>admin</v>
       </c>
-      <c r="C23" s="2" t="str">
+      <c r="C26" s="2" t="str">
         <f>$E$2</f>
         <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
-      <c r="D23" s="2" t="str">
+      <c r="D26" s="2" t="str">
         <f>$F$2</f>
         <v>0 - 15</v>
       </c>
-      <c r="E23" s="2" t="str">
+      <c r="E26" s="2" t="str">
         <f>$G$2</f>
         <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F26" s="2">
         <v>2</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="H26" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="I23" s="35" cm="1">
-        <f t="array" ref="I23">Tabell5[ISP-VLAN]</f>
+      <c r="I26" s="35" cm="1">
+        <f t="array" ref="I26">Tabell5[ISP-VLAN]</f>
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B28" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D28" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E28" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G28" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H28" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I28" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J28" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="K28" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="L25" s="25" t="s">
+      <c r="L28" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q25" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <f>ROW()-25</f>
+    <row r="29" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <f>ROW()-28</f>
         <v>1</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B29" s="7">
         <f>$B$5</f>
         <v>10</v>
       </c>
-      <c r="C26" s="7" t="str">
-        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A26+1)</f>
+      <c r="C29" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</f>
         <v>10.1.10.2</v>
       </c>
-      <c r="D26" s="7" t="str">
+      <c r="D29" s="7" t="str">
         <f>$E$5</f>
         <v>10.1.10.1</v>
       </c>
-      <c r="E26" s="7" t="str">
+      <c r="E29" s="7" t="str">
         <f>$F$5</f>
         <v>255.255.255.0</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F29" s="7">
         <v>25</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G29" s="7">
         <v>1</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H29" s="10">
         <v>0</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I29" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="2">
-        <f>IF($A26=1,F26-G26-H26*$F$23-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="ERSPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</f>
+      <c r="K29" s="2">
+        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
         <v>21</v>
       </c>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-    </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-    </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
       <c r="O29" s="31"/>
@@ -4003,9 +4092,27 @@
       <c r="P57" s="31"/>
       <c r="Q57" s="31"/>
     </row>
-    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+    </row>
+    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M59" s="31"/>
+      <c r="N59" s="31"/>
+      <c r="O59" s="31"/>
+      <c r="P59" s="31"/>
+      <c r="Q59" s="31"/>
+    </row>
+    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M60" s="31"/>
+      <c r="N60" s="31"/>
+      <c r="O60" s="31"/>
+      <c r="P60" s="31"/>
+      <c r="Q60" s="31"/>
+    </row>
     <row r="61" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4947,13 +5054,16 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="10">
-    <dataValidation type="list" sqref="G23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="G26" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="N2" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"OFF,STRICT,LOOSE"</formula1>
@@ -4961,10 +5071,10 @@
     <dataValidation type="list" sqref="Q2" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M26:N57 V2 R2:S2" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" sqref="M29:N60 V2 R2:S2" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"OLD,NEW"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T2 O26:O57" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" sqref="T2 O29:O60" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="U2" xr:uid="{00000000-0002-0000-0000-000006000000}">
@@ -4973,10 +5083,10 @@
     <dataValidation type="list" sqref="W2" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"IKEV1,IKEV2"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="X2 P26:P57" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" sqref="X2 P29:P60" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"AUTO,5,8,9"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Y2 Q26:Q57" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" sqref="Y2 Q29:Q60" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4994,7 +5104,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B45EDC77-8BBB-4908-955E-B9316A6BE4D3}">
-  <dimension ref="A1:AA995"/>
+  <dimension ref="A1:AA998"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.44140625" style="12" customWidth="1"/>
@@ -5222,7 +5332,7 @@
         <v>46</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>48</v>
@@ -5386,29 +5496,49 @@
       <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="A9" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="8">
+        <v>50</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f t="shared" ref="D9" si="3">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".0"</f>
+        <v>10.2.50.0</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <f t="shared" ref="E9" si="4">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".1"</f>
+        <v>10.2.50.1</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f t="shared" ref="G9" si="5">VALUE(LEFT(D9,FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+1)</f>
+        <v>10.2.50.1</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
+        <v>10.2.50.254</v>
+      </c>
+      <c r="I9" s="7">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
       <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>56</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
@@ -5420,15 +5550,14 @@
       <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="7">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7" t="str">
-        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B11</f>
-        <v>2.2.2.10</v>
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -5442,14 +5571,14 @@
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" s="7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f t="shared" ref="C12:C14" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
-        <v>2.2.2.20</v>
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
+        <v>2.2.2.10</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -5463,14 +5592,14 @@
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>2.2.2.30</v>
+        <f t="shared" ref="C13:C15" si="6">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
+        <v>2.2.2.20</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -5484,14 +5613,14 @@
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C14" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>2.2.2.40</v>
+        <f t="shared" si="6"/>
+        <v>2.2.2.30</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -5503,117 +5632,97 @@
       <c r="K14"/>
       <c r="L14" s="12"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="7">
+        <v>40</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>2.2.2.40</v>
+      </c>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15" s="12"/>
+    </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="12" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H17&amp;"."&amp;$A$2</f>
-        <v>172.16.10.2</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="A16" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="7">
         <v>50</v>
       </c>
-      <c r="E17" s="12" t="str">
-        <f t="shared" ref="E17:E20" si="4">$C$2</f>
-        <v>2.2.2.0</v>
-      </c>
-      <c r="F17"/>
-      <c r="G17" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="12">
-        <v>10</v>
-      </c>
-      <c r="I17" s="29" t="b">
-        <f>'Site 1 (HUB)'!I17</f>
-        <v>1</v>
-      </c>
-      <c r="J17"/>
-    </row>
+      <c r="C16" s="43" t="str">
+        <f t="shared" ref="C16" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B16</f>
+        <v>2.2.2.50</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="12" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H18&amp;"."&amp;$A$2</f>
-        <v>172.16.20.2</v>
+        <v>38</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v>2.2.2.0</v>
-      </c>
-      <c r="F18"/>
+        <v>43</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="G18" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="12">
-        <v>20</v>
-      </c>
-      <c r="I18" s="29" t="b" cm="1">
-        <f>'Site 1 (HUB)'!I18</f>
-        <v>0</v>
-      </c>
-      <c r="J18"/>
+        <v>61</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" s="12" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
-        <v>172.16.30.2</v>
+        <v>172.16.10.2</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E19:E23" si="8">$C$2</f>
         <v>2.2.2.0</v>
       </c>
       <c r="F19"/>
@@ -5621,7 +5730,7 @@
         <v>66</v>
       </c>
       <c r="H19" s="12">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I19" s="29" t="b">
         <f>'Site 1 (HUB)'!I19</f>
@@ -5631,20 +5740,20 @@
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="12" t="str">
-        <f t="shared" ref="C20" si="5">172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
-        <v>172.16.40.2</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
+        <v>172.16.20.2</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2.2.2.0</v>
       </c>
       <c r="F20"/>
@@ -5652,224 +5761,257 @@
         <v>66</v>
       </c>
       <c r="H20" s="12">
+        <v>20</v>
+      </c>
+      <c r="I20" s="29" t="b" cm="1">
+        <f>'Site 1 (HUB)'!I20</f>
+        <v>0</v>
+      </c>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="12" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H21&amp;"."&amp;$A$2</f>
+        <v>172.16.30.2</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="12">
+        <v>30</v>
+      </c>
+      <c r="I21" s="29" t="b">
+        <f>'Site 1 (HUB)'!I21</f>
+        <v>1</v>
+      </c>
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="12" t="str">
+        <f t="shared" ref="C22" si="9">172&amp;"."&amp;16&amp;"."&amp;H22&amp;"."&amp;$A$2</f>
+        <v>172.16.40.2</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="12">
         <v>40</v>
       </c>
-      <c r="I20" s="29" t="b">
-        <f>'Site 1 (HUB)'!I20</f>
+      <c r="I22" s="29" t="b">
+        <f>'Site 1 (HUB)'!I22</f>
         <v>1</v>
       </c>
-      <c r="J20"/>
-    </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="12" t="str">
+        <f t="shared" ref="C23" si="10">172&amp;"."&amp;16&amp;"."&amp;H23&amp;"."&amp;$A$2</f>
+        <v>172.16.40.2</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="12">
+        <v>40</v>
+      </c>
+      <c r="I23" s="29">
+        <f>'Site 1 (HUB)'!I24</f>
         <v>0</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="J23"/>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E25" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F25" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
         <f>$A$2</f>
         <v>2</v>
       </c>
-      <c r="B23" s="12" t="str">
+      <c r="B26" s="12" t="str">
         <f>$D$2</f>
         <v>admin</v>
       </c>
-      <c r="C23" s="12" t="str">
+      <c r="C26" s="12" t="str">
         <f>$E$2</f>
         <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
-      <c r="D23" s="12" t="str">
+      <c r="D26" s="12" t="str">
         <f>$F$2</f>
         <v>0 - 15</v>
       </c>
-      <c r="E23" s="12" t="str">
+      <c r="E26" s="12" t="str">
         <f>$G$2</f>
         <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F26" s="12">
         <v>2</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="30" t="s">
+      <c r="G26" s="2"/>
+      <c r="H26" s="30" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B28" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D28" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E28" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G28" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H28" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I28" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J28" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="K28" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="L25" s="25" t="s">
+      <c r="L28" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q25" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <f>ROW()-25</f>
+    <row r="29" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <f t="shared" ref="A29:A30" si="11">ROW()-28</f>
         <v>1</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B29" s="7">
         <f>$B$5</f>
         <v>10</v>
       </c>
-      <c r="C26" s="7" t="str">
-        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A26+1)</f>
+      <c r="C29" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</f>
         <v>10.2.10.2</v>
       </c>
-      <c r="D26" s="7" t="str">
+      <c r="D29" s="7" t="str">
         <f>$E$5</f>
         <v>10.2.10.1</v>
       </c>
-      <c r="E26" s="7" t="str">
+      <c r="E29" s="7" t="str">
         <f>$F$5</f>
         <v>255.255.255.0</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F29" s="7">
         <v>49</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G29" s="7">
         <v>1</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H29" s="10">
         <v>1</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I29" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K26" s="2">
-        <f>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</f>
+      <c r="K29" s="2">
+        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
         <v>44</v>
       </c>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-    </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <f>ROW()-25</f>
-        <v>2</v>
-      </c>
-      <c r="B27" s="7">
-        <f>$B$5</f>
-        <v>10</v>
-      </c>
-      <c r="C27" s="7" t="str">
-        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A27+1)</f>
-        <v>10.2.10.3</v>
-      </c>
-      <c r="D27" s="7" t="str">
-        <f>$E$5</f>
-        <v>10.2.10.1</v>
-      </c>
-      <c r="E27" s="7" t="str">
-        <f>$F$5</f>
-        <v>255.255.255.0</v>
-      </c>
-      <c r="F27" s="7">
-        <v>11</v>
-      </c>
-      <c r="G27" s="7">
-        <v>1</v>
-      </c>
-      <c r="H27" s="7">
-        <v>0</v>
-      </c>
-      <c r="I27" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" s="2">
-        <f>IF($A27=1,F27-G27-H27*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F27-G27-(1+H27)*$F$23-1)</f>
-        <v>7</v>
-      </c>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-    </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
       <c r="O29" s="31"/>
@@ -5877,6 +6019,45 @@
       <c r="Q29" s="31"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="B30" s="7">
+        <f>$B$5</f>
+        <v>10</v>
+      </c>
+      <c r="C30" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A30+1)</f>
+        <v>10.2.10.3</v>
+      </c>
+      <c r="D30" s="7" t="str">
+        <f>$E$5</f>
+        <v>10.2.10.1</v>
+      </c>
+      <c r="E30" s="7" t="str">
+        <f>$F$5</f>
+        <v>255.255.255.0</v>
+      </c>
+      <c r="F30" s="7">
+        <v>11</v>
+      </c>
+      <c r="G30" s="7">
+        <v>1</v>
+      </c>
+      <c r="H30" s="7">
+        <v>0</v>
+      </c>
+      <c r="I30" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="2">
+        <f>IF($A30=1,F30-G30-H30*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F30-G30-(1+H30)*$F$26-1)</f>
+        <v>7</v>
+      </c>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
       <c r="O30" s="31"/>
@@ -6072,9 +6253,27 @@
       <c r="P57" s="31"/>
       <c r="Q57" s="31"/>
     </row>
-    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+    </row>
+    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M59" s="31"/>
+      <c r="N59" s="31"/>
+      <c r="O59" s="31"/>
+      <c r="P59" s="31"/>
+      <c r="Q59" s="31"/>
+    </row>
+    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M60" s="31"/>
+      <c r="N60" s="31"/>
+      <c r="O60" s="31"/>
+      <c r="P60" s="31"/>
+      <c r="Q60" s="31"/>
+    </row>
     <row r="61" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7010,12 +7209,15 @@
     <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" sqref="V2 Q26:Q57" xr:uid="{39D8B1B3-368B-4AC5-A514-11645F40D89B}">
+    <dataValidation type="list" sqref="V2 Q29:Q60" xr:uid="{39D8B1B3-368B-4AC5-A514-11645F40D89B}">
       <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="U2 P26:P57" xr:uid="{40E87254-C5D0-4454-8C47-5100945ED78A}">
+    <dataValidation type="list" sqref="U2 P29:P60" xr:uid="{40E87254-C5D0-4454-8C47-5100945ED78A}">
       <formula1>"AUTO,5,8,9"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="T2" xr:uid="{D82DFD41-8835-4B4F-94E1-F31DD76B81DE}">
@@ -7024,37 +7226,38 @@
     <dataValidation type="list" sqref="R2" xr:uid="{F047568E-0FF5-4EA3-A7BF-468F3B62A5DC}">
       <formula1>"CLASSIC,NAMED"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Q2 O26:O57" xr:uid="{8398B055-E1AD-474F-AA4B-7C530D80F4B4}">
+    <dataValidation type="list" sqref="Q2 O29:O60" xr:uid="{8398B055-E1AD-474F-AA4B-7C530D80F4B4}">
       <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="O2:P2 S2 M26:N57" xr:uid="{3BA14544-E617-4EAB-8056-F1ADFAEBFA4A}">
+    <dataValidation type="list" sqref="O2:P2 S2 M29:N60" xr:uid="{3BA14544-E617-4EAB-8056-F1ADFAEBFA4A}">
       <formula1>"OLD,NEW"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26:I27" xr:uid="{5FB8B7A2-FDEC-49C6-A037-9F36974649E1}">
-      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29:I30" xr:uid="{5FB8B7A2-FDEC-49C6-A037-9F36974649E1}">
+      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="L2" xr:uid="{1CFE3BAF-8D34-4CA8-BE94-49E44A9437C4}">
       <formula1>"OFF,STRICT,LOOSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G23" xr:uid="{194DE05B-70E4-4CED-BEE9-B1A159236E6A}">
+    <dataValidation type="list" sqref="G26" xr:uid="{194DE05B-70E4-4CED-BEE9-B1A159236E6A}">
       <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="6">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AA994"/>
+  <dimension ref="A1:AA998"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.44140625" style="12" customWidth="1"/>
@@ -7282,7 +7485,7 @@
         <v>46</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>48</v>
@@ -7310,7 +7513,7 @@
         <v>50</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" ref="G5:G8" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
+        <f t="shared" ref="G5:G9" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
         <v>10.3.10.1</v>
       </c>
       <c r="H5" s="7" t="str">
@@ -7338,11 +7541,11 @@
         <v>0</v>
       </c>
       <c r="D6" s="7" t="str">
-        <f t="shared" ref="D6:D8" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
+        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
         <v>10.3.20.0</v>
       </c>
       <c r="E6" s="7" t="str">
-        <f t="shared" ref="E6:E8" si="2">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
+        <f t="shared" ref="E6:E9" si="2">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
         <v>10.3.20.1</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -7446,29 +7649,49 @@
       <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="A9" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="8">
+        <v>50</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>10.3.50.0</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>10.3.50.1</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.3.50.1</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
+        <v>10.3.50.254</v>
+      </c>
+      <c r="I9" s="7">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
       <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>56</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
@@ -7480,15 +7703,14 @@
       <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="7">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7" t="str">
-        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B11</f>
-        <v>3.3.3.10</v>
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -7502,14 +7724,14 @@
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" s="7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f t="shared" ref="C12:C14" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
-        <v>3.3.3.20</v>
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
+        <v>3.3.3.10</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -7523,14 +7745,14 @@
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>3.3.3.30</v>
+        <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
+        <v>3.3.3.20</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -7544,14 +7766,14 @@
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C14" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>3.3.3.40</v>
+        <v>3.3.3.30</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -7563,117 +7785,97 @@
       <c r="K14"/>
       <c r="L14" s="12"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="7">
+        <v>40</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>3.3.3.40</v>
+      </c>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15" s="12"/>
+    </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="12" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H17&amp;"."&amp;$A$2</f>
-        <v>172.16.10.3</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="A16" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="7">
         <v>50</v>
       </c>
-      <c r="E17" s="12" t="str">
-        <f t="shared" ref="E17:E20" si="4">$C$2</f>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F17"/>
-      <c r="G17" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="12">
-        <v>10</v>
-      </c>
-      <c r="I17" s="29" t="b">
-        <f>'Site 1 (HUB)'!I17</f>
-        <v>1</v>
-      </c>
-      <c r="J17"/>
-    </row>
+      <c r="C16" s="43" t="str">
+        <f t="shared" si="3"/>
+        <v>3.3.3.50</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="12" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H18&amp;"."&amp;$A$2</f>
-        <v>172.16.20.3</v>
+        <v>38</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F18"/>
+        <v>43</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="G18" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="12">
-        <v>20</v>
-      </c>
-      <c r="I18" s="29" t="b" cm="1">
-        <f>'Site 1 (HUB)'!I18</f>
-        <v>0</v>
-      </c>
-      <c r="J18"/>
+        <v>61</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" s="12" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
-        <v>172.16.30.3</v>
+        <v>172.16.10.3</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E19:E23" si="4">$C$2</f>
         <v>3.3.3.0</v>
       </c>
       <c r="F19"/>
@@ -7681,7 +7883,7 @@
         <v>66</v>
       </c>
       <c r="H19" s="12">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I19" s="29" t="b">
         <f>'Site 1 (HUB)'!I19</f>
@@ -7691,14 +7893,14 @@
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="12" t="str">
-        <f t="shared" ref="C20" si="5">172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
-        <v>172.16.40.3</v>
+        <f>172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
+        <v>172.16.20.3</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>50</v>
@@ -7712,185 +7914,257 @@
         <v>66</v>
       </c>
       <c r="H20" s="12">
+        <v>20</v>
+      </c>
+      <c r="I20" s="29" t="b" cm="1">
+        <f>'Site 1 (HUB)'!I20</f>
+        <v>0</v>
+      </c>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="12" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H21&amp;"."&amp;$A$2</f>
+        <v>172.16.30.3</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="12">
+        <v>30</v>
+      </c>
+      <c r="I21" s="29" t="b">
+        <f>'Site 1 (HUB)'!I21</f>
+        <v>1</v>
+      </c>
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="12" t="str">
+        <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;H22&amp;"."&amp;$A$2</f>
+        <v>172.16.40.3</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="12">
         <v>40</v>
       </c>
-      <c r="I20" s="29" t="b">
-        <f>'Site 1 (HUB)'!I20</f>
+      <c r="I22" s="29" t="b">
+        <f>'Site 1 (HUB)'!I22</f>
         <v>1</v>
       </c>
-      <c r="J20"/>
-    </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>172.16.40.3</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="12">
+        <v>40</v>
+      </c>
+      <c r="I23" s="29">
+        <f>'Site 1 (HUB)'!I24</f>
         <v>0</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="J23"/>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E25" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F25" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
         <f>$A$2</f>
         <v>3</v>
       </c>
-      <c r="B23" s="12" t="str">
+      <c r="B26" s="12" t="str">
         <f>$D$2</f>
         <v>admin</v>
       </c>
-      <c r="C23" s="12" t="str">
+      <c r="C26" s="12" t="str">
         <f>$E$2</f>
         <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
-      <c r="D23" s="12" t="str">
+      <c r="D26" s="12" t="str">
         <f>$F$2</f>
         <v>0 - 15</v>
       </c>
-      <c r="E23" s="12" t="str">
+      <c r="E26" s="12" t="str">
         <f>$G$2</f>
         <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F26" s="12">
         <v>2</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="30" t="s">
+      <c r="G26" s="2"/>
+      <c r="H26" s="30" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B28" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D28" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E28" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G28" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H28" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I28" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J28" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="K28" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="L25" s="25" t="s">
+      <c r="L28" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q25" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <f>ROW()-25</f>
+    <row r="29" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <f t="shared" ref="A29:A30" si="6">ROW()-28</f>
         <v>1</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B29" s="7">
         <f>$B$5</f>
         <v>10</v>
       </c>
-      <c r="C26" s="7" t="str">
-        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A26+1)</f>
+      <c r="C29" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</f>
         <v>10.3.10.2</v>
       </c>
-      <c r="D26" s="7" t="str">
+      <c r="D29" s="7" t="str">
         <f>$E$5</f>
         <v>10.3.10.1</v>
       </c>
-      <c r="E26" s="7" t="str">
+      <c r="E29" s="7" t="str">
         <f>$F$5</f>
         <v>255.255.255.0</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F29" s="7">
         <v>49</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G29" s="7">
         <v>1</v>
       </c>
-      <c r="H26" s="10">
-        <v>0</v>
-      </c>
-      <c r="I26" s="7" t="s">
+      <c r="H29" s="10">
+        <v>1</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K26" s="2">
-        <f>IF($A26=1,F26-G26-H26*$F$23-2-IF(OR(UPPER($G$23)="SPAN",UPPER($G$23)="RSPAN"),1,0),F26-G26-(1+H26)*$F$23-1)</f>
-        <v>46</v>
-      </c>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-    </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-    </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K29" s="2">
+        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <v>44</v>
+      </c>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
       <c r="O29" s="31"/>
@@ -7898,6 +8172,45 @@
       <c r="Q29" s="31"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="B30" s="7">
+        <f>$B$5</f>
+        <v>10</v>
+      </c>
+      <c r="C30" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A30+1)</f>
+        <v>10.3.10.3</v>
+      </c>
+      <c r="D30" s="7" t="str">
+        <f>$E$5</f>
+        <v>10.3.10.1</v>
+      </c>
+      <c r="E30" s="7" t="str">
+        <f>$F$5</f>
+        <v>255.255.255.0</v>
+      </c>
+      <c r="F30" s="7">
+        <v>11</v>
+      </c>
+      <c r="G30" s="7">
+        <v>1</v>
+      </c>
+      <c r="H30" s="7">
+        <v>0</v>
+      </c>
+      <c r="I30" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="2">
+        <f>IF($A30=1,F30-G30-H30*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F30-G30-(1+H30)*$F$26-1)</f>
+        <v>7</v>
+      </c>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
       <c r="O30" s="31"/>
@@ -8086,10 +8399,34 @@
       <c r="P56" s="31"/>
       <c r="Q56" s="31"/>
     </row>
-    <row r="57" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M57" s="31"/>
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+    </row>
+    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+    </row>
+    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M59" s="31"/>
+      <c r="N59" s="31"/>
+      <c r="O59" s="31"/>
+      <c r="P59" s="31"/>
+      <c r="Q59" s="31"/>
+    </row>
+    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M60" s="31"/>
+      <c r="N60" s="31"/>
+      <c r="O60" s="31"/>
+      <c r="P60" s="31"/>
+      <c r="Q60" s="31"/>
+    </row>
     <row r="61" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9024,34 +9361,38 @@
     <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="9">
-    <dataValidation type="list" sqref="G23" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations disablePrompts="1" count="9">
+    <dataValidation type="list" sqref="G26" xr:uid="{C3ECF952-F6F6-411D-8935-CDC103B5D4EC}">
       <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="L2" xr:uid="{8E5E9B82-B6E9-4F50-802A-79C5281D4523}">
       <formula1>"OFF,STRICT,LOOSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="O2:P2 S2 M26:N56" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" sqref="O2:P2 S2 M29:N60" xr:uid="{DC4FD792-C951-42B9-9398-EE752636FA33}">
       <formula1>"OLD,NEW"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Q2 O26:O56" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" sqref="Q2 O29:O60" xr:uid="{C7885E03-9EAB-4488-B2C3-6DDA152BCD1E}">
       <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="R2" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation type="list" sqref="R2" xr:uid="{F0E34391-1AAD-46B7-8AB3-1044AED733C6}">
       <formula1>"CLASSIC,NAMED"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T2" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="list" sqref="T2" xr:uid="{B8A0B74E-656E-434E-A62B-D696F296B01C}">
       <formula1>"IKEV1,IKEV2"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="U2 P26:P56" xr:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation type="list" sqref="U2 P29:P60" xr:uid="{D06C47C8-040C-442D-B082-B0E002F6446A}">
       <formula1>"AUTO,5,8,9"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="V2 Q26:Q56" xr:uid="{00000000-0002-0000-0100-000008000000}">
+    <dataValidation type="list" sqref="V2 Q29:Q60" xr:uid="{2B15C247-115A-480F-9C6D-9FE8FF7A1C49}">
       <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I26" xr:uid="{67E4AE03-2DF0-440B-B572-B891D49BFDE5}">
-      <formula1>IF(I26="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I26,"-"),"."))&lt;=K26)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29:I30" xr:uid="{076D1031-AA49-412C-8A13-87A449FBC603}">
+      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9356,6 +9697,21 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
       <c r="G14" t="s">
         <v>111</v>
       </c>
@@ -9373,16 +9729,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="A2:A200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="A2:A201" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"MGMT,INET,UNET,PA,MONITORING"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B2:B200" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="B2:B201" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"MGMT,INET,UNET,PA,MONITORING,INTERNET,ANY,DNS,DHCP,TACACS,SYSLOG,SELF"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C2:C200" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" sqref="C2:C201" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"ip,tcp,udp,icmp,gre,esp,ah"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E200" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="list" sqref="E2:E201" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"permit,deny"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7604A2-3663-42E4-8C01-017B85CE52F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2191D201-465A-438B-BCC1-E858E61FAFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="133">
   <si>
     <t>site</t>
   </si>
@@ -277,9 +277,6 @@
   </si>
   <si>
     <t>dot1x_vlans</t>
-  </si>
-  <si>
-    <t>20,30</t>
   </si>
   <si>
     <t>SW</t>
@@ -657,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -778,7 +775,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -791,6 +787,21 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -798,643 +809,643 @@
   <dxfs count="171">
     <dxf>
       <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <sz val="11"/>
         <color auto="1"/>
         <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
@@ -2342,29 +2353,29 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D32D18C4-0B05-425E-B28E-67E8EEF86C01}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A28:Q30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D32D18C4-0B05-425E-B28E-67E8EEF86C01}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A28:Q29" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{3D2619F9-8A27-48B4-BBAD-F8DAD24B7058}" name="SW" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{3D2619F9-8A27-48B4-BBAD-F8DAD24B7058}" name="SW" dataDxfId="12">
       <calculatedColumnFormula>ROW()-28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{79D48293-3CC1-4FC8-B959-C76EC31AF05A}" name="MGMT Vlan" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{79D48293-3CC1-4FC8-B959-C76EC31AF05A}" name="MGMT Vlan" dataDxfId="11">
       <calculatedColumnFormula>$B$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{636012CC-2311-45D4-B0A3-CBE1DDB288EA}" name="MGMT ip" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{636012CC-2311-45D4-B0A3-CBE1DDB288EA}" name="MGMT ip" dataDxfId="10">
       <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{57B036DD-2EC2-46AB-BA82-15C2E4251EE3}" name="gateway" dataDxfId="8">
+    <tableColumn id="4" xr3:uid="{57B036DD-2EC2-46AB-BA82-15C2E4251EE3}" name="gateway" dataDxfId="9">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D16308A-64E5-4F82-9997-B8BD8FE03B86}" name="mask" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{6D16308A-64E5-4F82-9997-B8BD8FE03B86}" name="mask" dataDxfId="8">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{10263F16-185C-4388-8A92-6BC4CA0E07C5}" name="num_ports_tot" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{337036FB-EC4A-4A8B-A2D4-886EF58ACF98}" name="skiped_ports" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{75ED65B8-97AC-498A-9CF3-0A234BF7E9F1}" name="num_downlink" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{D2EB23FE-1E37-4D17-B4EC-11CAC9B6F0DC}" name="vlan-antall" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{0815D94A-1C82-4867-98BC-98ABBA28ECDE}" name="intf_prefix" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{CDF41783-F241-44AB-837D-97EDFE6911D4}" name="num_port_ledig" dataDxfId="1">
+    <tableColumn id="10" xr3:uid="{10263F16-185C-4388-8A92-6BC4CA0E07C5}" name="num_ports_tot" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{337036FB-EC4A-4A8B-A2D4-886EF58ACF98}" name="skiped_ports" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{75ED65B8-97AC-498A-9CF3-0A234BF7E9F1}" name="num_downlink" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{D2EB23FE-1E37-4D17-B4EC-11CAC9B6F0DC}" name="vlan-antall" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{0815D94A-1C82-4867-98BC-98ABBA28ECDE}" name="intf_prefix" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{CDF41783-F241-44AB-837D-97EDFE6911D4}" name="num_port_ledig" dataDxfId="2">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{AACD1EB8-91AF-4962-8481-F05F6073247E}" name="MONITORING ip"/>
@@ -2397,7 +2408,7 @@
     <tableColumn id="8" xr3:uid="{09FF5408-B542-4803-BB81-19C6D96455ED}" name="address max">
       <calculatedColumnFormula>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1C2CE40E-C587-4306-B04C-05E7E830B912}" name="antall-res" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{1C2CE40E-C587-4306-B04C-05E7E830B912}" name="antall-res" dataDxfId="1"/>
     <tableColumn id="10" xr3:uid="{062A0975-F29C-4725-993D-1C745C38968F}" name=" "/>
     <tableColumn id="11" xr3:uid="{E9F272DB-833F-4003-8FE1-C3489DCBD223}" name="pri-1-10"/>
   </tableColumns>
@@ -2406,7 +2417,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{137249B9-B569-4AB4-A5F4-44E14EC73E12}" name="Tabell7715" displayName="Tabell7715" ref="A11:C15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{137249B9-B569-4AB4-A5F4-44E14EC73E12}" name="Tabell7715" displayName="Tabell7715" ref="A11:C16">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3A3EB178-6BB6-4F25-BFF2-BC4D427D60C7}" name="vrf"/>
     <tableColumn id="3" xr3:uid="{00063F96-3CCE-4FBF-AEA1-0FEA482EE82B}" name="loopback"/>
@@ -2466,7 +2477,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47444F68-52DD-4020-A8C3-121097047CE4}" name="Tabell493" displayName="Tabell493" ref="A18:J22" dataDxfId="142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47444F68-52DD-4020-A8C3-121097047CE4}" name="Tabell493" displayName="Tabell493" ref="A18:J23" dataDxfId="142">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{55B6356B-AFF1-4386-837E-122F110FE048}" name="tunnel id" dataDxfId="141"/>
     <tableColumn id="2" xr3:uid="{B5627186-AB74-4D83-9392-91908D53F7BB}" name="vrf" dataDxfId="140"/>
@@ -2606,7 +2617,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabell6" displayName="Tabell6" ref="A4:K8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabell6" displayName="Tabell6" ref="A4:K9">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="vrf"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="vlan"/>
@@ -2634,7 +2645,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabell7" displayName="Tabell7" ref="A11:C15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabell7" displayName="Tabell7" ref="A11:C16">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="vrf"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="loopback"/>
@@ -2647,7 +2658,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabell8" displayName="Tabell8" ref="A18:J22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabell8" displayName="Tabell8" ref="A18:J23">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="tunnel id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="vrf"/>
@@ -2680,8 +2691,8 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="76"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="75"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="72">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="73">
       <calculatedColumnFormula array="1">Tabell5[ISP-VLAN]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2692,28 +2703,28 @@
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:Q29" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="71">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="72">
       <calculatedColumnFormula>ROW()-28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="69">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="70">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="68">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="69">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="67">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="68">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="62"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="61">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="67"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="62">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="60"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="61"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="tacacs_syntax"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="radius_syntax"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="dot1x_syntax"/>
@@ -2725,97 +2736,97 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51BF1746-4E83-4B5C-8E47-1B33E5F0C823}" name="Tabell18" displayName="Tabell18" ref="A1:AA2" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51BF1746-4E83-4B5C-8E47-1B33E5F0C823}" name="Tabell18" displayName="Tabell18" ref="A1:AA2" dataDxfId="60">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{F301071E-AB49-411D-B862-3D5F1A8652F4}" name="site" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{28087ADC-D839-428A-B3B6-5D33053FC989}" name="intf_prefix" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{E07A6BD4-5C25-4907-8DBF-B7CD7A55F1D8}" name="router-id" dataDxfId="56">
+    <tableColumn id="1" xr3:uid="{F301071E-AB49-411D-B862-3D5F1A8652F4}" name="site" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{28087ADC-D839-428A-B3B6-5D33053FC989}" name="intf_prefix" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{E07A6BD4-5C25-4907-8DBF-B7CD7A55F1D8}" name="router-id" dataDxfId="57">
       <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E5D534F2-DADF-4E06-844E-EFC868A109BF}" name="brukernavn" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{8E37AE50-BD24-4C9E-97D1-6B548927DBB7}" name="passord" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{0A3407AA-8EBE-4074-85F9-778319C50E4E}" name="vty_lines" dataDxfId="53"/>
-    <tableColumn id="7" xr3:uid="{0E482BA6-C79D-40DB-B45E-FDC671702D74}" name="secret" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{C39694E5-0D09-45FB-A48D-8E9A8C91CA0E}" name="tacacs_key" dataDxfId="51">
+    <tableColumn id="4" xr3:uid="{E5D534F2-DADF-4E06-844E-EFC868A109BF}" name="brukernavn" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{8E37AE50-BD24-4C9E-97D1-6B548927DBB7}" name="passord" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{0A3407AA-8EBE-4074-85F9-778319C50E4E}" name="vty_lines" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{0E482BA6-C79D-40DB-B45E-FDC671702D74}" name="secret" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{C39694E5-0D09-45FB-A48D-8E9A8C91CA0E}" name="tacacs_key" dataDxfId="52">
       <calculatedColumnFormula>'Site 1 (HUB)'!I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{44EB3B31-5D13-48ED-A202-643DB3DE780D}" name="dns_servers" dataDxfId="50"/>
-    <tableColumn id="10" xr3:uid="{97E12567-6CA3-4115-A196-2529D7160615}" name="tacacs_server_ip" dataDxfId="49">
+    <tableColumn id="9" xr3:uid="{44EB3B31-5D13-48ED-A202-643DB3DE780D}" name="dns_servers" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{97E12567-6CA3-4115-A196-2529D7160615}" name="tacacs_server_ip" dataDxfId="50">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0346B8E5-A202-466C-AB4B-67EDD69B81A1}" name="syslog_server_ip" dataDxfId="48">
+    <tableColumn id="11" xr3:uid="{0346B8E5-A202-466C-AB4B-67EDD69B81A1}" name="syslog_server_ip" dataDxfId="49">
       <calculatedColumnFormula>'Site 1 (HUB)'!M2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE86801E-B0D0-4B58-832A-86AC77A7EC9A}" name="urpf_mode" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{5AAC65E5-8130-4C09-99B3-54C834DEE5C1}" name="radius_server_ip" dataDxfId="46">
+    <tableColumn id="12" xr3:uid="{EE86801E-B0D0-4B58-832A-86AC77A7EC9A}" name="urpf_mode" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{5AAC65E5-8130-4C09-99B3-54C834DEE5C1}" name="radius_server_ip" dataDxfId="47">
       <calculatedColumnFormula>'Site 1 (HUB)'!O2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1C900422-8FD8-4B49-B19A-47F4CE877466}" name="radius_key" dataDxfId="45">
+    <tableColumn id="15" xr3:uid="{1C900422-8FD8-4B49-B19A-47F4CE877466}" name="radius_key" dataDxfId="46">
       <calculatedColumnFormula>'Site 1 (HUB)'!P2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{AD662EC0-7940-4F3A-8F56-38E0BAEE7E2B}" name="tacacs_syntax" dataDxfId="44"/>
-    <tableColumn id="16" xr3:uid="{103CB279-D718-4AF9-A977-B976A8B36356}" name="radius_syntax" dataDxfId="43"/>
-    <tableColumn id="17" xr3:uid="{3496AD74-0539-4463-997F-A1CA64512F54}" name="dot1x_syntax" dataDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{F8B1DCD1-84B0-4090-BDAB-AD6FA5328F3C}" name="eigrp_syntax" dataDxfId="41"/>
-    <tableColumn id="19" xr3:uid="{E8281F74-01EE-4CFD-8DF1-C429390E1E04}" name="vrf_syntax" dataDxfId="40"/>
-    <tableColumn id="20" xr3:uid="{9FA158AF-3041-42DD-9BB3-CA83FCDE6CA1}" name="ike_version" dataDxfId="39"/>
-    <tableColumn id="21" xr3:uid="{045B3C14-6117-44CA-9A5A-D8BA1860F47E}" name="secret_type" dataDxfId="38"/>
-    <tableColumn id="22" xr3:uid="{3829C8E8-1959-4691-AF37-5B45456BC812}" name="trunk_encapsulation" dataDxfId="37"/>
-    <tableColumn id="23" xr3:uid="{4CE3B16C-67F6-4DC2-9BB2-F8E09C5C8D74}" name="snmpv3_enabled" dataDxfId="36"/>
-    <tableColumn id="24" xr3:uid="{7E57634C-C61D-454F-83A9-CCC1D7A3E9A7}" name="snmp_server_ip" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{DA892339-1F60-44AE-B105-D466545319B6}" name="snmp_user" dataDxfId="34"/>
-    <tableColumn id="26" xr3:uid="{10EE6F10-8503-4A58-9CA0-8FB438354050}" name="snmp_auth_password" dataDxfId="33"/>
-    <tableColumn id="27" xr3:uid="{66121011-59AB-4D41-BDF5-22B7624358BE}" name="snmp_priv_password" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{AD662EC0-7940-4F3A-8F56-38E0BAEE7E2B}" name="tacacs_syntax" dataDxfId="45"/>
+    <tableColumn id="16" xr3:uid="{103CB279-D718-4AF9-A977-B976A8B36356}" name="radius_syntax" dataDxfId="44"/>
+    <tableColumn id="17" xr3:uid="{3496AD74-0539-4463-997F-A1CA64512F54}" name="dot1x_syntax" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{F8B1DCD1-84B0-4090-BDAB-AD6FA5328F3C}" name="eigrp_syntax" dataDxfId="42"/>
+    <tableColumn id="19" xr3:uid="{E8281F74-01EE-4CFD-8DF1-C429390E1E04}" name="vrf_syntax" dataDxfId="41"/>
+    <tableColumn id="20" xr3:uid="{9FA158AF-3041-42DD-9BB3-CA83FCDE6CA1}" name="ike_version" dataDxfId="40"/>
+    <tableColumn id="21" xr3:uid="{045B3C14-6117-44CA-9A5A-D8BA1860F47E}" name="secret_type" dataDxfId="39"/>
+    <tableColumn id="22" xr3:uid="{3829C8E8-1959-4691-AF37-5B45456BC812}" name="trunk_encapsulation" dataDxfId="38"/>
+    <tableColumn id="23" xr3:uid="{4CE3B16C-67F6-4DC2-9BB2-F8E09C5C8D74}" name="snmpv3_enabled" dataDxfId="37"/>
+    <tableColumn id="24" xr3:uid="{7E57634C-C61D-454F-83A9-CCC1D7A3E9A7}" name="snmp_server_ip" dataDxfId="36"/>
+    <tableColumn id="25" xr3:uid="{DA892339-1F60-44AE-B105-D466545319B6}" name="snmp_user" dataDxfId="35"/>
+    <tableColumn id="26" xr3:uid="{10EE6F10-8503-4A58-9CA0-8FB438354050}" name="snmp_auth_password" dataDxfId="34"/>
+    <tableColumn id="27" xr3:uid="{66121011-59AB-4D41-BDF5-22B7624358BE}" name="snmp_priv_password" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A99B9E14-0F60-413C-83C8-281F7E727FAD}" name="Tabell49" displayName="Tabell49" ref="A18:J22" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A99B9E14-0F60-413C-83C8-281F7E727FAD}" name="Tabell49" displayName="Tabell49" ref="A18:J23" dataDxfId="32">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C939C381-1121-4153-B4EA-3E9AC4EFD622}" name="tunnel id" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{402267D7-3F42-4106-963C-A00D2C73C6A3}" name="vrf" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{4204F352-886B-4432-BF55-0DB72CCEC230}" name="ip address" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{C939C381-1121-4153-B4EA-3E9AC4EFD622}" name="tunnel id" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{402267D7-3F42-4106-963C-A00D2C73C6A3}" name="vrf" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{4204F352-886B-4432-BF55-0DB72CCEC230}" name="ip address" dataDxfId="29">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E652E851-68C8-44CC-A804-D4A898A26E6B}" name="mask" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{1B6660E8-062A-4243-A879-B9BBE79D61B2}" name="source" dataDxfId="26">
+    <tableColumn id="4" xr3:uid="{E652E851-68C8-44CC-A804-D4A898A26E6B}" name="mask" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{1B6660E8-062A-4243-A879-B9BBE79D61B2}" name="source" dataDxfId="27">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{31E83213-6808-4B06-B3A2-334B8AEA93A6}" name="destination" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{548BE719-FE15-47C2-BD8C-E15155610E6F}" name="gre mode" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{AC2699E3-BB2E-4992-9A64-D04428D784DC}" name="network-id" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{911A5F49-374E-494E-9F87-E559E2AEA74A}" name="ipsec" dataDxfId="22">
+    <tableColumn id="6" xr3:uid="{31E83213-6808-4B06-B3A2-334B8AEA93A6}" name="destination" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{548BE719-FE15-47C2-BD8C-E15155610E6F}" name="gre mode" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{AC2699E3-BB2E-4992-9A64-D04428D784DC}" name="network-id" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{911A5F49-374E-494E-9F87-E559E2AEA74A}" name="ipsec" dataDxfId="23">
       <calculatedColumnFormula>'Site 1 (HUB)'!I19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F9EF835F-35E0-4DBE-9B12-F79414F650B4}" name="ipsec key" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{F9EF835F-35E0-4DBE-9B12-F79414F650B4}" name="ipsec key" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DA31B441-D218-45B2-B01A-A4BBC8BD7979}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DA31B441-D218-45B2-B01A-A4BBC8BD7979}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="21">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F434D49E-3876-49A2-911F-716DB0E46944}" name="site" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{F434D49E-3876-49A2-911F-716DB0E46944}" name="site" dataDxfId="20">
       <calculatedColumnFormula>$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96C6D5FD-CBC3-49D8-AFD4-9E1E09633C5A}" name="brukernavn" dataDxfId="18">
+    <tableColumn id="4" xr3:uid="{96C6D5FD-CBC3-49D8-AFD4-9E1E09633C5A}" name="brukernavn" dataDxfId="19">
       <calculatedColumnFormula>$D$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{038EE345-4494-4999-88D7-0BF36304D24C}" name="passord" dataDxfId="17">
+    <tableColumn id="5" xr3:uid="{038EE345-4494-4999-88D7-0BF36304D24C}" name="passord" dataDxfId="18">
       <calculatedColumnFormula>$E$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{770D33D1-BE1F-45C0-8F6C-2E9C2A15365F}" name="vty_lines" dataDxfId="16">
+    <tableColumn id="3" xr3:uid="{770D33D1-BE1F-45C0-8F6C-2E9C2A15365F}" name="vty_lines" dataDxfId="17">
       <calculatedColumnFormula>$F$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{87FFB71D-3185-4317-BD65-911279FF4E36}" name="secret" dataDxfId="15">
+    <tableColumn id="2" xr3:uid="{87FFB71D-3185-4317-BD65-911279FF4E36}" name="secret" dataDxfId="16">
       <calculatedColumnFormula>$G$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{13F65231-00AD-4279-9566-BCCC6B905C94}" name="etherchan_num" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{32F614C6-376B-4371-8715-7B2614BB4DBC}" name="span_mode" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{70D4C587-3B90-40C4-BB6C-9CC884BED451}" name="dot1x_vlans" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{13F65231-00AD-4279-9566-BCCC6B905C94}" name="etherchan_num" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{32F614C6-376B-4371-8715-7B2614BB4DBC}" name="span_mode" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{70D4C587-3B90-40C4-BB6C-9CC884BED451}" name="dot1x_vlans" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3027,10 +3038,13 @@
     <col min="6" max="6" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="72.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.88671875" customWidth="1"/>
     <col min="11" max="11" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="24" width="18" customWidth="1"/>
+    <col min="12" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -3115,19 +3129,19 @@
         <v>24</v>
       </c>
       <c r="Z1" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA1" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="AA1" s="36" t="s">
+      <c r="AB1" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="AB1" s="36" t="s">
+      <c r="AC1" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="AC1" s="36" t="s">
+      <c r="AD1" s="36" t="s">
         <v>118</v>
-      </c>
-      <c r="AD1" s="36" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3148,7 +3162,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>27</v>
@@ -3163,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L2" s="19" t="s">
         <v>29</v>
@@ -3214,13 +3228,13 @@
         <v>29</v>
       </c>
       <c r="AB2" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC2" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="AC2" s="38" t="s">
+      <c r="AD2" s="38" t="s">
         <v>121</v>
-      </c>
-      <c r="AD2" s="38" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3427,35 +3441,35 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="45" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C9" s="7">
         <v>0</v>
       </c>
-      <c r="D9" s="7" t="str">
+      <c r="D9" s="49" t="str">
         <f>10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".0"</f>
-        <v>10.1.40.0</v>
+        <v>10.1.50.0</v>
       </c>
       <c r="E9" s="7" t="str">
         <f t="shared" ref="E9" si="4">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".1"</f>
-        <v>10.1.40.1</v>
+        <v>10.1.50.1</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="7" t="str">
         <f t="shared" ref="G9" si="5">VALUE(LEFT(D9,FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+1)</f>
-        <v>10.1.40.1</v>
-      </c>
-      <c r="H9" s="7" t="str">
+        <v>10.1.50.1</v>
+      </c>
+      <c r="H9" s="49" t="str">
         <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
-        <v>10.1.40.254</v>
-      </c>
-      <c r="I9" s="7">
+        <v>10.1.50.254</v>
+      </c>
+      <c r="I9" s="45">
         <v>40</v>
       </c>
       <c r="J9">
@@ -3529,15 +3543,15 @@
       </c>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="42" t="s">
         <v>54</v>
       </c>
       <c r="B16" s="7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C16" s="7" t="str">
         <f t="shared" ref="C16" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B16</f>
-        <v>1.1.1.40</v>
+        <v>1.1.1.50</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3694,20 +3708,20 @@
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23" s="43" t="s">
+      <c r="A23" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="7" t="str">
+      <c r="C23" s="49" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H23&amp;"."&amp;$A$2</f>
-        <v>172.16.40.1</v>
+        <v>172.16.50.1</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="7" t="str">
+      <c r="E23" s="49" t="str">
         <f>$C$2</f>
         <v>1.1.1.0</v>
       </c>
@@ -3716,7 +3730,7 @@
         <v>66</v>
       </c>
       <c r="H23" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I23" s="28" t="b">
         <v>1</v>
@@ -3786,10 +3800,10 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H26" s="42" t="s">
-        <v>128</v>
+        <v>124</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>127</v>
       </c>
       <c r="I26" s="35" cm="1">
         <f t="array" ref="I26">Tabell5[ISP-VLAN]</f>
@@ -3799,13 +3813,13 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>75</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>42</v>
@@ -3814,25 +3828,25 @@
         <v>43</v>
       </c>
       <c r="F28" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="H28" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="I28" s="13" t="s">
         <v>79</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>80</v>
       </c>
       <c r="J28" s="13" t="s">
         <v>1</v>
       </c>
       <c r="K28" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L28" s="25" t="s">
         <v>81</v>
-      </c>
-      <c r="L28" s="25" t="s">
-        <v>82</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>17</v>
@@ -3881,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>25</v>
@@ -5104,6 +5118,2115 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B45EDC77-8BBB-4908-955E-B9316A6BE4D3}">
+  <dimension ref="A1:AA997"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.44140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="75.88671875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="75.88671875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="75.88671875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" style="12" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" style="12" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="13" max="14" width="18" style="12" customWidth="1"/>
+    <col min="15" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="19.5546875" customWidth="1"/>
+    <col min="18" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.109375" style="12" customWidth="1"/>
+    <col min="24" max="24" width="13.44140625" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="27" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="X1" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y1" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z1" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA1" s="33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="12" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="12" t="str">
+        <f>'Site 1 (HUB)'!I2</f>
+        <v>TACACS-KEY</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="J2" s="14" t="str">
+        <f>'Site 1 (HUB)'!L2</f>
+        <v>10.1.10.10</v>
+      </c>
+      <c r="K2" s="14" t="str">
+        <f>'Site 1 (HUB)'!M2</f>
+        <v>10.1.10.10</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="30" t="str">
+        <f>'Site 1 (HUB)'!O2</f>
+        <v>10.1.10.10</v>
+      </c>
+      <c r="N2" s="30" t="str">
+        <f>'Site 1 (HUB)'!P2</f>
+        <v>RADIUS-KEY</v>
+      </c>
+      <c r="O2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" s="34">
+        <v>9</v>
+      </c>
+      <c r="V2" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z2" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA2" s="40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="8">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".0"</f>
+        <v>10.2.10.0</v>
+      </c>
+      <c r="E5" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".1"</f>
+        <v>10.2.10.1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <f t="shared" ref="G5:G8" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
+        <v>10.2.10.1</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</f>
+        <v>10.2.10.254</v>
+      </c>
+      <c r="I5" s="7">
+        <v>40</v>
+      </c>
+      <c r="J5" s="9">
+        <v>21</v>
+      </c>
+      <c r="K5" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="8">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <f t="shared" ref="D6:D8" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
+        <v>10.2.20.0</v>
+      </c>
+      <c r="E6" s="7" t="str">
+        <f t="shared" ref="E6:E8" si="2">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
+        <v>10.2.20.1</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.2.20.1</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f>(VALUE(LEFT(D6,FIND(".",D6)-1))+255-VALUE(LEFT(F6,FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6)+1,FIND(".",D6,FIND(".",D6)+1)-FIND(".",D6)-1))+255-VALUE(MID(F6,FIND(".",F6)+1,FIND(".",F6,FIND(".",F6)+1)-FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6,FIND(".",D6)+1)+1,FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)-FIND(".",D6,FIND(".",D6)+1)-1))+255-VALUE(MID(F6,FIND(".",F6,FIND(".",F6)+1)+1,FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)-FIND(".",F6,FIND(".",F6)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D6,LEN(D6)-FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)))+255-VALUE(RIGHT(F6,LEN(F6)-FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)))-1)</f>
+        <v>10.2.20.254</v>
+      </c>
+      <c r="I6" s="7">
+        <v>40</v>
+      </c>
+      <c r="J6" s="9">
+        <v>11</v>
+      </c>
+      <c r="K6" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="8">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>10.2.30.0</v>
+      </c>
+      <c r="E7" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>10.2.30.1</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.2.30.1</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f>(VALUE(LEFT(D7,FIND(".",D7)-1))+255-VALUE(LEFT(F7,FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7)+1,FIND(".",D7,FIND(".",D7)+1)-FIND(".",D7)-1))+255-VALUE(MID(F7,FIND(".",F7)+1,FIND(".",F7,FIND(".",F7)+1)-FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7,FIND(".",D7)+1)+1,FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)-FIND(".",D7,FIND(".",D7)+1)-1))+255-VALUE(MID(F7,FIND(".",F7,FIND(".",F7)+1)+1,FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)-FIND(".",F7,FIND(".",F7)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D7,LEN(D7)-FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)))+255-VALUE(RIGHT(F7,LEN(F7)-FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)))-1)</f>
+        <v>10.2.30.254</v>
+      </c>
+      <c r="I7" s="7">
+        <v>40</v>
+      </c>
+      <c r="J7">
+        <v>42</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="8">
+        <v>40</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>10.2.40.0</v>
+      </c>
+      <c r="E8" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>10.2.40.1</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>10.2.40.1</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f>(VALUE(LEFT(D8,FIND(".",D8)-1))+255-VALUE(LEFT(F8,FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8)+1,FIND(".",D8,FIND(".",D8)+1)-FIND(".",D8)-1))+255-VALUE(MID(F8,FIND(".",F8)+1,FIND(".",F8,FIND(".",F8)+1)-FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8,FIND(".",D8)+1)+1,FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)-FIND(".",D8,FIND(".",D8)+1)-1))+255-VALUE(MID(F8,FIND(".",F8,FIND(".",F8)+1)+1,FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)-FIND(".",F8,FIND(".",F8)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D8,LEN(D8)-FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)))+255-VALUE(RIGHT(F8,LEN(F8)-FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)))-1)</f>
+        <v>10.2.40.254</v>
+      </c>
+      <c r="I8" s="7">
+        <v>40</v>
+      </c>
+      <c r="J8">
+        <v>41</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="8">
+        <v>50</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f t="shared" ref="D9" si="3">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".0"</f>
+        <v>10.2.50.0</v>
+      </c>
+      <c r="E9" s="7" t="str">
+        <f t="shared" ref="E9" si="4">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".1"</f>
+        <v>10.2.50.1</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f t="shared" ref="G9" si="5">VALUE(LEFT(D9,FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+1)</f>
+        <v>10.2.50.1</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
+        <v>10.2.50.254</v>
+      </c>
+      <c r="I9" s="7">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11" s="12"/>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="7">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7" t="str">
+        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
+        <v>2.2.2.10</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="7">
+        <v>20</v>
+      </c>
+      <c r="C13" s="7" t="str">
+        <f t="shared" ref="C13:C15" si="6">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
+        <v>2.2.2.20</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="7">
+        <v>30</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>2.2.2.30</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14" s="12"/>
+    </row>
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="7">
+        <v>40</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>2.2.2.40</v>
+      </c>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15" s="12"/>
+    </row>
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="7">
+        <v>50</v>
+      </c>
+      <c r="C16" s="42" t="str">
+        <f t="shared" ref="C16" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B16</f>
+        <v>2.2.2.50</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="12" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
+        <v>172.16.10.2</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="12" t="str">
+        <f t="shared" ref="E19:E23" si="8">$C$2</f>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="12">
+        <v>10</v>
+      </c>
+      <c r="I19" s="29" t="b">
+        <f>'Site 1 (HUB)'!I19</f>
+        <v>1</v>
+      </c>
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="12" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
+        <v>172.16.20.2</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="12">
+        <v>20</v>
+      </c>
+      <c r="I20" s="29" t="b" cm="1">
+        <f>'Site 1 (HUB)'!I20</f>
+        <v>0</v>
+      </c>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="12" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;H21&amp;"."&amp;$A$2</f>
+        <v>172.16.30.2</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="12">
+        <v>30</v>
+      </c>
+      <c r="I21" s="29" t="b">
+        <f>'Site 1 (HUB)'!I21</f>
+        <v>1</v>
+      </c>
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="12" t="str">
+        <f t="shared" ref="C22" si="9">172&amp;"."&amp;16&amp;"."&amp;H22&amp;"."&amp;$A$2</f>
+        <v>172.16.40.2</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="12" t="str">
+        <f t="shared" si="8"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="12">
+        <v>40</v>
+      </c>
+      <c r="I22" s="29" t="b">
+        <f>'Site 1 (HUB)'!I22</f>
+        <v>1</v>
+      </c>
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="43" t="str">
+        <f t="shared" ref="C23" si="10">172&amp;"."&amp;16&amp;"."&amp;H23&amp;"."&amp;$A$2</f>
+        <v>172.16.40.2</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="46" t="str">
+        <f t="shared" si="8"/>
+        <v>2.2.2.0</v>
+      </c>
+      <c r="F23" s="47"/>
+      <c r="G23" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="43">
+        <v>40</v>
+      </c>
+      <c r="I23" s="29" t="b">
+        <f>'Site 1 (HUB)'!I23</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="47"/>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <f>$A$2</f>
+        <v>2</v>
+      </c>
+      <c r="B26" s="12" t="str">
+        <f>$D$2</f>
+        <v>admin</v>
+      </c>
+      <c r="C26" s="12" t="str">
+        <f>$E$2</f>
+        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
+      </c>
+      <c r="D26" s="12" t="str">
+        <f>$F$2</f>
+        <v>0 - 15</v>
+      </c>
+      <c r="E26" s="12" t="str">
+        <f>$G$2</f>
+        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
+      </c>
+      <c r="F26" s="12">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L28" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <f t="shared" ref="A29" si="11">ROW()-28</f>
+        <v>1</v>
+      </c>
+      <c r="B29" s="7">
+        <f>$B$5</f>
+        <v>10</v>
+      </c>
+      <c r="C29" s="7" t="str">
+        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</f>
+        <v>10.2.10.2</v>
+      </c>
+      <c r="D29" s="7" t="str">
+        <f>$E$5</f>
+        <v>10.2.10.1</v>
+      </c>
+      <c r="E29" s="7" t="str">
+        <f>$F$5</f>
+        <v>255.255.255.0</v>
+      </c>
+      <c r="F29" s="7">
+        <v>49</v>
+      </c>
+      <c r="G29" s="7">
+        <v>1</v>
+      </c>
+      <c r="H29" s="10">
+        <v>1</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K29" s="2">
+        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
+        <v>43</v>
+      </c>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+    </row>
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+    </row>
+    <row r="33" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+    </row>
+    <row r="34" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+    </row>
+    <row r="35" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="31"/>
+      <c r="Q35" s="31"/>
+    </row>
+    <row r="36" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M36" s="31"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="31"/>
+    </row>
+    <row r="37" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+    </row>
+    <row r="38" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M38" s="31"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="31"/>
+      <c r="Q38" s="31"/>
+    </row>
+    <row r="39" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M39" s="31"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="31"/>
+      <c r="Q39" s="31"/>
+    </row>
+    <row r="40" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+    </row>
+    <row r="41" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+    </row>
+    <row r="42" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+    </row>
+    <row r="43" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+    </row>
+    <row r="44" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+    </row>
+    <row r="45" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M45" s="31"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="31"/>
+      <c r="Q45" s="31"/>
+    </row>
+    <row r="46" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+    </row>
+    <row r="47" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+    </row>
+    <row r="48" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M48" s="31"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+    </row>
+    <row r="49" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+    </row>
+    <row r="50" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="31"/>
+      <c r="N50" s="31"/>
+      <c r="O50" s="31"/>
+      <c r="P50" s="31"/>
+      <c r="Q50" s="31"/>
+    </row>
+    <row r="51" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M51" s="31"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="31"/>
+    </row>
+    <row r="52" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+    </row>
+    <row r="53" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="31"/>
+      <c r="P53" s="31"/>
+      <c r="Q53" s="31"/>
+    </row>
+    <row r="54" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
+      <c r="P54" s="31"/>
+      <c r="Q54" s="31"/>
+    </row>
+    <row r="55" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+    </row>
+    <row r="56" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M56" s="31"/>
+      <c r="N56" s="31"/>
+      <c r="O56" s="31"/>
+      <c r="P56" s="31"/>
+      <c r="Q56" s="31"/>
+    </row>
+    <row r="57" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M57" s="31"/>
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+    </row>
+    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+    </row>
+    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M59" s="31"/>
+      <c r="N59" s="31"/>
+      <c r="O59" s="31"/>
+      <c r="P59" s="31"/>
+      <c r="Q59" s="31"/>
+    </row>
+    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <dataValidations count="9">
+    <dataValidation type="list" sqref="V2 Q29:Q59" xr:uid="{39D8B1B3-368B-4AC5-A514-11645F40D89B}">
+      <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="U2 P29:P59" xr:uid="{40E87254-C5D0-4454-8C47-5100945ED78A}">
+      <formula1>"AUTO,5,8,9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="T2" xr:uid="{D82DFD41-8835-4B4F-94E1-F31DD76B81DE}">
+      <formula1>"IKEV1,IKEV2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="R2" xr:uid="{F047568E-0FF5-4EA3-A7BF-468F3B62A5DC}">
+      <formula1>"CLASSIC,NAMED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="Q2 O29:O59" xr:uid="{8398B055-E1AD-474F-AA4B-7C530D80F4B4}">
+      <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="O2:P2 S2 M29:N59" xr:uid="{3BA14544-E617-4EAB-8056-F1ADFAEBFA4A}">
+      <formula1>"OLD,NEW"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{1CFE3BAF-8D34-4CA8-BE94-49E44A9437C4}">
+      <formula1>"OFF,STRICT,LOOSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="G26" xr:uid="{194DE05B-70E4-4CED-BEE9-B1A159236E6A}">
+      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29" xr:uid="{5FB8B7A2-FDEC-49C6-A037-9F36974649E1}">
+      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="6">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA998"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5198,31 +7321,31 @@
         <v>24</v>
       </c>
       <c r="W1" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="X1" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="X1" s="33" t="s">
+      <c r="Y1" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="Y1" s="33" t="s">
+      <c r="Z1" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="Z1" s="33" t="s">
+      <c r="AA1" s="33" t="s">
         <v>118</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="12" t="str">
         <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
-        <v>2.2.2.0</v>
+        <v>3.3.3.0</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>26</v>
@@ -5231,7 +7354,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>27</v>
@@ -5241,7 +7364,7 @@
         <v>TACACS-KEY</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J2" s="14" t="str">
         <f>'Site 1 (HUB)'!L2</f>
@@ -5284,7 +7407,7 @@
         <v>9</v>
       </c>
       <c r="V2" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W2" s="39" t="b">
         <v>1</v>
@@ -5293,13 +7416,13 @@
         <v>29</v>
       </c>
       <c r="Y2" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z2" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="Z2" s="40" t="s">
+      <c r="AA2" s="40" t="s">
         <v>121</v>
-      </c>
-      <c r="AA2" s="40" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5332,7 +7455,7 @@
         <v>46</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K4" s="27" t="s">
         <v>48</v>
@@ -5350,22 +7473,22 @@
       </c>
       <c r="D5" s="7" t="str">
         <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".0"</f>
-        <v>10.2.10.0</v>
+        <v>10.3.10.0</v>
       </c>
       <c r="E5" s="7" t="str">
         <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".1"</f>
-        <v>10.2.10.1</v>
+        <v>10.3.10.1</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" ref="G5:G8" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
-        <v>10.2.10.1</v>
+        <f t="shared" ref="G5:G9" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
+        <v>10.3.10.1</v>
       </c>
       <c r="H5" s="7" t="str">
         <f>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</f>
-        <v>10.2.10.254</v>
+        <v>10.3.10.254</v>
       </c>
       <c r="I5" s="7">
         <v>40</v>
@@ -5388,23 +7511,23 @@
         <v>0</v>
       </c>
       <c r="D6" s="7" t="str">
-        <f t="shared" ref="D6:D8" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
-        <v>10.2.20.0</v>
+        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
+        <v>10.3.20.0</v>
       </c>
       <c r="E6" s="7" t="str">
-        <f t="shared" ref="E6:E8" si="2">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
-        <v>10.2.20.1</v>
+        <f t="shared" ref="E6:E9" si="2">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
+        <v>10.3.20.1</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>10.2.20.1</v>
+        <v>10.3.20.1</v>
       </c>
       <c r="H6" s="7" t="str">
         <f>(VALUE(LEFT(D6,FIND(".",D6)-1))+255-VALUE(LEFT(F6,FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6)+1,FIND(".",D6,FIND(".",D6)+1)-FIND(".",D6)-1))+255-VALUE(MID(F6,FIND(".",F6)+1,FIND(".",F6,FIND(".",F6)+1)-FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6,FIND(".",D6)+1)+1,FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)-FIND(".",D6,FIND(".",D6)+1)-1))+255-VALUE(MID(F6,FIND(".",F6,FIND(".",F6)+1)+1,FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)-FIND(".",F6,FIND(".",F6)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D6,LEN(D6)-FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)))+255-VALUE(RIGHT(F6,LEN(F6)-FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)))-1)</f>
-        <v>10.2.20.254</v>
+        <v>10.3.20.254</v>
       </c>
       <c r="I6" s="7">
         <v>40</v>
@@ -5428,22 +7551,22 @@
       </c>
       <c r="D7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>10.2.30.0</v>
+        <v>10.3.30.0</v>
       </c>
       <c r="E7" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>10.2.30.1</v>
+        <v>10.3.30.1</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>10.2.30.1</v>
+        <v>10.3.30.1</v>
       </c>
       <c r="H7" s="7" t="str">
         <f>(VALUE(LEFT(D7,FIND(".",D7)-1))+255-VALUE(LEFT(F7,FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7)+1,FIND(".",D7,FIND(".",D7)+1)-FIND(".",D7)-1))+255-VALUE(MID(F7,FIND(".",F7)+1,FIND(".",F7,FIND(".",F7)+1)-FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7,FIND(".",D7)+1)+1,FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)-FIND(".",D7,FIND(".",D7)+1)-1))+255-VALUE(MID(F7,FIND(".",F7,FIND(".",F7)+1)+1,FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)-FIND(".",F7,FIND(".",F7)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D7,LEN(D7)-FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)))+255-VALUE(RIGHT(F7,LEN(F7)-FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)))-1)</f>
-        <v>10.2.30.254</v>
+        <v>10.3.30.254</v>
       </c>
       <c r="I7" s="7">
         <v>40</v>
@@ -5467,22 +7590,22 @@
       </c>
       <c r="D8" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>10.2.40.0</v>
+        <v>10.3.40.0</v>
       </c>
       <c r="E8" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>10.2.40.1</v>
+        <v>10.3.40.1</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>10.2.40.1</v>
+        <v>10.3.40.1</v>
       </c>
       <c r="H8" s="7" t="str">
         <f>(VALUE(LEFT(D8,FIND(".",D8)-1))+255-VALUE(LEFT(F8,FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8)+1,FIND(".",D8,FIND(".",D8)+1)-FIND(".",D8)-1))+255-VALUE(MID(F8,FIND(".",F8)+1,FIND(".",F8,FIND(".",F8)+1)-FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8,FIND(".",D8)+1)+1,FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)-FIND(".",D8,FIND(".",D8)+1)-1))+255-VALUE(MID(F8,FIND(".",F8,FIND(".",F8)+1)+1,FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)-FIND(".",F8,FIND(".",F8)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D8,LEN(D8)-FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)))+255-VALUE(RIGHT(F8,LEN(F8)-FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)))-1)</f>
-        <v>10.2.40.254</v>
+        <v>10.3.40.254</v>
       </c>
       <c r="I8" s="7">
         <v>40</v>
@@ -5496,7 +7619,7 @@
       <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="42" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="8">
@@ -5506,23 +7629,23 @@
         <v>0</v>
       </c>
       <c r="D9" s="7" t="str">
-        <f t="shared" ref="D9" si="3">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".0"</f>
-        <v>10.2.50.0</v>
+        <f t="shared" si="1"/>
+        <v>10.3.50.0</v>
       </c>
       <c r="E9" s="7" t="str">
-        <f t="shared" ref="E9" si="4">10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".1"</f>
-        <v>10.2.50.1</v>
+        <f t="shared" si="2"/>
+        <v>10.3.50.1</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="7" t="str">
-        <f t="shared" ref="G9" si="5">VALUE(LEFT(D9,FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+1)</f>
-        <v>10.2.50.1</v>
+        <f t="shared" si="0"/>
+        <v>10.3.50.1</v>
       </c>
       <c r="H9" s="7" t="str">
         <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
-        <v>10.2.50.254</v>
+        <v>10.3.50.254</v>
       </c>
       <c r="I9" s="7">
         <v>40</v>
@@ -5578,7 +7701,7 @@
       </c>
       <c r="C12" s="7" t="str">
         <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
-        <v>2.2.2.10</v>
+        <v>3.3.3.10</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -5598,8 +7721,8 @@
         <v>20</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f t="shared" ref="C13:C15" si="6">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
-        <v>2.2.2.20</v>
+        <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
+        <v>3.3.3.20</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -5619,8 +7742,8 @@
         <v>30</v>
       </c>
       <c r="C14" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>2.2.2.30</v>
+        <f t="shared" si="3"/>
+        <v>3.3.3.30</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -5640,8 +7763,8 @@
         <v>40</v>
       </c>
       <c r="C15" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>2.2.2.40</v>
+        <f t="shared" si="3"/>
+        <v>3.3.3.40</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -5654,15 +7777,15 @@
       <c r="L15" s="12"/>
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="42" t="s">
         <v>54</v>
       </c>
       <c r="B16" s="7">
         <v>50</v>
       </c>
-      <c r="C16" s="43" t="str">
-        <f t="shared" ref="C16" si="7">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B16</f>
-        <v>2.2.2.50</v>
+      <c r="C16" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>3.3.3.50</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -5716,14 +7839,14 @@
       </c>
       <c r="C19" s="12" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
-        <v>172.16.10.2</v>
+        <v>172.16.10.3</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="12" t="str">
-        <f t="shared" ref="E19:E23" si="8">$C$2</f>
-        <v>2.2.2.0</v>
+        <f t="shared" ref="E19:E23" si="4">$C$2</f>
+        <v>3.3.3.0</v>
       </c>
       <c r="F19"/>
       <c r="G19" s="12" t="s">
@@ -5747,14 +7870,14 @@
       </c>
       <c r="C20" s="12" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
-        <v>172.16.20.2</v>
+        <v>172.16.20.3</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v>2.2.2.0</v>
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
       </c>
       <c r="F20"/>
       <c r="G20" s="12" t="s">
@@ -5778,14 +7901,14 @@
       </c>
       <c r="C21" s="12" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H21&amp;"."&amp;$A$2</f>
-        <v>172.16.30.2</v>
+        <v>172.16.30.3</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E21" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v>2.2.2.0</v>
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
       </c>
       <c r="F21"/>
       <c r="G21" s="12" t="s">
@@ -5801,66 +7924,66 @@
       <c r="J21"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="12" t="str">
-        <f t="shared" ref="C22" si="9">172&amp;"."&amp;16&amp;"."&amp;H22&amp;"."&amp;$A$2</f>
-        <v>172.16.40.2</v>
-      </c>
-      <c r="D22" s="12" t="s">
+      <c r="C22" s="43" t="str">
+        <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;H22&amp;"."&amp;$A$2</f>
+        <v>172.16.40.3</v>
+      </c>
+      <c r="D22" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v>2.2.2.0</v>
-      </c>
-      <c r="F22"/>
-      <c r="G22" s="12" t="s">
+      <c r="E22" s="46" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F22" s="47"/>
+      <c r="G22" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="43">
         <v>40</v>
       </c>
-      <c r="I22" s="29" t="b">
+      <c r="I22" s="48" t="b">
         <f>'Site 1 (HUB)'!I22</f>
         <v>1</v>
       </c>
-      <c r="J22"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23" s="44" t="s">
+      <c r="A23" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="12" t="str">
-        <f t="shared" ref="C23" si="10">172&amp;"."&amp;16&amp;"."&amp;H23&amp;"."&amp;$A$2</f>
-        <v>172.16.40.2</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="C23" s="43" t="str">
+        <f t="shared" si="5"/>
+        <v>172.16.40.3</v>
+      </c>
+      <c r="D23" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v>2.2.2.0</v>
-      </c>
-      <c r="F23"/>
-      <c r="G23" s="12" t="s">
+      <c r="E23" s="46" t="str">
+        <f t="shared" si="4"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F23" s="47"/>
+      <c r="G23" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="43">
         <v>40</v>
       </c>
-      <c r="I23" s="29">
-        <f>'Site 1 (HUB)'!I24</f>
-        <v>0</v>
-      </c>
-      <c r="J23"/>
+      <c r="I23" s="48" t="b">
+        <f>'Site 1 (HUB)'!I23</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5892,7 +8015,7 @@
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <f>$A$2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" s="12" t="str">
         <f>$D$2</f>
@@ -5913,21 +8036,23 @@
       <c r="F26" s="12">
         <v>2</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="30" t="s">
-        <v>73</v>
+      <c r="G26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>75</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>42</v>
@@ -5936,25 +8061,25 @@
         <v>43</v>
       </c>
       <c r="F28" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="H28" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="I28" s="13" t="s">
         <v>79</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>80</v>
       </c>
       <c r="J28" s="13" t="s">
         <v>1</v>
       </c>
       <c r="K28" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L28" s="25" t="s">
         <v>81</v>
-      </c>
-      <c r="L28" s="25" t="s">
-        <v>82</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>17</v>
@@ -5974,7 +8099,7 @@
     </row>
     <row r="29" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
-        <f t="shared" ref="A29:A30" si="11">ROW()-28</f>
+        <f t="shared" ref="A29:A30" si="6">ROW()-28</f>
         <v>1</v>
       </c>
       <c r="B29" s="7">
@@ -5983,11 +8108,11 @@
       </c>
       <c r="C29" s="7" t="str">
         <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</f>
-        <v>10.2.10.2</v>
+        <v>10.3.10.2</v>
       </c>
       <c r="D29" s="7" t="str">
         <f>$E$5</f>
-        <v>10.2.10.1</v>
+        <v>10.3.10.1</v>
       </c>
       <c r="E29" s="7" t="str">
         <f>$F$5</f>
@@ -6003,14 +8128,14 @@
         <v>1</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K29" s="2">
         <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
@@ -6020,7 +8145,7 @@
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="B30" s="7">
@@ -6029,11 +8154,11 @@
       </c>
       <c r="C30" s="7" t="str">
         <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A30+1)</f>
-        <v>10.2.10.3</v>
+        <v>10.3.10.3</v>
       </c>
       <c r="D30" s="7" t="str">
         <f>$E$5</f>
-        <v>10.2.10.1</v>
+        <v>10.3.10.1</v>
       </c>
       <c r="E30" s="7" t="str">
         <f>$F$5</f>
@@ -6049,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>25</v>
@@ -7214,2159 +9339,6 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="list" sqref="V2 Q29:Q60" xr:uid="{39D8B1B3-368B-4AC5-A514-11645F40D89B}">
-      <formula1>"AUTO,DOT1Q_CMD,NO_CMD"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="U2 P29:P60" xr:uid="{40E87254-C5D0-4454-8C47-5100945ED78A}">
-      <formula1>"AUTO,5,8,9"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="T2" xr:uid="{D82DFD41-8835-4B4F-94E1-F31DD76B81DE}">
-      <formula1>"IKEV1,IKEV2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="R2" xr:uid="{F047568E-0FF5-4EA3-A7BF-468F3B62A5DC}">
-      <formula1>"CLASSIC,NAMED"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="Q2 O29:O60" xr:uid="{8398B055-E1AD-474F-AA4B-7C530D80F4B4}">
-      <formula1>"LEGACY,AUTH,ACCESS_SESSION"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="O2:P2 S2 M29:N60" xr:uid="{3BA14544-E617-4EAB-8056-F1ADFAEBFA4A}">
-      <formula1>"OLD,NEW"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I29:I30" xr:uid="{5FB8B7A2-FDEC-49C6-A037-9F36974649E1}">
-      <formula1>IF(I29="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(I29,"-"),"."))&lt;=K29)</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="L2" xr:uid="{1CFE3BAF-8D34-4CA8-BE94-49E44A9437C4}">
-      <formula1>"OFF,STRICT,LOOSE"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="G26" xr:uid="{194DE05B-70E4-4CED-BEE9-B1A159236E6A}">
-      <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="6">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AA998"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.44140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="75.88671875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="75.88671875" style="12" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" style="12" customWidth="1"/>
-    <col min="7" max="7" width="75.88671875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="12" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" style="12" customWidth="1"/>
-    <col min="10" max="10" width="16.109375" style="12" customWidth="1"/>
-    <col min="11" max="11" width="16.88671875" style="12" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" customWidth="1"/>
-    <col min="13" max="14" width="18" style="12" customWidth="1"/>
-    <col min="15" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="19.5546875" customWidth="1"/>
-    <col min="18" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.109375" style="12" customWidth="1"/>
-    <col min="24" max="24" width="13.44140625" customWidth="1"/>
-    <col min="25" max="25" width="9.44140625" customWidth="1"/>
-    <col min="26" max="27" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q1" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="T1" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="U1" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="V1" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="W1" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="X1" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y1" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z1" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
-        <v>3</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="12" t="str">
-        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="12" t="str">
-        <f>'Site 1 (HUB)'!I2</f>
-        <v>TACACS-KEY</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="J2" s="14" t="str">
-        <f>'Site 1 (HUB)'!L2</f>
-        <v>10.1.10.10</v>
-      </c>
-      <c r="K2" s="14" t="str">
-        <f>'Site 1 (HUB)'!M2</f>
-        <v>10.1.10.10</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="30" t="str">
-        <f>'Site 1 (HUB)'!O2</f>
-        <v>10.1.10.10</v>
-      </c>
-      <c r="N2" s="30" t="str">
-        <f>'Site 1 (HUB)'!P2</f>
-        <v>RADIUS-KEY</v>
-      </c>
-      <c r="O2" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" s="34">
-        <v>9</v>
-      </c>
-      <c r="V2" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="W2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="X2" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y2" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z2" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA2" s="40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="K4" s="27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="8">
-        <v>10</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="str">
-        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".0"</f>
-        <v>10.3.10.0</v>
-      </c>
-      <c r="E5" s="7" t="str">
-        <f>10&amp;"."&amp;$A$2&amp;"."&amp;B5&amp;".1"</f>
-        <v>10.3.10.1</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="7" t="str">
-        <f t="shared" ref="G5:G9" si="0">VALUE(LEFT(D5,FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))&amp;"."&amp;VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+1)</f>
-        <v>10.3.10.1</v>
-      </c>
-      <c r="H5" s="7" t="str">
-        <f>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</f>
-        <v>10.3.10.254</v>
-      </c>
-      <c r="I5" s="7">
-        <v>40</v>
-      </c>
-      <c r="J5" s="9">
-        <v>21</v>
-      </c>
-      <c r="K5" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="8">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="str">
-        <f t="shared" ref="D6:D9" si="1">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".0"</f>
-        <v>10.3.20.0</v>
-      </c>
-      <c r="E6" s="7" t="str">
-        <f t="shared" ref="E6:E9" si="2">10&amp;"."&amp;$A$2&amp;"."&amp;B6&amp;".1"</f>
-        <v>10.3.20.1</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>10.3.20.1</v>
-      </c>
-      <c r="H6" s="7" t="str">
-        <f>(VALUE(LEFT(D6,FIND(".",D6)-1))+255-VALUE(LEFT(F6,FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6)+1,FIND(".",D6,FIND(".",D6)+1)-FIND(".",D6)-1))+255-VALUE(MID(F6,FIND(".",F6)+1,FIND(".",F6,FIND(".",F6)+1)-FIND(".",F6)-1)))&amp;"."&amp;(VALUE(MID(D6,FIND(".",D6,FIND(".",D6)+1)+1,FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)-FIND(".",D6,FIND(".",D6)+1)-1))+255-VALUE(MID(F6,FIND(".",F6,FIND(".",F6)+1)+1,FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)-FIND(".",F6,FIND(".",F6)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D6,LEN(D6)-FIND(".",D6,FIND(".",D6,FIND(".",D6)+1)+1)))+255-VALUE(RIGHT(F6,LEN(F6)-FIND(".",F6,FIND(".",F6,FIND(".",F6)+1)+1)))-1)</f>
-        <v>10.3.20.254</v>
-      </c>
-      <c r="I6" s="7">
-        <v>40</v>
-      </c>
-      <c r="J6" s="9">
-        <v>11</v>
-      </c>
-      <c r="K6" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="8">
-        <v>30</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.3.30.0</v>
-      </c>
-      <c r="E7" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>10.3.30.1</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>10.3.30.1</v>
-      </c>
-      <c r="H7" s="7" t="str">
-        <f>(VALUE(LEFT(D7,FIND(".",D7)-1))+255-VALUE(LEFT(F7,FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7)+1,FIND(".",D7,FIND(".",D7)+1)-FIND(".",D7)-1))+255-VALUE(MID(F7,FIND(".",F7)+1,FIND(".",F7,FIND(".",F7)+1)-FIND(".",F7)-1)))&amp;"."&amp;(VALUE(MID(D7,FIND(".",D7,FIND(".",D7)+1)+1,FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)-FIND(".",D7,FIND(".",D7)+1)-1))+255-VALUE(MID(F7,FIND(".",F7,FIND(".",F7)+1)+1,FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)-FIND(".",F7,FIND(".",F7)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D7,LEN(D7)-FIND(".",D7,FIND(".",D7,FIND(".",D7)+1)+1)))+255-VALUE(RIGHT(F7,LEN(F7)-FIND(".",F7,FIND(".",F7,FIND(".",F7)+1)+1)))-1)</f>
-        <v>10.3.30.254</v>
-      </c>
-      <c r="I7" s="7">
-        <v>40</v>
-      </c>
-      <c r="J7">
-        <v>42</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="8">
-        <v>40</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.3.40.0</v>
-      </c>
-      <c r="E8" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>10.3.40.1</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>10.3.40.1</v>
-      </c>
-      <c r="H8" s="7" t="str">
-        <f>(VALUE(LEFT(D8,FIND(".",D8)-1))+255-VALUE(LEFT(F8,FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8)+1,FIND(".",D8,FIND(".",D8)+1)-FIND(".",D8)-1))+255-VALUE(MID(F8,FIND(".",F8)+1,FIND(".",F8,FIND(".",F8)+1)-FIND(".",F8)-1)))&amp;"."&amp;(VALUE(MID(D8,FIND(".",D8,FIND(".",D8)+1)+1,FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)-FIND(".",D8,FIND(".",D8)+1)-1))+255-VALUE(MID(F8,FIND(".",F8,FIND(".",F8)+1)+1,FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)-FIND(".",F8,FIND(".",F8)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D8,LEN(D8)-FIND(".",D8,FIND(".",D8,FIND(".",D8)+1)+1)))+255-VALUE(RIGHT(F8,LEN(F8)-FIND(".",F8,FIND(".",F8,FIND(".",F8)+1)+1)))-1)</f>
-        <v>10.3.40.254</v>
-      </c>
-      <c r="I8" s="7">
-        <v>40</v>
-      </c>
-      <c r="J8">
-        <v>41</v>
-      </c>
-      <c r="K8">
-        <v>10</v>
-      </c>
-      <c r="L8" s="12"/>
-    </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="8">
-        <v>50</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>10.3.50.0</v>
-      </c>
-      <c r="E9" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>10.3.50.1</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="7" t="str">
-        <f t="shared" si="0"/>
-        <v>10.3.50.1</v>
-      </c>
-      <c r="H9" s="7" t="str">
-        <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
-        <v>10.3.50.254</v>
-      </c>
-      <c r="I9" s="7">
-        <v>40</v>
-      </c>
-      <c r="J9">
-        <v>41</v>
-      </c>
-      <c r="K9">
-        <v>10</v>
-      </c>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10" s="12"/>
-    </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11" s="12"/>
-    </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="7">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7" t="str">
-        <f>$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B12</f>
-        <v>3.3.3.10</v>
-      </c>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12" s="12"/>
-    </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="7">
-        <v>20</v>
-      </c>
-      <c r="C13" s="7" t="str">
-        <f t="shared" ref="C13:C16" si="3">$A$2&amp;"."&amp;$A$2&amp;"."&amp;$A$2&amp;"."&amp;B13</f>
-        <v>3.3.3.20</v>
-      </c>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13" s="12"/>
-    </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="7">
-        <v>30</v>
-      </c>
-      <c r="C14" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>3.3.3.30</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14" s="12"/>
-    </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="7">
-        <v>40</v>
-      </c>
-      <c r="C15" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>3.3.3.40</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15" s="12"/>
-    </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="7">
-        <v>50</v>
-      </c>
-      <c r="C16" s="43" t="str">
-        <f t="shared" si="3"/>
-        <v>3.3.3.50</v>
-      </c>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16" s="12"/>
-    </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="12" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</f>
-        <v>172.16.10.3</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="12" t="str">
-        <f t="shared" ref="E19:E23" si="4">$C$2</f>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F19"/>
-      <c r="G19" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="12">
-        <v>10</v>
-      </c>
-      <c r="I19" s="29" t="b">
-        <f>'Site 1 (HUB)'!I19</f>
-        <v>1</v>
-      </c>
-      <c r="J19"/>
-    </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="12" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H20&amp;"."&amp;$A$2</f>
-        <v>172.16.20.3</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F20"/>
-      <c r="G20" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="12">
-        <v>20</v>
-      </c>
-      <c r="I20" s="29" t="b" cm="1">
-        <f>'Site 1 (HUB)'!I20</f>
-        <v>0</v>
-      </c>
-      <c r="J20"/>
-    </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="12" t="str">
-        <f>172&amp;"."&amp;16&amp;"."&amp;H21&amp;"."&amp;$A$2</f>
-        <v>172.16.30.3</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F21"/>
-      <c r="G21" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" s="12">
-        <v>30</v>
-      </c>
-      <c r="I21" s="29" t="b">
-        <f>'Site 1 (HUB)'!I21</f>
-        <v>1</v>
-      </c>
-      <c r="J21"/>
-    </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="12" t="str">
-        <f t="shared" ref="C22:C23" si="5">172&amp;"."&amp;16&amp;"."&amp;H22&amp;"."&amp;$A$2</f>
-        <v>172.16.40.3</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F22"/>
-      <c r="G22" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H22" s="12">
-        <v>40</v>
-      </c>
-      <c r="I22" s="29" t="b">
-        <f>'Site 1 (HUB)'!I22</f>
-        <v>1</v>
-      </c>
-      <c r="J22"/>
-    </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v>172.16.40.3</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v>3.3.3.0</v>
-      </c>
-      <c r="F23"/>
-      <c r="G23" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" s="12">
-        <v>40</v>
-      </c>
-      <c r="I23" s="29">
-        <f>'Site 1 (HUB)'!I24</f>
-        <v>0</v>
-      </c>
-      <c r="J23"/>
-    </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
-        <f>$A$2</f>
-        <v>3</v>
-      </c>
-      <c r="B26" s="12" t="str">
-        <f>$D$2</f>
-        <v>admin</v>
-      </c>
-      <c r="C26" s="12" t="str">
-        <f>$E$2</f>
-        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
-      </c>
-      <c r="D26" s="12" t="str">
-        <f>$F$2</f>
-        <v>0 - 15</v>
-      </c>
-      <c r="E26" s="12" t="str">
-        <f>$G$2</f>
-        <v>$9$0nNdTjfcaOQFlP$4VgON16XmZXlfGr4BcOzEN7OoRxfPIAcXDQ0afwx67k</v>
-      </c>
-      <c r="F26" s="12">
-        <v>2</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:17" ht="27.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="L28" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <f t="shared" ref="A29:A30" si="6">ROW()-28</f>
-        <v>1</v>
-      </c>
-      <c r="B29" s="7">
-        <f>$B$5</f>
-        <v>10</v>
-      </c>
-      <c r="C29" s="7" t="str">
-        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</f>
-        <v>10.3.10.2</v>
-      </c>
-      <c r="D29" s="7" t="str">
-        <f>$E$5</f>
-        <v>10.3.10.1</v>
-      </c>
-      <c r="E29" s="7" t="str">
-        <f>$F$5</f>
-        <v>255.255.255.0</v>
-      </c>
-      <c r="F29" s="7">
-        <v>49</v>
-      </c>
-      <c r="G29" s="7">
-        <v>1</v>
-      </c>
-      <c r="H29" s="10">
-        <v>1</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K29" s="2">
-        <f>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</f>
-        <v>44</v>
-      </c>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-    </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="B30" s="7">
-        <f>$B$5</f>
-        <v>10</v>
-      </c>
-      <c r="C30" s="7" t="str">
-        <f>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A30+1)</f>
-        <v>10.3.10.3</v>
-      </c>
-      <c r="D30" s="7" t="str">
-        <f>$E$5</f>
-        <v>10.3.10.1</v>
-      </c>
-      <c r="E30" s="7" t="str">
-        <f>$F$5</f>
-        <v>255.255.255.0</v>
-      </c>
-      <c r="F30" s="7">
-        <v>11</v>
-      </c>
-      <c r="G30" s="7">
-        <v>1</v>
-      </c>
-      <c r="H30" s="7">
-        <v>0</v>
-      </c>
-      <c r="I30" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" s="2">
-        <f>IF($A30=1,F30-G30-H30*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F30-G30-(1+H30)*$F$26-1)</f>
-        <v>7</v>
-      </c>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="31"/>
-      <c r="Q30" s="31"/>
-    </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="31"/>
-    </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-    </row>
-    <row r="33" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-    </row>
-    <row r="34" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-    </row>
-    <row r="35" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-    </row>
-    <row r="36" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="31"/>
-    </row>
-    <row r="37" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-    </row>
-    <row r="38" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M38" s="31"/>
-      <c r="N38" s="31"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="31"/>
-      <c r="Q38" s="31"/>
-    </row>
-    <row r="39" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
-    </row>
-    <row r="40" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
-    </row>
-    <row r="41" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
-      <c r="Q41" s="31"/>
-    </row>
-    <row r="42" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-    </row>
-    <row r="43" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M43" s="31"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="31"/>
-      <c r="Q43" s="31"/>
-    </row>
-    <row r="44" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M44" s="31"/>
-      <c r="N44" s="31"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="31"/>
-      <c r="Q44" s="31"/>
-    </row>
-    <row r="45" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="31"/>
-      <c r="P45" s="31"/>
-      <c r="Q45" s="31"/>
-    </row>
-    <row r="46" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="31"/>
-    </row>
-    <row r="47" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-    </row>
-    <row r="48" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="31"/>
-    </row>
-    <row r="49" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M49" s="31"/>
-      <c r="N49" s="31"/>
-      <c r="O49" s="31"/>
-      <c r="P49" s="31"/>
-      <c r="Q49" s="31"/>
-    </row>
-    <row r="50" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="31"/>
-      <c r="Q50" s="31"/>
-    </row>
-    <row r="51" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M51" s="31"/>
-      <c r="N51" s="31"/>
-      <c r="O51" s="31"/>
-      <c r="P51" s="31"/>
-      <c r="Q51" s="31"/>
-    </row>
-    <row r="52" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M52" s="31"/>
-      <c r="N52" s="31"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="31"/>
-      <c r="Q52" s="31"/>
-    </row>
-    <row r="53" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-    </row>
-    <row r="54" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M54" s="31"/>
-      <c r="N54" s="31"/>
-      <c r="O54" s="31"/>
-      <c r="P54" s="31"/>
-      <c r="Q54" s="31"/>
-    </row>
-    <row r="55" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M55" s="31"/>
-      <c r="N55" s="31"/>
-      <c r="O55" s="31"/>
-      <c r="P55" s="31"/>
-      <c r="Q55" s="31"/>
-    </row>
-    <row r="56" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M56" s="31"/>
-      <c r="N56" s="31"/>
-      <c r="O56" s="31"/>
-      <c r="P56" s="31"/>
-      <c r="Q56" s="31"/>
-    </row>
-    <row r="57" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M57" s="31"/>
-      <c r="N57" s="31"/>
-      <c r="O57" s="31"/>
-      <c r="P57" s="31"/>
-      <c r="Q57" s="31"/>
-    </row>
-    <row r="58" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M58" s="31"/>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-    </row>
-    <row r="59" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M59" s="31"/>
-      <c r="N59" s="31"/>
-      <c r="O59" s="31"/>
-      <c r="P59" s="31"/>
-      <c r="Q59" s="31"/>
-    </row>
-    <row r="60" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M60" s="31"/>
-      <c r="N60" s="31"/>
-      <c r="O60" s="31"/>
-      <c r="P60" s="31"/>
-      <c r="Q60" s="31"/>
-    </row>
-    <row r="61" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="13:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <dataValidations disablePrompts="1" count="9">
     <dataValidation type="list" sqref="G26" xr:uid="{C3ECF952-F6F6-411D-8935-CDC103B5D4EC}">
       <formula1>"SPAN,RSPAN,ERSPAN"</formula1>
     </dataValidation>
@@ -9429,19 +9401,19 @@
         <v>60</v>
       </c>
       <c r="C1" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="G1" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="17" t="s">
         <v>87</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
@@ -9452,19 +9424,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="16">
         <v>67</v>
       </c>
       <c r="E2" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="H2" s="18" t="s">
         <v>91</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
@@ -9475,19 +9447,19 @@
         <v>49</v>
       </c>
       <c r="C3" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="E3" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="18" t="s">
+      <c r="H3" s="18" t="s">
         <v>95</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
@@ -9498,19 +9470,19 @@
         <v>9</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" s="16">
         <v>67</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G4" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="18" t="s">
         <v>97</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
@@ -9521,19 +9493,19 @@
         <v>51</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>94</v>
-      </c>
       <c r="E5" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G5" s="18" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
@@ -9541,22 +9513,22 @@
         <v>51</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="16">
         <v>53</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G6" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="18" t="s">
         <v>102</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
@@ -9564,22 +9536,22 @@
         <v>51</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="16">
         <v>53</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G7" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>105</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
@@ -9587,22 +9559,22 @@
         <v>51</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" s="16">
         <v>80</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>54</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
@@ -9610,22 +9582,22 @@
         <v>51</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D9" s="16">
         <v>443</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>109</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -9636,13 +9608,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" s="16">
         <v>67</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -9653,13 +9625,13 @@
         <v>52</v>
       </c>
       <c r="C11" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>94</v>
-      </c>
       <c r="E11" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -9670,13 +9642,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="16">
         <v>67</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -9687,13 +9659,13 @@
         <v>53</v>
       </c>
       <c r="C13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>94</v>
-      </c>
       <c r="E13" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -9704,27 +9676,27 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
         <v>93</v>
       </c>
-      <c r="D14" t="s">
-        <v>94</v>
-      </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" t="s">
         <v>111</v>
-      </c>
-      <c r="H14" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G15" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" t="s">
         <v>113</v>
-      </c>
-      <c r="H15" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nanik\Music\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2191D201-465A-438B-BCC1-E858E61FAFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15D5477-CE90-46C5-9E5A-248963FBC5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
@@ -654,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -787,9 +787,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -799,9 +796,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -809,643 +803,643 @@
   <dxfs count="171">
     <dxf>
       <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <sz val="11"/>
         <color auto="1"/>
         <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
@@ -2355,27 +2349,27 @@
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{D32D18C4-0B05-425E-B28E-67E8EEF86C01}" name="Tabell16182428253212" displayName="Tabell16182428253212" ref="A28:Q29" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{3D2619F9-8A27-48B4-BBAD-F8DAD24B7058}" name="SW" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{3D2619F9-8A27-48B4-BBAD-F8DAD24B7058}" name="SW" dataDxfId="122">
       <calculatedColumnFormula>ROW()-28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{79D48293-3CC1-4FC8-B959-C76EC31AF05A}" name="MGMT Vlan" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{79D48293-3CC1-4FC8-B959-C76EC31AF05A}" name="MGMT Vlan" dataDxfId="121">
       <calculatedColumnFormula>$B$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{636012CC-2311-45D4-B0A3-CBE1DDB288EA}" name="MGMT ip" dataDxfId="10">
+    <tableColumn id="3" xr3:uid="{636012CC-2311-45D4-B0A3-CBE1DDB288EA}" name="MGMT ip" dataDxfId="120">
       <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{57B036DD-2EC2-46AB-BA82-15C2E4251EE3}" name="gateway" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{57B036DD-2EC2-46AB-BA82-15C2E4251EE3}" name="gateway" dataDxfId="119">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D16308A-64E5-4F82-9997-B8BD8FE03B86}" name="mask" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{6D16308A-64E5-4F82-9997-B8BD8FE03B86}" name="mask" dataDxfId="118">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{10263F16-185C-4388-8A92-6BC4CA0E07C5}" name="num_ports_tot" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{337036FB-EC4A-4A8B-A2D4-886EF58ACF98}" name="skiped_ports" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{75ED65B8-97AC-498A-9CF3-0A234BF7E9F1}" name="num_downlink" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{D2EB23FE-1E37-4D17-B4EC-11CAC9B6F0DC}" name="vlan-antall" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{0815D94A-1C82-4867-98BC-98ABBA28ECDE}" name="intf_prefix" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{CDF41783-F241-44AB-837D-97EDFE6911D4}" name="num_port_ledig" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{10263F16-185C-4388-8A92-6BC4CA0E07C5}" name="num_ports_tot" dataDxfId="117"/>
+    <tableColumn id="11" xr3:uid="{337036FB-EC4A-4A8B-A2D4-886EF58ACF98}" name="skiped_ports" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{75ED65B8-97AC-498A-9CF3-0A234BF7E9F1}" name="num_downlink" dataDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{D2EB23FE-1E37-4D17-B4EC-11CAC9B6F0DC}" name="vlan-antall" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{0815D94A-1C82-4867-98BC-98ABBA28ECDE}" name="intf_prefix" dataDxfId="113"/>
+    <tableColumn id="9" xr3:uid="{CDF41783-F241-44AB-837D-97EDFE6911D4}" name="num_port_ledig" dataDxfId="112">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{AACD1EB8-91AF-4962-8481-F05F6073247E}" name="MONITORING ip"/>
@@ -2408,7 +2402,7 @@
     <tableColumn id="8" xr3:uid="{09FF5408-B542-4803-BB81-19C6D96455ED}" name="address max">
       <calculatedColumnFormula>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1C2CE40E-C587-4306-B04C-05E7E830B912}" name="antall-res" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{1C2CE40E-C587-4306-B04C-05E7E830B912}" name="antall-res" dataDxfId="111"/>
     <tableColumn id="10" xr3:uid="{062A0975-F29C-4725-993D-1C745C38968F}" name=" "/>
     <tableColumn id="11" xr3:uid="{E9F272DB-833F-4003-8FE1-C3489DCBD223}" name="pri-1-10"/>
   </tableColumns>
@@ -2430,97 +2424,97 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C60AC8E-4581-4040-8CC5-F80E674B402C}" name="Tabell182" displayName="Tabell182" ref="A1:AA2" dataDxfId="170">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C60AC8E-4581-4040-8CC5-F80E674B402C}" name="Tabell182" displayName="Tabell182" ref="A1:AA2" dataDxfId="59">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{DFCE91FF-608A-44ED-A5CB-ACD8B514AF73}" name="site" dataDxfId="169"/>
-    <tableColumn id="2" xr3:uid="{5DF854F6-DD6B-482C-B348-01B229D7B185}" name="intf_prefix" dataDxfId="168"/>
-    <tableColumn id="3" xr3:uid="{790C3FB9-3DCF-4CFE-B434-3841F3F4CF2D}" name="router-id" dataDxfId="167">
+    <tableColumn id="1" xr3:uid="{DFCE91FF-608A-44ED-A5CB-ACD8B514AF73}" name="site" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{5DF854F6-DD6B-482C-B348-01B229D7B185}" name="intf_prefix" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{790C3FB9-3DCF-4CFE-B434-3841F3F4CF2D}" name="router-id" dataDxfId="56">
       <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FA3F5E0E-C16D-4EA4-BDD0-AB9FF9D36A22}" name="brukernavn" dataDxfId="166"/>
-    <tableColumn id="5" xr3:uid="{D4D947B6-A29A-4505-A4DA-815913EDDA88}" name="passord" dataDxfId="165"/>
-    <tableColumn id="6" xr3:uid="{7A49D571-9CC6-43ED-B79F-D38304D89536}" name="vty_lines" dataDxfId="164"/>
-    <tableColumn id="7" xr3:uid="{12F1C824-518B-4333-B662-47EC33509F9D}" name="secret" dataDxfId="163"/>
-    <tableColumn id="8" xr3:uid="{0DDBDB15-F6E1-4438-8FA4-CBDC7F940431}" name="tacacs_key" dataDxfId="162">
+    <tableColumn id="4" xr3:uid="{FA3F5E0E-C16D-4EA4-BDD0-AB9FF9D36A22}" name="brukernavn" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{D4D947B6-A29A-4505-A4DA-815913EDDA88}" name="passord" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{7A49D571-9CC6-43ED-B79F-D38304D89536}" name="vty_lines" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{12F1C824-518B-4333-B662-47EC33509F9D}" name="secret" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{0DDBDB15-F6E1-4438-8FA4-CBDC7F940431}" name="tacacs_key" dataDxfId="51">
       <calculatedColumnFormula>'Site 1 (HUB)'!I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DCAD99D0-D61D-4F08-8352-0D7B17728799}" name="dns_servers" dataDxfId="161"/>
-    <tableColumn id="10" xr3:uid="{B6B56649-3DA3-4CFB-92A6-6719284F2DDA}" name="tacacs_server_ip" dataDxfId="160">
+    <tableColumn id="9" xr3:uid="{DCAD99D0-D61D-4F08-8352-0D7B17728799}" name="dns_servers" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{B6B56649-3DA3-4CFB-92A6-6719284F2DDA}" name="tacacs_server_ip" dataDxfId="49">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2734B32E-340C-4B96-8086-D16467942071}" name="syslog_server_ip" dataDxfId="159">
+    <tableColumn id="11" xr3:uid="{2734B32E-340C-4B96-8086-D16467942071}" name="syslog_server_ip" dataDxfId="48">
       <calculatedColumnFormula>'Site 1 (HUB)'!M2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{932EA2FA-00C9-4B65-96DE-2A8C7CCC9623}" name="urpf_mode" dataDxfId="158"/>
-    <tableColumn id="14" xr3:uid="{0A05EAA9-4619-4CC8-AF17-9890232CE0A7}" name="radius_server_ip" dataDxfId="157">
+    <tableColumn id="12" xr3:uid="{932EA2FA-00C9-4B65-96DE-2A8C7CCC9623}" name="urpf_mode" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{0A05EAA9-4619-4CC8-AF17-9890232CE0A7}" name="radius_server_ip" dataDxfId="46">
       <calculatedColumnFormula>'Site 1 (HUB)'!O2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{B3F95825-6EF4-4409-B363-0BE17244502B}" name="radius_key" dataDxfId="156">
+    <tableColumn id="15" xr3:uid="{B3F95825-6EF4-4409-B363-0BE17244502B}" name="radius_key" dataDxfId="45">
       <calculatedColumnFormula>'Site 1 (HUB)'!P2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{58ECFE80-A988-475F-BD24-A26F8EFC7A8D}" name="tacacs_syntax" dataDxfId="155"/>
-    <tableColumn id="16" xr3:uid="{79E9C26B-4DDA-44F0-88A9-BD1FFF65EA6D}" name="radius_syntax" dataDxfId="154"/>
-    <tableColumn id="17" xr3:uid="{45BFC1E5-9227-484E-A609-C4DBCB058F2C}" name="dot1x_syntax" dataDxfId="153"/>
-    <tableColumn id="18" xr3:uid="{DE5CD905-AB0A-4281-96DD-1500626743D4}" name="eigrp_syntax" dataDxfId="152"/>
-    <tableColumn id="19" xr3:uid="{B072AF5E-0DB2-49BB-8F74-FA3249A788FE}" name="vrf_syntax" dataDxfId="151"/>
-    <tableColumn id="20" xr3:uid="{6706F7F4-BF14-4761-9D16-BD6D20F80622}" name="ike_version" dataDxfId="150"/>
-    <tableColumn id="21" xr3:uid="{1A182393-1100-428B-8B4D-9AFB98D01661}" name="secret_type" dataDxfId="149"/>
-    <tableColumn id="22" xr3:uid="{49E7B89A-8DF7-4889-839B-D8838B6390C7}" name="trunk_encapsulation" dataDxfId="148"/>
-    <tableColumn id="23" xr3:uid="{FAA8BF28-43AD-4E66-BF05-ACADD2A986A6}" name="snmpv3_enabled" dataDxfId="147"/>
-    <tableColumn id="24" xr3:uid="{BE8ED0D7-0829-4E21-8670-4897E3ADE322}" name="snmp_server_ip" dataDxfId="146"/>
-    <tableColumn id="25" xr3:uid="{C61E16D6-489B-4639-A0C5-A22F2664CCB2}" name="snmp_user" dataDxfId="145"/>
-    <tableColumn id="26" xr3:uid="{2900EC79-7717-462E-B651-5F02EAEE0440}" name="snmp_auth_password" dataDxfId="144"/>
-    <tableColumn id="27" xr3:uid="{CC2C2D42-240D-452D-B846-BB1DEF70F8D8}" name="snmp_priv_password" dataDxfId="143"/>
+    <tableColumn id="13" xr3:uid="{58ECFE80-A988-475F-BD24-A26F8EFC7A8D}" name="tacacs_syntax" dataDxfId="44"/>
+    <tableColumn id="16" xr3:uid="{79E9C26B-4DDA-44F0-88A9-BD1FFF65EA6D}" name="radius_syntax" dataDxfId="43"/>
+    <tableColumn id="17" xr3:uid="{45BFC1E5-9227-484E-A609-C4DBCB058F2C}" name="dot1x_syntax" dataDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{DE5CD905-AB0A-4281-96DD-1500626743D4}" name="eigrp_syntax" dataDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{B072AF5E-0DB2-49BB-8F74-FA3249A788FE}" name="vrf_syntax" dataDxfId="40"/>
+    <tableColumn id="20" xr3:uid="{6706F7F4-BF14-4761-9D16-BD6D20F80622}" name="ike_version" dataDxfId="39"/>
+    <tableColumn id="21" xr3:uid="{1A182393-1100-428B-8B4D-9AFB98D01661}" name="secret_type" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{49E7B89A-8DF7-4889-839B-D8838B6390C7}" name="trunk_encapsulation" dataDxfId="37"/>
+    <tableColumn id="23" xr3:uid="{FAA8BF28-43AD-4E66-BF05-ACADD2A986A6}" name="snmpv3_enabled" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{BE8ED0D7-0829-4E21-8670-4897E3ADE322}" name="snmp_server_ip" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{C61E16D6-489B-4639-A0C5-A22F2664CCB2}" name="snmp_user" dataDxfId="34"/>
+    <tableColumn id="26" xr3:uid="{2900EC79-7717-462E-B651-5F02EAEE0440}" name="snmp_auth_password" dataDxfId="33"/>
+    <tableColumn id="27" xr3:uid="{CC2C2D42-240D-452D-B846-BB1DEF70F8D8}" name="snmp_priv_password" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47444F68-52DD-4020-A8C3-121097047CE4}" name="Tabell493" displayName="Tabell493" ref="A18:J23" dataDxfId="142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47444F68-52DD-4020-A8C3-121097047CE4}" name="Tabell493" displayName="Tabell493" ref="A18:J23" dataDxfId="31">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{55B6356B-AFF1-4386-837E-122F110FE048}" name="tunnel id" dataDxfId="141"/>
-    <tableColumn id="2" xr3:uid="{B5627186-AB74-4D83-9392-91908D53F7BB}" name="vrf" dataDxfId="140"/>
-    <tableColumn id="3" xr3:uid="{5D8B1DCA-3FFB-4C14-9357-5B2911B0414B}" name="ip address" dataDxfId="139">
+    <tableColumn id="1" xr3:uid="{55B6356B-AFF1-4386-837E-122F110FE048}" name="tunnel id" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{B5627186-AB74-4D83-9392-91908D53F7BB}" name="vrf" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{5D8B1DCA-3FFB-4C14-9357-5B2911B0414B}" name="ip address" dataDxfId="28">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5E9F71E8-6C96-465D-8829-6F95E415C54C}" name="mask" dataDxfId="138"/>
-    <tableColumn id="5" xr3:uid="{04B93F27-2105-4CD1-8282-A96667B8D048}" name="source" dataDxfId="137">
+    <tableColumn id="4" xr3:uid="{5E9F71E8-6C96-465D-8829-6F95E415C54C}" name="mask" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{04B93F27-2105-4CD1-8282-A96667B8D048}" name="source" dataDxfId="26">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4F9F6E3C-23F1-4807-9408-1055BD20C8BE}" name="destination" dataDxfId="136"/>
-    <tableColumn id="7" xr3:uid="{63AC65C8-779A-43ED-8BCC-861F84A05B7B}" name="gre mode" dataDxfId="135"/>
-    <tableColumn id="8" xr3:uid="{12CFCF68-1AA6-478A-A878-30BEAAD47165}" name="network-id" dataDxfId="134"/>
-    <tableColumn id="9" xr3:uid="{96158AEC-6587-4768-B48B-03A505CBF781}" name="ipsec" dataDxfId="133">
+    <tableColumn id="6" xr3:uid="{4F9F6E3C-23F1-4807-9408-1055BD20C8BE}" name="destination" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{63AC65C8-779A-43ED-8BCC-861F84A05B7B}" name="gre mode" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{12CFCF68-1AA6-478A-A878-30BEAAD47165}" name="network-id" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{96158AEC-6587-4768-B48B-03A505CBF781}" name="ipsec" dataDxfId="22">
       <calculatedColumnFormula>'Site 1 (HUB)'!I19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8928B759-FF4A-40F1-971D-0C0EE8DD40B4}" name="ipsec key" dataDxfId="132"/>
+    <tableColumn id="10" xr3:uid="{8928B759-FF4A-40F1-971D-0C0EE8DD40B4}" name="ipsec key" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D4039491-9BC9-46AA-ACDA-873C6CFE06D8}" name="Tabell13192530107" displayName="Tabell13192530107" ref="A25:H26" dataDxfId="131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D4039491-9BC9-46AA-ACDA-873C6CFE06D8}" name="Tabell13192530107" displayName="Tabell13192530107" ref="A25:H26" dataDxfId="20">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{5FE8027B-1EBD-40FA-9138-BFA1D40F7043}" name="site" dataDxfId="130">
+    <tableColumn id="1" xr3:uid="{5FE8027B-1EBD-40FA-9138-BFA1D40F7043}" name="site" dataDxfId="19">
       <calculatedColumnFormula>$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{328AA2B5-7A14-44F9-B093-0500F8F3797B}" name="brukernavn" dataDxfId="129">
+    <tableColumn id="4" xr3:uid="{328AA2B5-7A14-44F9-B093-0500F8F3797B}" name="brukernavn" dataDxfId="18">
       <calculatedColumnFormula>$D$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{03DDB2FF-50BB-44A4-9A30-EAB05A418213}" name="passord" dataDxfId="128">
+    <tableColumn id="5" xr3:uid="{03DDB2FF-50BB-44A4-9A30-EAB05A418213}" name="passord" dataDxfId="17">
       <calculatedColumnFormula>$E$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1297971E-A08E-4A6B-9A9B-6BE6B919F309}" name="vty_lines" dataDxfId="127">
+    <tableColumn id="3" xr3:uid="{1297971E-A08E-4A6B-9A9B-6BE6B919F309}" name="vty_lines" dataDxfId="16">
       <calculatedColumnFormula>$F$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C8384C9-AA8F-4EF7-A6C3-F4B2C5EF2EAC}" name="secret" dataDxfId="126">
+    <tableColumn id="2" xr3:uid="{0C8384C9-AA8F-4EF7-A6C3-F4B2C5EF2EAC}" name="secret" dataDxfId="15">
       <calculatedColumnFormula>$G$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{2CA86CB3-1D71-42BA-A7B0-DBD5BB2916B6}" name="etherchan_num" dataDxfId="125"/>
-    <tableColumn id="7" xr3:uid="{755D61CE-A84F-47D5-B7F6-717BDFC54940}" name="span_mode" dataDxfId="124"/>
-    <tableColumn id="8" xr3:uid="{D00F4A82-CD6D-4CB8-AE6D-E90F4F86412E}" name="dot1x_vlans" dataDxfId="123"/>
+    <tableColumn id="6" xr3:uid="{2CA86CB3-1D71-42BA-A7B0-DBD5BB2916B6}" name="etherchan_num" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{755D61CE-A84F-47D5-B7F6-717BDFC54940}" name="span_mode" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{D00F4A82-CD6D-4CB8-AE6D-E90F4F86412E}" name="dot1x_vlans" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2529,27 +2523,27 @@
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{763708C6-BBA5-4081-A5A6-5F727C0852E6}" name="Tabell1618242825321216" displayName="Tabell1618242825321216" ref="A28:Q30" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{45194AB5-B480-4B1A-B95B-CA50B65B1264}" name="SW" dataDxfId="122">
+    <tableColumn id="1" xr3:uid="{45194AB5-B480-4B1A-B95B-CA50B65B1264}" name="SW" dataDxfId="11">
       <calculatedColumnFormula>ROW()-28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E26F807A-4589-44B4-82F1-D4548A0F0070}" name="MGMT Vlan" dataDxfId="121">
+    <tableColumn id="2" xr3:uid="{E26F807A-4589-44B4-82F1-D4548A0F0070}" name="MGMT Vlan" dataDxfId="10">
       <calculatedColumnFormula>$B$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6109B699-5B93-4FEA-8E30-9F0B359DB86F}" name="MGMT ip" dataDxfId="120">
+    <tableColumn id="3" xr3:uid="{6109B699-5B93-4FEA-8E30-9F0B359DB86F}" name="MGMT ip" dataDxfId="9">
       <calculatedColumnFormula>10&amp;"."&amp;$A$2&amp;"."&amp;$B$5&amp;"."&amp;(A29+1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{90803DA6-8268-4AAF-94FC-6CB82C7D1B68}" name="gateway" dataDxfId="119">
+    <tableColumn id="4" xr3:uid="{90803DA6-8268-4AAF-94FC-6CB82C7D1B68}" name="gateway" dataDxfId="8">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A7E5E398-6D1D-4B22-8003-FDDC8C87876E}" name="mask" dataDxfId="118">
+    <tableColumn id="5" xr3:uid="{A7E5E398-6D1D-4B22-8003-FDDC8C87876E}" name="mask" dataDxfId="7">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B5FC786B-C70A-4E77-B469-9373A58198A2}" name="num_ports_tot" dataDxfId="117"/>
-    <tableColumn id="11" xr3:uid="{A766979F-B52B-4052-9122-D365A4600150}" name="skiped_ports" dataDxfId="116"/>
-    <tableColumn id="6" xr3:uid="{956ED757-3CF2-47A9-83E1-224C04FC15E2}" name="num_downlink" dataDxfId="115"/>
-    <tableColumn id="7" xr3:uid="{AC8CB3C3-95F4-48BC-A5C7-7D1BC47D2896}" name="vlan-antall" dataDxfId="114"/>
-    <tableColumn id="8" xr3:uid="{DFD5F6B7-25A1-4113-847E-63C8C8D1F3A5}" name="intf_prefix" dataDxfId="113"/>
-    <tableColumn id="9" xr3:uid="{6240FEDA-0A81-4D8B-9087-893236958125}" name="num_port_ledig" dataDxfId="112">
+    <tableColumn id="10" xr3:uid="{B5FC786B-C70A-4E77-B469-9373A58198A2}" name="num_ports_tot" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{A766979F-B52B-4052-9122-D365A4600150}" name="skiped_ports" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{956ED757-3CF2-47A9-83E1-224C04FC15E2}" name="num_downlink" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{AC8CB3C3-95F4-48BC-A5C7-7D1BC47D2896}" name="vlan-antall" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{DFD5F6B7-25A1-4113-847E-63C8C8D1F3A5}" name="intf_prefix" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{6240FEDA-0A81-4D8B-9087-893236958125}" name="num_port_ledig" dataDxfId="1">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{B80135C7-C94A-4B44-9E4B-48954B72D5AF}" name="MONITORING ip"/>
@@ -2582,7 +2576,7 @@
     <tableColumn id="8" xr3:uid="{36B80577-2EA1-4CA8-A93B-C744BC10CA3F}" name="address max">
       <calculatedColumnFormula>(VALUE(LEFT(D5,FIND(".",D5)-1))+255-VALUE(LEFT(F5,FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5)+1,FIND(".",D5,FIND(".",D5)+1)-FIND(".",D5)-1))+255-VALUE(MID(F5,FIND(".",F5)+1,FIND(".",F5,FIND(".",F5)+1)-FIND(".",F5)-1)))&amp;"."&amp;(VALUE(MID(D5,FIND(".",D5,FIND(".",D5)+1)+1,FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)-FIND(".",D5,FIND(".",D5)+1)-1))+255-VALUE(MID(F5,FIND(".",F5,FIND(".",F5)+1)+1,FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)-FIND(".",F5,FIND(".",F5)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D5,LEN(D5)-FIND(".",D5,FIND(".",D5,FIND(".",D5)+1)+1)))+255-VALUE(RIGHT(F5,LEN(F5)-FIND(".",F5,FIND(".",F5,FIND(".",F5)+1)+1)))-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{452A6983-A082-48CF-A21D-B00E01BAEC99}" name="antall-res" dataDxfId="111"/>
+    <tableColumn id="9" xr3:uid="{452A6983-A082-48CF-A21D-B00E01BAEC99}" name="antall-res" dataDxfId="0"/>
     <tableColumn id="10" xr3:uid="{7CD1C757-50B2-45D7-B177-2458072FF692}" name=" "/>
     <tableColumn id="11" xr3:uid="{585E7ADE-9615-485F-8639-F60F08837CB8}" name="pri-1-10"/>
   </tableColumns>
@@ -2691,8 +2685,8 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="secret" dataDxfId="76"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="etherchan_num" dataDxfId="75"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="span_mode" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="73">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="dot1x_vlans" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="ISP-VLAN" dataDxfId="72">
       <calculatedColumnFormula array="1">Tabell5[ISP-VLAN]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2703,28 +2697,28 @@
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A28:Q29" totalsRowShown="0">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="72">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="SW" dataDxfId="71">
       <calculatedColumnFormula>ROW()-28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="70">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="MGMT Vlan" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="MGMT ip" dataDxfId="69">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A29)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="69">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="gateway" dataDxfId="68">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="68">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="mask" dataDxfId="67">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="67"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="62">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="num_ports_tot" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="skiped_ports" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="num_downlink" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="vlan-antall" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="intf_prefix" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="num_port_ledig" dataDxfId="61">
       <calculatedColumnFormula>IF($A29=1,F29-G29-H29*$F$26-2-IF($L$2&lt;&gt;$M$2,1,0)-IF(OR(UPPER($G$26)="SPAN",UPPER($G$26)="ERSPAN",UPPER($G$26)="RSPAN"),1,0),F29-G29-(1+H29)*$F$26-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="61"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0500-00000C000000}" name="MONITORING ip" dataDxfId="60"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0500-00000D000000}" name="tacacs_syntax"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0500-00000E000000}" name="radius_syntax"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0500-00000F000000}" name="dot1x_syntax"/>
@@ -2736,97 +2730,97 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51BF1746-4E83-4B5C-8E47-1B33E5F0C823}" name="Tabell18" displayName="Tabell18" ref="A1:AA2" dataDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{51BF1746-4E83-4B5C-8E47-1B33E5F0C823}" name="Tabell18" displayName="Tabell18" ref="A1:AA2" dataDxfId="170">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{F301071E-AB49-411D-B862-3D5F1A8652F4}" name="site" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{28087ADC-D839-428A-B3B6-5D33053FC989}" name="intf_prefix" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{E07A6BD4-5C25-4907-8DBF-B7CD7A55F1D8}" name="router-id" dataDxfId="57">
+    <tableColumn id="1" xr3:uid="{F301071E-AB49-411D-B862-3D5F1A8652F4}" name="site" dataDxfId="169"/>
+    <tableColumn id="2" xr3:uid="{28087ADC-D839-428A-B3B6-5D33053FC989}" name="intf_prefix" dataDxfId="168"/>
+    <tableColumn id="3" xr3:uid="{E07A6BD4-5C25-4907-8DBF-B7CD7A55F1D8}" name="router-id" dataDxfId="167">
       <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E5D534F2-DADF-4E06-844E-EFC868A109BF}" name="brukernavn" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{8E37AE50-BD24-4C9E-97D1-6B548927DBB7}" name="passord" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{0A3407AA-8EBE-4074-85F9-778319C50E4E}" name="vty_lines" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{0E482BA6-C79D-40DB-B45E-FDC671702D74}" name="secret" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{C39694E5-0D09-45FB-A48D-8E9A8C91CA0E}" name="tacacs_key" dataDxfId="52">
+    <tableColumn id="4" xr3:uid="{E5D534F2-DADF-4E06-844E-EFC868A109BF}" name="brukernavn" dataDxfId="166"/>
+    <tableColumn id="5" xr3:uid="{8E37AE50-BD24-4C9E-97D1-6B548927DBB7}" name="passord" dataDxfId="165"/>
+    <tableColumn id="6" xr3:uid="{0A3407AA-8EBE-4074-85F9-778319C50E4E}" name="vty_lines" dataDxfId="164"/>
+    <tableColumn id="7" xr3:uid="{0E482BA6-C79D-40DB-B45E-FDC671702D74}" name="secret" dataDxfId="163"/>
+    <tableColumn id="8" xr3:uid="{C39694E5-0D09-45FB-A48D-8E9A8C91CA0E}" name="tacacs_key" dataDxfId="162">
       <calculatedColumnFormula>'Site 1 (HUB)'!I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{44EB3B31-5D13-48ED-A202-643DB3DE780D}" name="dns_servers" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{97E12567-6CA3-4115-A196-2529D7160615}" name="tacacs_server_ip" dataDxfId="50">
+    <tableColumn id="9" xr3:uid="{44EB3B31-5D13-48ED-A202-643DB3DE780D}" name="dns_servers" dataDxfId="161"/>
+    <tableColumn id="10" xr3:uid="{97E12567-6CA3-4115-A196-2529D7160615}" name="tacacs_server_ip" dataDxfId="160">
       <calculatedColumnFormula>'Site 1 (HUB)'!L2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{0346B8E5-A202-466C-AB4B-67EDD69B81A1}" name="syslog_server_ip" dataDxfId="49">
+    <tableColumn id="11" xr3:uid="{0346B8E5-A202-466C-AB4B-67EDD69B81A1}" name="syslog_server_ip" dataDxfId="159">
       <calculatedColumnFormula>'Site 1 (HUB)'!M2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE86801E-B0D0-4B58-832A-86AC77A7EC9A}" name="urpf_mode" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{5AAC65E5-8130-4C09-99B3-54C834DEE5C1}" name="radius_server_ip" dataDxfId="47">
+    <tableColumn id="12" xr3:uid="{EE86801E-B0D0-4B58-832A-86AC77A7EC9A}" name="urpf_mode" dataDxfId="158"/>
+    <tableColumn id="14" xr3:uid="{5AAC65E5-8130-4C09-99B3-54C834DEE5C1}" name="radius_server_ip" dataDxfId="157">
       <calculatedColumnFormula>'Site 1 (HUB)'!O2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1C900422-8FD8-4B49-B19A-47F4CE877466}" name="radius_key" dataDxfId="46">
+    <tableColumn id="15" xr3:uid="{1C900422-8FD8-4B49-B19A-47F4CE877466}" name="radius_key" dataDxfId="156">
       <calculatedColumnFormula>'Site 1 (HUB)'!P2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{AD662EC0-7940-4F3A-8F56-38E0BAEE7E2B}" name="tacacs_syntax" dataDxfId="45"/>
-    <tableColumn id="16" xr3:uid="{103CB279-D718-4AF9-A977-B976A8B36356}" name="radius_syntax" dataDxfId="44"/>
-    <tableColumn id="17" xr3:uid="{3496AD74-0539-4463-997F-A1CA64512F54}" name="dot1x_syntax" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{F8B1DCD1-84B0-4090-BDAB-AD6FA5328F3C}" name="eigrp_syntax" dataDxfId="42"/>
-    <tableColumn id="19" xr3:uid="{E8281F74-01EE-4CFD-8DF1-C429390E1E04}" name="vrf_syntax" dataDxfId="41"/>
-    <tableColumn id="20" xr3:uid="{9FA158AF-3041-42DD-9BB3-CA83FCDE6CA1}" name="ike_version" dataDxfId="40"/>
-    <tableColumn id="21" xr3:uid="{045B3C14-6117-44CA-9A5A-D8BA1860F47E}" name="secret_type" dataDxfId="39"/>
-    <tableColumn id="22" xr3:uid="{3829C8E8-1959-4691-AF37-5B45456BC812}" name="trunk_encapsulation" dataDxfId="38"/>
-    <tableColumn id="23" xr3:uid="{4CE3B16C-67F6-4DC2-9BB2-F8E09C5C8D74}" name="snmpv3_enabled" dataDxfId="37"/>
-    <tableColumn id="24" xr3:uid="{7E57634C-C61D-454F-83A9-CCC1D7A3E9A7}" name="snmp_server_ip" dataDxfId="36"/>
-    <tableColumn id="25" xr3:uid="{DA892339-1F60-44AE-B105-D466545319B6}" name="snmp_user" dataDxfId="35"/>
-    <tableColumn id="26" xr3:uid="{10EE6F10-8503-4A58-9CA0-8FB438354050}" name="snmp_auth_password" dataDxfId="34"/>
-    <tableColumn id="27" xr3:uid="{66121011-59AB-4D41-BDF5-22B7624358BE}" name="snmp_priv_password" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{AD662EC0-7940-4F3A-8F56-38E0BAEE7E2B}" name="tacacs_syntax" dataDxfId="155"/>
+    <tableColumn id="16" xr3:uid="{103CB279-D718-4AF9-A977-B976A8B36356}" name="radius_syntax" dataDxfId="154"/>
+    <tableColumn id="17" xr3:uid="{3496AD74-0539-4463-997F-A1CA64512F54}" name="dot1x_syntax" dataDxfId="153"/>
+    <tableColumn id="18" xr3:uid="{F8B1DCD1-84B0-4090-BDAB-AD6FA5328F3C}" name="eigrp_syntax" dataDxfId="152"/>
+    <tableColumn id="19" xr3:uid="{E8281F74-01EE-4CFD-8DF1-C429390E1E04}" name="vrf_syntax" dataDxfId="151"/>
+    <tableColumn id="20" xr3:uid="{9FA158AF-3041-42DD-9BB3-CA83FCDE6CA1}" name="ike_version" dataDxfId="150"/>
+    <tableColumn id="21" xr3:uid="{045B3C14-6117-44CA-9A5A-D8BA1860F47E}" name="secret_type" dataDxfId="149"/>
+    <tableColumn id="22" xr3:uid="{3829C8E8-1959-4691-AF37-5B45456BC812}" name="trunk_encapsulation" dataDxfId="148"/>
+    <tableColumn id="23" xr3:uid="{4CE3B16C-67F6-4DC2-9BB2-F8E09C5C8D74}" name="snmpv3_enabled" dataDxfId="147"/>
+    <tableColumn id="24" xr3:uid="{7E57634C-C61D-454F-83A9-CCC1D7A3E9A7}" name="snmp_server_ip" dataDxfId="146"/>
+    <tableColumn id="25" xr3:uid="{DA892339-1F60-44AE-B105-D466545319B6}" name="snmp_user" dataDxfId="145"/>
+    <tableColumn id="26" xr3:uid="{10EE6F10-8503-4A58-9CA0-8FB438354050}" name="snmp_auth_password" dataDxfId="144"/>
+    <tableColumn id="27" xr3:uid="{66121011-59AB-4D41-BDF5-22B7624358BE}" name="snmp_priv_password" dataDxfId="143"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A99B9E14-0F60-413C-83C8-281F7E727FAD}" name="Tabell49" displayName="Tabell49" ref="A18:J23" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A99B9E14-0F60-413C-83C8-281F7E727FAD}" name="Tabell49" displayName="Tabell49" ref="A18:J23" dataDxfId="142">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C939C381-1121-4153-B4EA-3E9AC4EFD622}" name="tunnel id" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{402267D7-3F42-4106-963C-A00D2C73C6A3}" name="vrf" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{4204F352-886B-4432-BF55-0DB72CCEC230}" name="ip address" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{C939C381-1121-4153-B4EA-3E9AC4EFD622}" name="tunnel id" dataDxfId="141"/>
+    <tableColumn id="2" xr3:uid="{402267D7-3F42-4106-963C-A00D2C73C6A3}" name="vrf" dataDxfId="140"/>
+    <tableColumn id="3" xr3:uid="{4204F352-886B-4432-BF55-0DB72CCEC230}" name="ip address" dataDxfId="139">
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;H19&amp;"."&amp;$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E652E851-68C8-44CC-A804-D4A898A26E6B}" name="mask" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{1B6660E8-062A-4243-A879-B9BBE79D61B2}" name="source" dataDxfId="27">
+    <tableColumn id="4" xr3:uid="{E652E851-68C8-44CC-A804-D4A898A26E6B}" name="mask" dataDxfId="138"/>
+    <tableColumn id="5" xr3:uid="{1B6660E8-062A-4243-A879-B9BBE79D61B2}" name="source" dataDxfId="137">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{31E83213-6808-4B06-B3A2-334B8AEA93A6}" name="destination" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{548BE719-FE15-47C2-BD8C-E15155610E6F}" name="gre mode" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{AC2699E3-BB2E-4992-9A64-D04428D784DC}" name="network-id" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{911A5F49-374E-494E-9F87-E559E2AEA74A}" name="ipsec" dataDxfId="23">
+    <tableColumn id="6" xr3:uid="{31E83213-6808-4B06-B3A2-334B8AEA93A6}" name="destination" dataDxfId="136"/>
+    <tableColumn id="7" xr3:uid="{548BE719-FE15-47C2-BD8C-E15155610E6F}" name="gre mode" dataDxfId="135"/>
+    <tableColumn id="8" xr3:uid="{AC2699E3-BB2E-4992-9A64-D04428D784DC}" name="network-id" dataDxfId="134"/>
+    <tableColumn id="9" xr3:uid="{911A5F49-374E-494E-9F87-E559E2AEA74A}" name="ipsec" dataDxfId="133">
       <calculatedColumnFormula>'Site 1 (HUB)'!I19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F9EF835F-35E0-4DBE-9B12-F79414F650B4}" name="ipsec key" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{F9EF835F-35E0-4DBE-9B12-F79414F650B4}" name="ipsec key" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DA31B441-D218-45B2-B01A-A4BBC8BD7979}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{DA31B441-D218-45B2-B01A-A4BBC8BD7979}" name="Tabell1319253010" displayName="Tabell1319253010" ref="A25:H26" dataDxfId="131">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F434D49E-3876-49A2-911F-716DB0E46944}" name="site" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{F434D49E-3876-49A2-911F-716DB0E46944}" name="site" dataDxfId="130">
       <calculatedColumnFormula>$A$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{96C6D5FD-CBC3-49D8-AFD4-9E1E09633C5A}" name="brukernavn" dataDxfId="19">
+    <tableColumn id="4" xr3:uid="{96C6D5FD-CBC3-49D8-AFD4-9E1E09633C5A}" name="brukernavn" dataDxfId="129">
       <calculatedColumnFormula>$D$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{038EE345-4494-4999-88D7-0BF36304D24C}" name="passord" dataDxfId="18">
+    <tableColumn id="5" xr3:uid="{038EE345-4494-4999-88D7-0BF36304D24C}" name="passord" dataDxfId="128">
       <calculatedColumnFormula>$E$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{770D33D1-BE1F-45C0-8F6C-2E9C2A15365F}" name="vty_lines" dataDxfId="17">
+    <tableColumn id="3" xr3:uid="{770D33D1-BE1F-45C0-8F6C-2E9C2A15365F}" name="vty_lines" dataDxfId="127">
       <calculatedColumnFormula>$F$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{87FFB71D-3185-4317-BD65-911279FF4E36}" name="secret" dataDxfId="16">
+    <tableColumn id="2" xr3:uid="{87FFB71D-3185-4317-BD65-911279FF4E36}" name="secret" dataDxfId="126">
       <calculatedColumnFormula>$G$2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{13F65231-00AD-4279-9566-BCCC6B905C94}" name="etherchan_num" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{32F614C6-376B-4371-8715-7B2614BB4DBC}" name="span_mode" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{70D4C587-3B90-40C4-BB6C-9CC884BED451}" name="dot1x_vlans" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{13F65231-00AD-4279-9566-BCCC6B905C94}" name="etherchan_num" dataDxfId="125"/>
+    <tableColumn id="7" xr3:uid="{32F614C6-376B-4371-8715-7B2614BB4DBC}" name="span_mode" dataDxfId="124"/>
+    <tableColumn id="8" xr3:uid="{70D4C587-3B90-40C4-BB6C-9CC884BED451}" name="dot1x_vlans" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3450,7 +3444,7 @@
       <c r="C9" s="7">
         <v>0</v>
       </c>
-      <c r="D9" s="49" t="str">
+      <c r="D9" s="7" t="str">
         <f>10&amp;"."&amp;$A$2&amp;"."&amp;B9&amp;".0"</f>
         <v>10.1.50.0</v>
       </c>
@@ -3465,7 +3459,7 @@
         <f t="shared" ref="G9" si="5">VALUE(LEFT(D9,FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))&amp;"."&amp;VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+1)</f>
         <v>10.1.50.1</v>
       </c>
-      <c r="H9" s="49" t="str">
+      <c r="H9" s="7" t="str">
         <f>(VALUE(LEFT(D9,FIND(".",D9)-1))+255-VALUE(LEFT(F9,FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9)+1,FIND(".",D9,FIND(".",D9)+1)-FIND(".",D9)-1))+255-VALUE(MID(F9,FIND(".",F9)+1,FIND(".",F9,FIND(".",F9)+1)-FIND(".",F9)-1)))&amp;"."&amp;(VALUE(MID(D9,FIND(".",D9,FIND(".",D9)+1)+1,FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)-FIND(".",D9,FIND(".",D9)+1)-1))+255-VALUE(MID(F9,FIND(".",F9,FIND(".",F9)+1)+1,FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)-FIND(".",F9,FIND(".",F9)+1)-1)))&amp;"."&amp;(VALUE(RIGHT(D9,LEN(D9)-FIND(".",D9,FIND(".",D9,FIND(".",D9)+1)+1)))+255-VALUE(RIGHT(F9,LEN(F9)-FIND(".",F9,FIND(".",F9,FIND(".",F9)+1)+1)))-1)</f>
         <v>10.1.50.254</v>
       </c>
@@ -3714,14 +3708,14 @@
       <c r="B23" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="49" t="str">
+      <c r="C23" s="7" t="str">
         <f>172&amp;"."&amp;16&amp;"."&amp;H23&amp;"."&amp;$A$2</f>
         <v>172.16.50.1</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="49" t="str">
+      <c r="E23" s="7" t="str">
         <f>$C$2</f>
         <v>1.1.1.0</v>
       </c>
@@ -3802,7 +3796,7 @@
       <c r="G26" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="47" t="s">
+      <c r="H26" s="46" t="s">
         <v>127</v>
       </c>
       <c r="I26" s="35" cm="1">
@@ -5859,11 +5853,11 @@
       <c r="D23" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="46" t="str">
+      <c r="E23" s="43" t="str">
         <f t="shared" si="8"/>
         <v>2.2.2.0</v>
       </c>
-      <c r="F23" s="47"/>
+      <c r="F23" s="46"/>
       <c r="G23" s="43" t="s">
         <v>66</v>
       </c>
@@ -5874,7 +5868,7 @@
         <f>'Site 1 (HUB)'!I23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="47"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5930,7 +5924,7 @@
       <c r="G26" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="47" t="s">
+      <c r="H26" s="46" t="s">
         <v>127</v>
       </c>
     </row>
@@ -7937,22 +7931,22 @@
       <c r="D22" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="46" t="str">
+      <c r="E22" s="43" t="str">
         <f t="shared" si="4"/>
         <v>3.3.3.0</v>
       </c>
-      <c r="F22" s="47"/>
+      <c r="F22" s="46"/>
       <c r="G22" s="43" t="s">
         <v>66</v>
       </c>
       <c r="H22" s="43">
         <v>40</v>
       </c>
-      <c r="I22" s="48" t="b">
+      <c r="I22" s="47" t="b">
         <f>'Site 1 (HUB)'!I22</f>
         <v>1</v>
       </c>
-      <c r="J22" s="47"/>
+      <c r="J22" s="46"/>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="44" t="s">
@@ -7963,27 +7957,27 @@
       </c>
       <c r="C23" s="43" t="str">
         <f t="shared" si="5"/>
-        <v>172.16.40.3</v>
+        <v>172.16.50.3</v>
       </c>
       <c r="D23" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="46" t="str">
+      <c r="E23" s="43" t="str">
         <f t="shared" si="4"/>
         <v>3.3.3.0</v>
       </c>
-      <c r="F23" s="47"/>
+      <c r="F23" s="46"/>
       <c r="G23" s="43" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="43">
-        <v>40</v>
-      </c>
-      <c r="I23" s="48" t="b">
+        <v>50</v>
+      </c>
+      <c r="I23" s="47" t="b">
         <f>'Site 1 (HUB)'!I23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="47"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8039,7 +8033,7 @@
       <c r="G26" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="47" t="s">
+      <c r="H26" s="46" t="s">
         <v>127</v>
       </c>
     </row>
